--- a/output/2025-04-22.xlsx
+++ b/output/2025-04-22.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="F14" t="n">
-        <v>7.87</v>
+        <v>7.73</v>
       </c>
       <c r="G14" t="n">
-        <v>333</v>
+        <v>337.2</v>
       </c>
       <c r="H14" t="n">
-        <v>30.2</v>
+        <v>38.4</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-57.87</v>
+        <v>60.17</v>
       </c>
       <c r="K14" t="n">
-        <v>32.64</v>
+        <v>-145.07</v>
       </c>
       <c r="L14" t="n">
-        <v>66.44</v>
+        <v>157.05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:52:54</t>
+          <t>05:52:09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="F15" t="n">
-        <v>7.45</v>
+        <v>7.4</v>
       </c>
       <c r="G15" t="n">
-        <v>329.5</v>
+        <v>325.9</v>
       </c>
       <c r="H15" t="n">
-        <v>39.4</v>
+        <v>31.2</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.4</v>
+        <v>28</v>
       </c>
       <c r="K15" t="n">
-        <v>-27.92</v>
+        <v>-159.07</v>
       </c>
       <c r="L15" t="n">
-        <v>29.79</v>
+        <v>161.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:55:50</t>
+          <t>05:54:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="F16" t="n">
-        <v>7.27</v>
+        <v>7.42</v>
       </c>
       <c r="G16" t="n">
-        <v>337.9</v>
+        <v>341.3</v>
       </c>
       <c r="H16" t="n">
-        <v>38.3</v>
+        <v>29.3</v>
       </c>
       <c r="I16" t="n">
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-74.31</v>
+        <v>36.3</v>
       </c>
       <c r="K16" t="n">
-        <v>-101.77</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>126.01</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:59:15</t>
+          <t>05:58:19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="F17" t="n">
-        <v>7.73</v>
+        <v>7.24</v>
       </c>
       <c r="G17" t="n">
-        <v>338.3</v>
+        <v>337.5</v>
       </c>
       <c r="H17" t="n">
-        <v>33</v>
+        <v>42.6</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-104.17</v>
+        <v>42.92</v>
       </c>
       <c r="K17" t="n">
-        <v>-57.97</v>
+        <v>122.93</v>
       </c>
       <c r="L17" t="n">
-        <v>119.22</v>
+        <v>130.21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:00:30</t>
+          <t>05:59:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="F18" t="n">
-        <v>7.5</v>
+        <v>6.94</v>
       </c>
       <c r="G18" t="n">
-        <v>343</v>
+        <v>316.1</v>
       </c>
       <c r="H18" t="n">
-        <v>34.9</v>
+        <v>29.4</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>35.69</v>
+        <v>171.97</v>
       </c>
       <c r="K18" t="n">
-        <v>54.14</v>
+        <v>178.57</v>
       </c>
       <c r="L18" t="n">
-        <v>64.84</v>
+        <v>247.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:02:13</t>
+          <t>06:00:45</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="F19" t="n">
-        <v>7.16</v>
+        <v>6.59</v>
       </c>
       <c r="G19" t="n">
-        <v>341.4</v>
+        <v>322.8</v>
       </c>
       <c r="H19" t="n">
-        <v>31.8</v>
+        <v>28.2</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>111.25</v>
+        <v>-64.97</v>
       </c>
       <c r="K19" t="n">
-        <v>116.6</v>
+        <v>23.53</v>
       </c>
       <c r="L19" t="n">
-        <v>161.16</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:08:22</t>
+          <t>06:05:23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="F20" t="n">
-        <v>7.06</v>
+        <v>7.4</v>
       </c>
       <c r="G20" t="n">
-        <v>330.9</v>
+        <v>325.5</v>
       </c>
       <c r="H20" t="n">
-        <v>34.6</v>
+        <v>36.6</v>
       </c>
       <c r="I20" t="n">
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-255.82</v>
+        <v>184.59</v>
       </c>
       <c r="K20" t="n">
-        <v>254.16</v>
+        <v>11.2</v>
       </c>
       <c r="L20" t="n">
-        <v>360.62</v>
+        <v>184.93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:09:54</t>
+          <t>06:07:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="F21" t="n">
-        <v>6.92</v>
+        <v>7.87</v>
       </c>
       <c r="G21" t="n">
-        <v>319.9</v>
+        <v>314.5</v>
       </c>
       <c r="H21" t="n">
-        <v>39.8</v>
+        <v>36.6</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-92.56</v>
+        <v>29.89</v>
       </c>
       <c r="K21" t="n">
-        <v>215.45</v>
+        <v>319.29</v>
       </c>
       <c r="L21" t="n">
-        <v>234.49</v>
+        <v>320.69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:10:46</t>
+          <t>06:10:05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="F22" t="n">
-        <v>6.93</v>
+        <v>7.07</v>
       </c>
       <c r="G22" t="n">
-        <v>324.7</v>
+        <v>340.8</v>
       </c>
       <c r="H22" t="n">
-        <v>29.9</v>
+        <v>33.6</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-151.41</v>
+        <v>-77.93000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-165.08</v>
+        <v>119.61</v>
       </c>
       <c r="L22" t="n">
-        <v>224</v>
+        <v>142.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:16:52</t>
+          <t>06:15:16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="F23" t="n">
-        <v>8.19</v>
+        <v>7.64</v>
       </c>
       <c r="G23" t="n">
-        <v>320.2</v>
+        <v>329.1</v>
       </c>
       <c r="H23" t="n">
-        <v>28.4</v>
+        <v>34.3</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.83</v>
+        <v>272.28</v>
       </c>
       <c r="K23" t="n">
-        <v>170.84</v>
+        <v>202.34</v>
       </c>
       <c r="L23" t="n">
-        <v>170.84</v>
+        <v>339.23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:17:43</t>
+          <t>06:17:49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="F24" t="n">
-        <v>7.89</v>
+        <v>7.74</v>
       </c>
       <c r="G24" t="n">
-        <v>325.8</v>
+        <v>332.3</v>
       </c>
       <c r="H24" t="n">
-        <v>38.1</v>
+        <v>35.6</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-246.36</v>
+        <v>-289.91</v>
       </c>
       <c r="K24" t="n">
-        <v>75.67</v>
+        <v>18.2</v>
       </c>
       <c r="L24" t="n">
-        <v>257.72</v>
+        <v>290.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:19:45</t>
+          <t>06:18:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="F25" t="n">
-        <v>7.36</v>
+        <v>7.89</v>
       </c>
       <c r="G25" t="n">
-        <v>332.5</v>
+        <v>332.4</v>
       </c>
       <c r="H25" t="n">
-        <v>30.8</v>
+        <v>34.5</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-339.22</v>
+        <v>-313.74</v>
       </c>
       <c r="K25" t="n">
-        <v>-159.73</v>
+        <v>278.19</v>
       </c>
       <c r="L25" t="n">
-        <v>374.94</v>
+        <v>419.31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:24:40</t>
+          <t>06:22:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="F26" t="n">
-        <v>7.95</v>
+        <v>7.25</v>
       </c>
       <c r="G26" t="n">
-        <v>334.5</v>
+        <v>339.1</v>
       </c>
       <c r="H26" t="n">
-        <v>29.3</v>
+        <v>37.7</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>45.06</v>
+        <v>-619.92</v>
       </c>
       <c r="K26" t="n">
-        <v>-612.23</v>
+        <v>-272.76</v>
       </c>
       <c r="L26" t="n">
-        <v>613.89</v>
+        <v>677.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:26:16</t>
+          <t>06:24:34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.86</v>
+        <v>2.17</v>
       </c>
       <c r="F27" t="n">
-        <v>7.73</v>
+        <v>7.38</v>
       </c>
       <c r="G27" t="n">
-        <v>320.8</v>
+        <v>341.6</v>
       </c>
       <c r="H27" t="n">
-        <v>42.9</v>
+        <v>34.5</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>521.37</v>
+        <v>393</v>
       </c>
       <c r="K27" t="n">
-        <v>122.71</v>
+        <v>-213.44</v>
       </c>
       <c r="L27" t="n">
-        <v>535.61</v>
+        <v>447.22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:27:08</t>
+          <t>06:26:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.24</v>
+        <v>2.51</v>
       </c>
       <c r="F28" t="n">
-        <v>7.67</v>
+        <v>6.86</v>
       </c>
       <c r="G28" t="n">
-        <v>333.6</v>
+        <v>343.4</v>
       </c>
       <c r="H28" t="n">
-        <v>33.7</v>
+        <v>34.7</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-36.26</v>
+        <v>-158.9</v>
       </c>
       <c r="K28" t="n">
-        <v>323.28</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>325.31</v>
+        <v>159.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:36:47</t>
+          <t>06:35:51</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="F29" t="n">
-        <v>8.369999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="G29" t="n">
-        <v>341</v>
+        <v>332.8</v>
       </c>
       <c r="H29" t="n">
-        <v>37.9</v>
+        <v>30.6</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>71.28</v>
+        <v>1.16</v>
       </c>
       <c r="K29" t="n">
-        <v>30.83</v>
+        <v>196.38</v>
       </c>
       <c r="L29" t="n">
-        <v>77.67</v>
+        <v>196.38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:39:05</t>
+          <t>06:38:06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="F30" t="n">
-        <v>7.37</v>
+        <v>7.09</v>
       </c>
       <c r="G30" t="n">
-        <v>332.7</v>
+        <v>325.3</v>
       </c>
       <c r="H30" t="n">
-        <v>34.2</v>
+        <v>41.9</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-65.14</v>
+        <v>-45.27</v>
       </c>
       <c r="K30" t="n">
-        <v>62.12</v>
+        <v>-152.37</v>
       </c>
       <c r="L30" t="n">
-        <v>90.02</v>
+        <v>158.96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:41:04</t>
+          <t>06:40:13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="F31" t="n">
-        <v>7.77</v>
+        <v>6.87</v>
       </c>
       <c r="G31" t="n">
-        <v>343.8</v>
+        <v>333</v>
       </c>
       <c r="H31" t="n">
-        <v>36</v>
+        <v>35.3</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>7.52</v>
+        <v>46.38</v>
       </c>
       <c r="K31" t="n">
-        <v>52.16</v>
+        <v>-133.18</v>
       </c>
       <c r="L31" t="n">
-        <v>52.7</v>
+        <v>141.03</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:45:30</t>
+          <t>06:44:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1384,31 +1384,31 @@
         <v>2.55</v>
       </c>
       <c r="F32" t="n">
-        <v>7.63</v>
+        <v>7.61</v>
       </c>
       <c r="G32" t="n">
-        <v>329.8</v>
+        <v>332.5</v>
       </c>
       <c r="H32" t="n">
-        <v>39.4</v>
+        <v>29.7</v>
       </c>
       <c r="I32" t="n">
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>163.4</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>59.64</v>
+        <v>-63.48</v>
       </c>
       <c r="L32" t="n">
-        <v>173.95</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:46:54</t>
+          <t>06:46:57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.69</v>
+        <v>2.23</v>
       </c>
       <c r="F33" t="n">
-        <v>7.35</v>
+        <v>7.26</v>
       </c>
       <c r="G33" t="n">
-        <v>336.8</v>
+        <v>326.9</v>
       </c>
       <c r="H33" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>80.15000000000001</v>
+        <v>88.98</v>
       </c>
       <c r="K33" t="n">
-        <v>101.83</v>
+        <v>34.99</v>
       </c>
       <c r="L33" t="n">
-        <v>129.59</v>
+        <v>95.61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:48:47</t>
+          <t>06:48:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="F34" t="n">
-        <v>7.05</v>
+        <v>6.99</v>
       </c>
       <c r="G34" t="n">
-        <v>334.4</v>
+        <v>323.4</v>
       </c>
       <c r="H34" t="n">
-        <v>33.2</v>
+        <v>34.1</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>4.55</v>
+        <v>-92.92</v>
       </c>
       <c r="K34" t="n">
-        <v>17.4</v>
+        <v>-76.88</v>
       </c>
       <c r="L34" t="n">
-        <v>17.99</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:53:14</t>
+          <t>06:52:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="F35" t="n">
-        <v>7.68</v>
+        <v>7.05</v>
       </c>
       <c r="G35" t="n">
-        <v>342.2</v>
+        <v>335.5</v>
       </c>
       <c r="H35" t="n">
-        <v>34.6</v>
+        <v>35.2</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>292.95</v>
+        <v>-20.89</v>
       </c>
       <c r="K35" t="n">
-        <v>-110.86</v>
+        <v>130.79</v>
       </c>
       <c r="L35" t="n">
-        <v>313.23</v>
+        <v>132.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:55:18</t>
+          <t>06:55:03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="F36" t="n">
-        <v>7.62</v>
+        <v>7.24</v>
       </c>
       <c r="G36" t="n">
-        <v>325.5</v>
+        <v>328.5</v>
       </c>
       <c r="H36" t="n">
-        <v>42.4</v>
+        <v>35.6</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-80.56</v>
+        <v>158.91</v>
       </c>
       <c r="K36" t="n">
-        <v>84.11</v>
+        <v>-38.61</v>
       </c>
       <c r="L36" t="n">
-        <v>116.47</v>
+        <v>163.53</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:57:57</t>
+          <t>06:57:28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.64</v>
+        <v>2.31</v>
       </c>
       <c r="F37" t="n">
-        <v>6.86</v>
+        <v>6.9</v>
       </c>
       <c r="G37" t="n">
-        <v>325.2</v>
+        <v>333.3</v>
       </c>
       <c r="H37" t="n">
-        <v>44.4</v>
+        <v>26.3</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>405.83</v>
+        <v>-29.93</v>
       </c>
       <c r="K37" t="n">
-        <v>-252.62</v>
+        <v>-248.26</v>
       </c>
       <c r="L37" t="n">
-        <v>478.03</v>
+        <v>250.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:01:41</t>
+          <t>07:03:40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.19</v>
+        <v>2.89</v>
       </c>
       <c r="F38" t="n">
-        <v>6.93</v>
+        <v>7.87</v>
       </c>
       <c r="G38" t="n">
-        <v>326.5</v>
+        <v>332.2</v>
       </c>
       <c r="H38" t="n">
-        <v>35.6</v>
+        <v>33.9</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-255.43</v>
+        <v>268.12</v>
       </c>
       <c r="K38" t="n">
-        <v>31.68</v>
+        <v>15.85</v>
       </c>
       <c r="L38" t="n">
-        <v>257.39</v>
+        <v>268.59</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:02:41</t>
+          <t>07:04:31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="F39" t="n">
-        <v>6.9</v>
+        <v>7.08</v>
       </c>
       <c r="G39" t="n">
-        <v>333.1</v>
+        <v>330.6</v>
       </c>
       <c r="H39" t="n">
-        <v>31.8</v>
+        <v>29.9</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>183.43</v>
+        <v>-213.11</v>
       </c>
       <c r="K39" t="n">
-        <v>-613.46</v>
+        <v>-141.23</v>
       </c>
       <c r="L39" t="n">
-        <v>640.3</v>
+        <v>255.66</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:03:45</t>
+          <t>07:05:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.96</v>
+        <v>2.39</v>
       </c>
       <c r="F40" t="n">
-        <v>7.7</v>
+        <v>7.37</v>
       </c>
       <c r="G40" t="n">
-        <v>341.3</v>
+        <v>339.4</v>
       </c>
       <c r="H40" t="n">
-        <v>32.3</v>
+        <v>37.2</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>295.21</v>
+        <v>404.94</v>
       </c>
       <c r="K40" t="n">
-        <v>-389.71</v>
+        <v>362.45</v>
       </c>
       <c r="L40" t="n">
-        <v>488.9</v>
+        <v>543.46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:09:12</t>
+          <t>07:12:09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="F41" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>336.8</v>
+        <v>330.6</v>
       </c>
       <c r="H41" t="n">
-        <v>36.3</v>
+        <v>29.5</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-139.75</v>
+        <v>-39.02</v>
       </c>
       <c r="K41" t="n">
-        <v>690.14</v>
+        <v>514.52</v>
       </c>
       <c r="L41" t="n">
-        <v>704.15</v>
+        <v>515.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:10:00</t>
+          <t>07:14:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="F42" t="n">
-        <v>7.23</v>
+        <v>7.65</v>
       </c>
       <c r="G42" t="n">
-        <v>330.5</v>
+        <v>335.2</v>
       </c>
       <c r="H42" t="n">
-        <v>38.1</v>
+        <v>35.8</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>51.45</v>
+        <v>417.54</v>
       </c>
       <c r="K42" t="n">
-        <v>261.4</v>
+        <v>-104.6</v>
       </c>
       <c r="L42" t="n">
-        <v>266.42</v>
+        <v>430.44</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:11:27</t>
+          <t>07:15:51</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="F43" t="n">
-        <v>8.01</v>
+        <v>7.06</v>
       </c>
       <c r="G43" t="n">
-        <v>338.7</v>
+        <v>323.6</v>
       </c>
       <c r="H43" t="n">
-        <v>39.7</v>
+        <v>29.1</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-64.62</v>
+        <v>-253.18</v>
       </c>
       <c r="K43" t="n">
-        <v>40.95</v>
+        <v>348.67</v>
       </c>
       <c r="L43" t="n">
-        <v>76.5</v>
+        <v>430.89</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:24:09</t>
+          <t>07:26:28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.19</v>
+        <v>2.23</v>
       </c>
       <c r="F44" t="n">
-        <v>7.2</v>
+        <v>7.44</v>
       </c>
       <c r="G44" t="n">
-        <v>338.4</v>
+        <v>328.1</v>
       </c>
       <c r="H44" t="n">
-        <v>34.7</v>
+        <v>29.8</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-28.29</v>
+        <v>106.32</v>
       </c>
       <c r="K44" t="n">
-        <v>30.73</v>
+        <v>-49.12</v>
       </c>
       <c r="L44" t="n">
-        <v>41.77</v>
+        <v>117.12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:25:47</t>
+          <t>07:28:35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="F45" t="n">
-        <v>7.91</v>
+        <v>7.85</v>
       </c>
       <c r="G45" t="n">
-        <v>321.5</v>
+        <v>334.5</v>
       </c>
       <c r="H45" t="n">
-        <v>39</v>
+        <v>28.9</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>41.24</v>
+        <v>-156.03</v>
       </c>
       <c r="K45" t="n">
-        <v>133.75</v>
+        <v>-40.77</v>
       </c>
       <c r="L45" t="n">
-        <v>139.96</v>
+        <v>161.27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:27:28</t>
+          <t>07:30:51</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="F46" t="n">
-        <v>7.34</v>
+        <v>7.88</v>
       </c>
       <c r="G46" t="n">
-        <v>324.6</v>
+        <v>313.3</v>
       </c>
       <c r="H46" t="n">
         <v>35.4</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>49.26</v>
+        <v>19.8</v>
       </c>
       <c r="K46" t="n">
-        <v>70.28</v>
+        <v>31.73</v>
       </c>
       <c r="L46" t="n">
-        <v>85.81999999999999</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:33:42</t>
+          <t>07:35:24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="F47" t="n">
-        <v>7.56</v>
+        <v>7.4</v>
       </c>
       <c r="G47" t="n">
-        <v>337.6</v>
+        <v>334</v>
       </c>
       <c r="H47" t="n">
-        <v>32.7</v>
+        <v>33.5</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>58.23</v>
+        <v>-211.81</v>
       </c>
       <c r="K47" t="n">
-        <v>-213.71</v>
+        <v>65.45</v>
       </c>
       <c r="L47" t="n">
-        <v>221.5</v>
+        <v>221.69</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:35:35</t>
+          <t>07:37:03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.76</v>
+        <v>2.59</v>
       </c>
       <c r="F48" t="n">
-        <v>8.029999999999999</v>
+        <v>7.46</v>
       </c>
       <c r="G48" t="n">
-        <v>334.6</v>
+        <v>330.5</v>
       </c>
       <c r="H48" t="n">
-        <v>32.2</v>
+        <v>38.1</v>
       </c>
       <c r="I48" t="n">
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-56.16</v>
+        <v>96.72</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.7</v>
+        <v>171.95</v>
       </c>
       <c r="L48" t="n">
-        <v>56.23</v>
+        <v>197.28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:36:35</t>
+          <t>07:39:26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="F49" t="n">
-        <v>7.33</v>
+        <v>7.59</v>
       </c>
       <c r="G49" t="n">
-        <v>336.3</v>
+        <v>320.3</v>
       </c>
       <c r="H49" t="n">
-        <v>38.5</v>
+        <v>30.5</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.48</v>
+        <v>31.49</v>
       </c>
       <c r="K49" t="n">
-        <v>-111.91</v>
+        <v>51.4</v>
       </c>
       <c r="L49" t="n">
-        <v>112.04</v>
+        <v>60.28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:42:46</t>
+          <t>07:43:45</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="F50" t="n">
-        <v>7.75</v>
+        <v>6.82</v>
       </c>
       <c r="G50" t="n">
-        <v>334.2</v>
+        <v>331.3</v>
       </c>
       <c r="H50" t="n">
-        <v>31.2</v>
+        <v>33.1</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-189.95</v>
+        <v>-63.76</v>
       </c>
       <c r="K50" t="n">
-        <v>-63.85</v>
+        <v>152.65</v>
       </c>
       <c r="L50" t="n">
-        <v>200.39</v>
+        <v>165.43</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:44:12</t>
+          <t>07:45:52</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="F51" t="n">
-        <v>7.88</v>
+        <v>7.33</v>
       </c>
       <c r="G51" t="n">
-        <v>340</v>
+        <v>334.9</v>
       </c>
       <c r="H51" t="n">
-        <v>34.6</v>
+        <v>34.3</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>81.95</v>
+        <v>-255.65</v>
       </c>
       <c r="K51" t="n">
-        <v>-69.69</v>
+        <v>-91.88</v>
       </c>
       <c r="L51" t="n">
-        <v>107.58</v>
+        <v>271.66</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:46:00</t>
+          <t>07:47:06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.22</v>
+        <v>2.54</v>
       </c>
       <c r="F52" t="n">
-        <v>7.83</v>
+        <v>7.77</v>
       </c>
       <c r="G52" t="n">
-        <v>335.1</v>
+        <v>317</v>
       </c>
       <c r="H52" t="n">
-        <v>27</v>
+        <v>31.2</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>20.16</v>
+        <v>-242.84</v>
       </c>
       <c r="K52" t="n">
-        <v>107.22</v>
+        <v>-535.61</v>
       </c>
       <c r="L52" t="n">
-        <v>109.1</v>
+        <v>588.09</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:50:07</t>
+          <t>07:52:05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="F53" t="n">
-        <v>7.36</v>
+        <v>7.4</v>
       </c>
       <c r="G53" t="n">
-        <v>321.9</v>
+        <v>324.4</v>
       </c>
       <c r="H53" t="n">
-        <v>38.4</v>
+        <v>37.1</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>98.06999999999999</v>
+        <v>35.51</v>
       </c>
       <c r="K53" t="n">
-        <v>-459.21</v>
+        <v>-25.62</v>
       </c>
       <c r="L53" t="n">
-        <v>469.57</v>
+        <v>43.79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:52:27</t>
+          <t>07:54:33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.66</v>
+        <v>2.33</v>
       </c>
       <c r="F54" t="n">
-        <v>7.74</v>
+        <v>7.24</v>
       </c>
       <c r="G54" t="n">
-        <v>336.5</v>
+        <v>322.9</v>
       </c>
       <c r="H54" t="n">
-        <v>39.5</v>
+        <v>36.5</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-299.15</v>
+        <v>-65.48999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-26.96</v>
+        <v>371.04</v>
       </c>
       <c r="L54" t="n">
-        <v>300.36</v>
+        <v>376.77</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:54:09</t>
+          <t>07:56:42</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.52</v>
+        <v>3.02</v>
       </c>
       <c r="F55" t="n">
-        <v>7.06</v>
+        <v>7.34</v>
       </c>
       <c r="G55" t="n">
-        <v>331.5</v>
+        <v>344.2</v>
       </c>
       <c r="H55" t="n">
-        <v>29.5</v>
+        <v>27.7</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>244.5</v>
+        <v>-373.43</v>
       </c>
       <c r="K55" t="n">
-        <v>-87.64</v>
+        <v>282.93</v>
       </c>
       <c r="L55" t="n">
-        <v>259.74</v>
+        <v>468.51</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:59:08</t>
+          <t>08:00:20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.6</v>
+        <v>1.99</v>
       </c>
       <c r="F56" t="n">
-        <v>6.56</v>
+        <v>7.3</v>
       </c>
       <c r="G56" t="n">
-        <v>322.1</v>
+        <v>336.6</v>
       </c>
       <c r="H56" t="n">
-        <v>33.2</v>
+        <v>34.6</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-567.62</v>
+        <v>119</v>
       </c>
       <c r="K56" t="n">
-        <v>-160.4</v>
+        <v>22.02</v>
       </c>
       <c r="L56" t="n">
-        <v>589.85</v>
+        <v>121.02</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:00:06</t>
+          <t>08:02:08</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="F57" t="n">
-        <v>7.65</v>
+        <v>7.59</v>
       </c>
       <c r="G57" t="n">
-        <v>326.6</v>
+        <v>332.5</v>
       </c>
       <c r="H57" t="n">
-        <v>34.1</v>
+        <v>38</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>275.44</v>
+        <v>-350.66</v>
       </c>
       <c r="K57" t="n">
-        <v>-45.75</v>
+        <v>-123.42</v>
       </c>
       <c r="L57" t="n">
-        <v>279.21</v>
+        <v>371.75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:02:07</t>
+          <t>08:03:17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.29</v>
+        <v>2.53</v>
       </c>
       <c r="F58" t="n">
-        <v>7.13</v>
+        <v>6.99</v>
       </c>
       <c r="G58" t="n">
-        <v>339.7</v>
+        <v>328.8</v>
       </c>
       <c r="H58" t="n">
-        <v>26.2</v>
+        <v>44.5</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>159.17</v>
+        <v>-334.63</v>
       </c>
       <c r="K58" t="n">
-        <v>295.4</v>
+        <v>-355.17</v>
       </c>
       <c r="L58" t="n">
-        <v>335.55</v>
+        <v>487.98</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:15:26</t>
+          <t>08:14:46</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.26</v>
+        <v>2.63</v>
       </c>
       <c r="F59" t="n">
-        <v>6.92</v>
+        <v>6.97</v>
       </c>
       <c r="G59" t="n">
-        <v>327.2</v>
+        <v>334.8</v>
       </c>
       <c r="H59" t="n">
-        <v>26.6</v>
+        <v>39.4</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.16</v>
+        <v>-117.13</v>
       </c>
       <c r="K59" t="n">
-        <v>23.94</v>
+        <v>-47.52</v>
       </c>
       <c r="L59" t="n">
-        <v>25.63</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:17:22</t>
+          <t>08:17:11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="F60" t="n">
-        <v>7.75</v>
+        <v>7.39</v>
       </c>
       <c r="G60" t="n">
-        <v>326.2</v>
+        <v>323.2</v>
       </c>
       <c r="H60" t="n">
-        <v>35.5</v>
+        <v>27.1</v>
       </c>
       <c r="I60" t="n">
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-95.73999999999999</v>
+        <v>104.18</v>
       </c>
       <c r="K60" t="n">
-        <v>-56.18</v>
+        <v>122.47</v>
       </c>
       <c r="L60" t="n">
-        <v>111.01</v>
+        <v>160.79</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:18:45</t>
+          <t>08:18:43</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.39</v>
+        <v>2.14</v>
       </c>
       <c r="F61" t="n">
-        <v>7.64</v>
+        <v>7.74</v>
       </c>
       <c r="G61" t="n">
-        <v>333.5</v>
+        <v>327.6</v>
       </c>
       <c r="H61" t="n">
-        <v>33.5</v>
+        <v>33.8</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>19.84</v>
+        <v>94.16</v>
       </c>
       <c r="K61" t="n">
-        <v>-58.37</v>
+        <v>-43.36</v>
       </c>
       <c r="L61" t="n">
-        <v>61.65</v>
+        <v>103.66</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:23:01</t>
+          <t>08:23:05</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="F62" t="n">
-        <v>7.76</v>
+        <v>6.64</v>
       </c>
       <c r="G62" t="n">
-        <v>333.6</v>
+        <v>331.8</v>
       </c>
       <c r="H62" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-102.47</v>
+        <v>90.63</v>
       </c>
       <c r="K62" t="n">
-        <v>-48.53</v>
+        <v>-80.84</v>
       </c>
       <c r="L62" t="n">
-        <v>113.38</v>
+        <v>121.44</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:24:37</t>
+          <t>08:25:25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.41</v>
+        <v>2.58</v>
       </c>
       <c r="F63" t="n">
-        <v>7.4</v>
+        <v>7.29</v>
       </c>
       <c r="G63" t="n">
-        <v>329.9</v>
+        <v>328.2</v>
       </c>
       <c r="H63" t="n">
-        <v>35.5</v>
+        <v>39.7</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-67.13</v>
+        <v>7.74</v>
       </c>
       <c r="K63" t="n">
-        <v>-115.37</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>133.48</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:25:23</t>
+          <t>08:26:46</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.71</v>
+        <v>2.07</v>
       </c>
       <c r="F64" t="n">
-        <v>7.82</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>328</v>
+        <v>335.3</v>
       </c>
       <c r="H64" t="n">
-        <v>35.2</v>
+        <v>34.6</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-101.05</v>
+        <v>-124.78</v>
       </c>
       <c r="K64" t="n">
-        <v>-78.8</v>
+        <v>21.91</v>
       </c>
       <c r="L64" t="n">
-        <v>128.14</v>
+        <v>126.69</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:29:32</t>
+          <t>08:32:28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2770,31 +2770,31 @@
         <v>2.51</v>
       </c>
       <c r="F65" t="n">
-        <v>7.42</v>
+        <v>6.85</v>
       </c>
       <c r="G65" t="n">
-        <v>318.5</v>
+        <v>318.6</v>
       </c>
       <c r="H65" t="n">
-        <v>39.1</v>
+        <v>31</v>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-341.39</v>
+        <v>-57.18</v>
       </c>
       <c r="K65" t="n">
-        <v>10.29</v>
+        <v>-73.20999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>341.55</v>
+        <v>92.89</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:30:38</t>
+          <t>08:34:21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="F66" t="n">
-        <v>7.49</v>
+        <v>7.11</v>
       </c>
       <c r="G66" t="n">
-        <v>330.8</v>
+        <v>333.6</v>
       </c>
       <c r="H66" t="n">
-        <v>30.2</v>
+        <v>27.5</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-151.37</v>
+        <v>-99.79000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-324.3</v>
+        <v>187.41</v>
       </c>
       <c r="L66" t="n">
-        <v>357.89</v>
+        <v>212.32</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:32:27</t>
+          <t>08:36:22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="F67" t="n">
-        <v>7.81</v>
+        <v>7.38</v>
       </c>
       <c r="G67" t="n">
-        <v>335.9</v>
+        <v>342</v>
       </c>
       <c r="H67" t="n">
-        <v>32.2</v>
+        <v>37.3</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-244.11</v>
+        <v>-131.21</v>
       </c>
       <c r="K67" t="n">
-        <v>-15.42</v>
+        <v>-134.24</v>
       </c>
       <c r="L67" t="n">
-        <v>244.6</v>
+        <v>187.71</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:36:56</t>
+          <t>08:41:11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
       <c r="F68" t="n">
-        <v>6.46</v>
+        <v>7.06</v>
       </c>
       <c r="G68" t="n">
-        <v>322.7</v>
+        <v>315.7</v>
       </c>
       <c r="H68" t="n">
-        <v>42.1</v>
+        <v>32.6</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-243.01</v>
+        <v>-200.37</v>
       </c>
       <c r="K68" t="n">
-        <v>-77.59999999999999</v>
+        <v>101.47</v>
       </c>
       <c r="L68" t="n">
-        <v>255.1</v>
+        <v>224.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:38:37</t>
+          <t>08:41:57</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.72</v>
+        <v>2.57</v>
       </c>
       <c r="F69" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="G69" t="n">
-        <v>325.1</v>
+        <v>344.5</v>
       </c>
       <c r="H69" t="n">
-        <v>35.5</v>
+        <v>38.6</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>679.63</v>
+        <v>239.47</v>
       </c>
       <c r="K69" t="n">
-        <v>140.48</v>
+        <v>400.15</v>
       </c>
       <c r="L69" t="n">
-        <v>694</v>
+        <v>466.34</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:39:40</t>
+          <t>08:44:20</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="F70" t="n">
-        <v>7.38</v>
+        <v>7.44</v>
       </c>
       <c r="G70" t="n">
-        <v>318.2</v>
+        <v>328.3</v>
       </c>
       <c r="H70" t="n">
-        <v>33.4</v>
+        <v>35.2</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-164.77</v>
+        <v>212.64</v>
       </c>
       <c r="K70" t="n">
-        <v>81.56</v>
+        <v>222.65</v>
       </c>
       <c r="L70" t="n">
-        <v>183.85</v>
+        <v>307.88</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:43:04</t>
+          <t>08:48:25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.01</v>
+        <v>2.1</v>
       </c>
       <c r="F71" t="n">
-        <v>7.38</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>328.5</v>
+        <v>331.6</v>
       </c>
       <c r="H71" t="n">
-        <v>34.3</v>
+        <v>39.7</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-117.11</v>
+        <v>-189.62</v>
       </c>
       <c r="K71" t="n">
-        <v>446.9</v>
+        <v>-412.84</v>
       </c>
       <c r="L71" t="n">
-        <v>461.99</v>
+        <v>454.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:45:35</t>
+          <t>08:49:56</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.51</v>
+        <v>2.14</v>
       </c>
       <c r="F72" t="n">
-        <v>6.91</v>
+        <v>7.34</v>
       </c>
       <c r="G72" t="n">
-        <v>328.9</v>
+        <v>312.2</v>
       </c>
       <c r="H72" t="n">
-        <v>33.6</v>
+        <v>32.2</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>309.89</v>
+        <v>-484.87</v>
       </c>
       <c r="K72" t="n">
-        <v>-310.77</v>
+        <v>155.31</v>
       </c>
       <c r="L72" t="n">
-        <v>438.87</v>
+        <v>509.14</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:47:20</t>
+          <t>08:51:15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="F73" t="n">
-        <v>8.15</v>
+        <v>7.88</v>
       </c>
       <c r="G73" t="n">
-        <v>331.2</v>
+        <v>342.5</v>
       </c>
       <c r="H73" t="n">
-        <v>37.7</v>
+        <v>31.7</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-71</v>
+        <v>-511.69</v>
       </c>
       <c r="K73" t="n">
-        <v>-447.43</v>
+        <v>-290.75</v>
       </c>
       <c r="L73" t="n">
-        <v>453.03</v>
+        <v>588.53</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:56:03</t>
+          <t>09:04:22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.56</v>
+        <v>1.93</v>
       </c>
       <c r="F74" t="n">
-        <v>6.79</v>
+        <v>7.35</v>
       </c>
       <c r="G74" t="n">
-        <v>334.7</v>
+        <v>331.5</v>
       </c>
       <c r="H74" t="n">
-        <v>25.1</v>
+        <v>36.2</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>20</v>
+        <v>27.64</v>
       </c>
       <c r="K74" t="n">
-        <v>132.32</v>
+        <v>-51.48</v>
       </c>
       <c r="L74" t="n">
-        <v>133.82</v>
+        <v>58.43</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:57:47</t>
+          <t>09:06:04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="F75" t="n">
-        <v>6.92</v>
+        <v>7.59</v>
       </c>
       <c r="G75" t="n">
-        <v>327</v>
+        <v>330.5</v>
       </c>
       <c r="H75" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>49.46</v>
+        <v>-63.64</v>
       </c>
       <c r="K75" t="n">
-        <v>-52.05</v>
+        <v>0.6</v>
       </c>
       <c r="L75" t="n">
-        <v>71.8</v>
+        <v>63.65</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:00:02</t>
+          <t>09:07:12</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.41</v>
+        <v>2.85</v>
       </c>
       <c r="F76" t="n">
-        <v>8.07</v>
+        <v>7.4</v>
       </c>
       <c r="G76" t="n">
-        <v>352.7</v>
+        <v>337.9</v>
       </c>
       <c r="H76" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="I76" t="n">
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>19.22</v>
+        <v>26.8</v>
       </c>
       <c r="K76" t="n">
-        <v>65.77</v>
+        <v>-228.05</v>
       </c>
       <c r="L76" t="n">
-        <v>68.52</v>
+        <v>229.62</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:05:09</t>
+          <t>09:11:31</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.62</v>
+        <v>1.78</v>
       </c>
       <c r="F77" t="n">
-        <v>7.01</v>
+        <v>7.77</v>
       </c>
       <c r="G77" t="n">
-        <v>331.4</v>
+        <v>324.3</v>
       </c>
       <c r="H77" t="n">
-        <v>32.6</v>
+        <v>27.7</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>64.03</v>
+        <v>72.14</v>
       </c>
       <c r="K77" t="n">
-        <v>117.73</v>
+        <v>44.76</v>
       </c>
       <c r="L77" t="n">
-        <v>134.01</v>
+        <v>84.89</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:06:52</t>
+          <t>09:14:02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="F78" t="n">
-        <v>7.14</v>
+        <v>7.42</v>
       </c>
       <c r="G78" t="n">
-        <v>336.8</v>
+        <v>330</v>
       </c>
       <c r="H78" t="n">
-        <v>34.3</v>
+        <v>36.6</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.49</v>
+        <v>-92.37</v>
       </c>
       <c r="K78" t="n">
-        <v>12.08</v>
+        <v>134.56</v>
       </c>
       <c r="L78" t="n">
-        <v>13.72</v>
+        <v>163.21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:08:35</t>
+          <t>09:14:57</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.09</v>
+        <v>2.64</v>
       </c>
       <c r="F79" t="n">
-        <v>7.6</v>
+        <v>7.13</v>
       </c>
       <c r="G79" t="n">
-        <v>324.1</v>
+        <v>327.2</v>
       </c>
       <c r="H79" t="n">
-        <v>39.9</v>
+        <v>29.1</v>
       </c>
       <c r="I79" t="n">
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-107.49</v>
+        <v>153.26</v>
       </c>
       <c r="K79" t="n">
-        <v>-52.04</v>
+        <v>-125.75</v>
       </c>
       <c r="L79" t="n">
-        <v>119.43</v>
+        <v>198.25</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:13:45</t>
+          <t>09:18:53</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.75</v>
+        <v>3.29</v>
       </c>
       <c r="F80" t="n">
-        <v>7.4</v>
+        <v>7.42</v>
       </c>
       <c r="G80" t="n">
-        <v>332.6</v>
+        <v>330.9</v>
       </c>
       <c r="H80" t="n">
-        <v>30.7</v>
+        <v>35.7</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-185.52</v>
+        <v>223.37</v>
       </c>
       <c r="K80" t="n">
-        <v>196.12</v>
+        <v>-170.14</v>
       </c>
       <c r="L80" t="n">
-        <v>269.96</v>
+        <v>280.79</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:14:20</t>
+          <t>09:21:04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="F81" t="n">
-        <v>7.35</v>
+        <v>7.73</v>
       </c>
       <c r="G81" t="n">
-        <v>319.9</v>
+        <v>314.8</v>
       </c>
       <c r="H81" t="n">
-        <v>37.7</v>
+        <v>39.3</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-305.96</v>
+        <v>-10.16</v>
       </c>
       <c r="K81" t="n">
-        <v>-114.67</v>
+        <v>-186.69</v>
       </c>
       <c r="L81" t="n">
-        <v>326.75</v>
+        <v>186.97</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:15:52</t>
+          <t>09:22:49</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="F82" t="n">
-        <v>6.61</v>
+        <v>7.32</v>
       </c>
       <c r="G82" t="n">
-        <v>330</v>
+        <v>328.5</v>
       </c>
       <c r="H82" t="n">
-        <v>37.5</v>
+        <v>38.2</v>
       </c>
       <c r="I82" t="n">
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>221.09</v>
+        <v>-199.16</v>
       </c>
       <c r="K82" t="n">
-        <v>90.52</v>
+        <v>187.99</v>
       </c>
       <c r="L82" t="n">
-        <v>238.9</v>
+        <v>273.87</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:20:40</t>
+          <t>09:27:12</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.19</v>
+        <v>2.61</v>
       </c>
       <c r="F83" t="n">
-        <v>8.09</v>
+        <v>6.93</v>
       </c>
       <c r="G83" t="n">
-        <v>338.8</v>
+        <v>336.7</v>
       </c>
       <c r="H83" t="n">
-        <v>34.8</v>
+        <v>29.1</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>104.51</v>
+        <v>130.84</v>
       </c>
       <c r="K83" t="n">
-        <v>-270.41</v>
+        <v>272.1</v>
       </c>
       <c r="L83" t="n">
-        <v>289.9</v>
+        <v>301.93</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:22:06</t>
+          <t>09:28:40</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="F84" t="n">
-        <v>7.13</v>
+        <v>7.87</v>
       </c>
       <c r="G84" t="n">
-        <v>324.1</v>
+        <v>334.3</v>
       </c>
       <c r="H84" t="n">
-        <v>28.3</v>
+        <v>42.3</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-99</v>
+        <v>-262.63</v>
       </c>
       <c r="K84" t="n">
-        <v>-429.04</v>
+        <v>175.78</v>
       </c>
       <c r="L84" t="n">
-        <v>440.31</v>
+        <v>316.02</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:23:10</t>
+          <t>09:29:53</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="F85" t="n">
-        <v>7.13</v>
+        <v>7.8</v>
       </c>
       <c r="G85" t="n">
-        <v>321.4</v>
+        <v>332.3</v>
       </c>
       <c r="H85" t="n">
-        <v>41.5</v>
+        <v>35.2</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>114.26</v>
+        <v>-95.33</v>
       </c>
       <c r="K85" t="n">
-        <v>284.6</v>
+        <v>-308.88</v>
       </c>
       <c r="L85" t="n">
-        <v>306.68</v>
+        <v>323.26</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:27:52</t>
+          <t>09:34:23</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.64</v>
+        <v>3.79</v>
       </c>
       <c r="F86" t="n">
-        <v>7.32</v>
+        <v>7.53</v>
       </c>
       <c r="G86" t="n">
-        <v>334.5</v>
+        <v>333.3</v>
       </c>
       <c r="H86" t="n">
-        <v>32.9</v>
+        <v>33.9</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>113.05</v>
+        <v>556.8099999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>-265.41</v>
+        <v>-315.98</v>
       </c>
       <c r="L86" t="n">
-        <v>288.49</v>
+        <v>640.21</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:30:25</t>
+          <t>09:35:21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.85</v>
+        <v>2.52</v>
       </c>
       <c r="F87" t="n">
-        <v>7.75</v>
+        <v>7.56</v>
       </c>
       <c r="G87" t="n">
-        <v>339.6</v>
+        <v>331.7</v>
       </c>
       <c r="H87" t="n">
-        <v>32.4</v>
+        <v>37.5</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>359.42</v>
+        <v>-92.68000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-274.81</v>
+        <v>-434.84</v>
       </c>
       <c r="L87" t="n">
-        <v>452.44</v>
+        <v>444.6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:31:59</t>
+          <t>09:36:32</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="F88" t="n">
-        <v>7.75</v>
+        <v>7.48</v>
       </c>
       <c r="G88" t="n">
-        <v>330.5</v>
+        <v>330</v>
       </c>
       <c r="H88" t="n">
-        <v>34.4</v>
+        <v>25.8</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>130.38</v>
+        <v>-419.13</v>
       </c>
       <c r="K88" t="n">
-        <v>74.95</v>
+        <v>67.7</v>
       </c>
       <c r="L88" t="n">
-        <v>150.39</v>
+        <v>424.56</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-22.xlsx
+++ b/output/2025-04-22.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>60.17</v>
+        <v>38.09</v>
       </c>
       <c r="K14" t="n">
-        <v>-145.07</v>
+        <v>-91.84</v>
       </c>
       <c r="L14" t="n">
-        <v>157.05</v>
+        <v>99.42</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>28</v>
+        <v>21.14</v>
       </c>
       <c r="K15" t="n">
-        <v>-159.07</v>
+        <v>-120.1</v>
       </c>
       <c r="L15" t="n">
-        <v>161.52</v>
+        <v>121.94</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>36.3</v>
+        <v>51.09</v>
       </c>
       <c r="K16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L16" t="n">
-        <v>36.3</v>
+        <v>51.09</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>42.92</v>
+        <v>38.77</v>
       </c>
       <c r="K17" t="n">
-        <v>122.93</v>
+        <v>111.05</v>
       </c>
       <c r="L17" t="n">
-        <v>130.21</v>
+        <v>117.62</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>171.97</v>
+        <v>139.04</v>
       </c>
       <c r="K18" t="n">
-        <v>178.57</v>
+        <v>144.37</v>
       </c>
       <c r="L18" t="n">
-        <v>247.92</v>
+        <v>200.43</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-64.97</v>
+        <v>-72.2</v>
       </c>
       <c r="K19" t="n">
-        <v>23.53</v>
+        <v>26.14</v>
       </c>
       <c r="L19" t="n">
-        <v>69.09999999999999</v>
+        <v>76.79000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>184.59</v>
+        <v>187.8</v>
       </c>
       <c r="K20" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="L20" t="n">
-        <v>184.93</v>
+        <v>188.15</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>29.89</v>
+        <v>27.34</v>
       </c>
       <c r="K21" t="n">
-        <v>319.29</v>
+        <v>291.99</v>
       </c>
       <c r="L21" t="n">
-        <v>320.69</v>
+        <v>293.27</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-77.93000000000001</v>
+        <v>-92.70999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>119.61</v>
+        <v>142.3</v>
       </c>
       <c r="L22" t="n">
-        <v>142.76</v>
+        <v>169.84</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>272.28</v>
+        <v>290.93</v>
       </c>
       <c r="K23" t="n">
-        <v>202.34</v>
+        <v>216.2</v>
       </c>
       <c r="L23" t="n">
-        <v>339.23</v>
+        <v>362.47</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-289.91</v>
+        <v>-306.16</v>
       </c>
       <c r="K24" t="n">
-        <v>18.2</v>
+        <v>19.22</v>
       </c>
       <c r="L24" t="n">
-        <v>290.48</v>
+        <v>306.76</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-313.74</v>
+        <v>-279.74</v>
       </c>
       <c r="K25" t="n">
-        <v>278.19</v>
+        <v>248.04</v>
       </c>
       <c r="L25" t="n">
-        <v>419.31</v>
+        <v>373.87</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-619.92</v>
+        <v>-609.71</v>
       </c>
       <c r="K26" t="n">
-        <v>-272.76</v>
+        <v>-268.27</v>
       </c>
       <c r="L26" t="n">
-        <v>677.27</v>
+        <v>666.12</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>393</v>
+        <v>435.14</v>
       </c>
       <c r="K27" t="n">
-        <v>-213.44</v>
+        <v>-236.33</v>
       </c>
       <c r="L27" t="n">
-        <v>447.22</v>
+        <v>495.17</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-158.9</v>
+        <v>-297.89</v>
       </c>
       <c r="K28" t="n">
-        <v>-9.460000000000001</v>
+        <v>-17.74</v>
       </c>
       <c r="L28" t="n">
-        <v>159.18</v>
+        <v>298.41</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>1.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>196.38</v>
+        <v>159.3</v>
       </c>
       <c r="L29" t="n">
-        <v>196.38</v>
+        <v>159.31</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-45.27</v>
+        <v>-32.19</v>
       </c>
       <c r="K30" t="n">
-        <v>-152.37</v>
+        <v>-108.34</v>
       </c>
       <c r="L30" t="n">
-        <v>158.96</v>
+        <v>113.02</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>46.38</v>
+        <v>33.67</v>
       </c>
       <c r="K31" t="n">
-        <v>-133.18</v>
+        <v>-96.68000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>141.03</v>
+        <v>102.37</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>70.54000000000001</v>
+        <v>80.42</v>
       </c>
       <c r="K32" t="n">
-        <v>-63.48</v>
+        <v>-72.38</v>
       </c>
       <c r="L32" t="n">
-        <v>94.90000000000001</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>88.98</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>34.99</v>
+        <v>33.27</v>
       </c>
       <c r="L33" t="n">
-        <v>95.61</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-92.92</v>
+        <v>-90.95999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-76.88</v>
+        <v>-75.26000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>120.6</v>
+        <v>118.06</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-20.89</v>
+        <v>-26.19</v>
       </c>
       <c r="K35" t="n">
-        <v>130.79</v>
+        <v>163.93</v>
       </c>
       <c r="L35" t="n">
-        <v>132.45</v>
+        <v>166.01</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>158.91</v>
+        <v>146.06</v>
       </c>
       <c r="K36" t="n">
-        <v>-38.61</v>
+        <v>-35.49</v>
       </c>
       <c r="L36" t="n">
-        <v>163.53</v>
+        <v>150.31</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-29.93</v>
+        <v>-29.78</v>
       </c>
       <c r="K37" t="n">
-        <v>-248.26</v>
+        <v>-247.03</v>
       </c>
       <c r="L37" t="n">
-        <v>250.06</v>
+        <v>248.82</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>268.12</v>
+        <v>365.13</v>
       </c>
       <c r="K38" t="n">
-        <v>15.85</v>
+        <v>21.58</v>
       </c>
       <c r="L38" t="n">
-        <v>268.59</v>
+        <v>365.77</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-213.11</v>
+        <v>-246.4</v>
       </c>
       <c r="K39" t="n">
-        <v>-141.23</v>
+        <v>-163.3</v>
       </c>
       <c r="L39" t="n">
-        <v>255.66</v>
+        <v>295.6</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>404.94</v>
+        <v>359.13</v>
       </c>
       <c r="K40" t="n">
-        <v>362.45</v>
+        <v>321.44</v>
       </c>
       <c r="L40" t="n">
-        <v>543.46</v>
+        <v>481.97</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-39.02</v>
+        <v>-43.58</v>
       </c>
       <c r="K41" t="n">
-        <v>514.52</v>
+        <v>574.63</v>
       </c>
       <c r="L41" t="n">
-        <v>515.99</v>
+        <v>576.28</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>417.54</v>
+        <v>456.12</v>
       </c>
       <c r="K42" t="n">
-        <v>-104.6</v>
+        <v>-114.26</v>
       </c>
       <c r="L42" t="n">
-        <v>430.44</v>
+        <v>470.22</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-253.18</v>
+        <v>-285.53</v>
       </c>
       <c r="K43" t="n">
-        <v>348.67</v>
+        <v>393.22</v>
       </c>
       <c r="L43" t="n">
-        <v>430.89</v>
+        <v>485.95</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>106.32</v>
+        <v>89.8</v>
       </c>
       <c r="K44" t="n">
-        <v>-49.12</v>
+        <v>-41.49</v>
       </c>
       <c r="L44" t="n">
-        <v>117.12</v>
+        <v>98.92</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-156.03</v>
+        <v>-125.46</v>
       </c>
       <c r="K45" t="n">
-        <v>-40.77</v>
+        <v>-32.78</v>
       </c>
       <c r="L45" t="n">
-        <v>161.27</v>
+        <v>129.68</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>19.8</v>
+        <v>29.18</v>
       </c>
       <c r="K46" t="n">
-        <v>31.73</v>
+        <v>46.76</v>
       </c>
       <c r="L46" t="n">
-        <v>37.4</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-211.81</v>
+        <v>-186.98</v>
       </c>
       <c r="K47" t="n">
-        <v>65.45</v>
+        <v>57.78</v>
       </c>
       <c r="L47" t="n">
-        <v>221.69</v>
+        <v>195.71</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>96.72</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>171.95</v>
+        <v>146.1</v>
       </c>
       <c r="L48" t="n">
-        <v>197.28</v>
+        <v>167.63</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>31.49</v>
+        <v>42.14</v>
       </c>
       <c r="K49" t="n">
-        <v>51.4</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>60.28</v>
+        <v>80.68000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-63.76</v>
+        <v>-56.71</v>
       </c>
       <c r="K50" t="n">
-        <v>152.65</v>
+        <v>135.77</v>
       </c>
       <c r="L50" t="n">
-        <v>165.43</v>
+        <v>147.14</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-255.65</v>
+        <v>-241.68</v>
       </c>
       <c r="K51" t="n">
-        <v>-91.88</v>
+        <v>-86.86</v>
       </c>
       <c r="L51" t="n">
-        <v>271.66</v>
+        <v>256.82</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-242.84</v>
+        <v>-209.34</v>
       </c>
       <c r="K52" t="n">
-        <v>-535.61</v>
+        <v>-461.72</v>
       </c>
       <c r="L52" t="n">
-        <v>588.09</v>
+        <v>506.96</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>35.51</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-25.62</v>
+        <v>-63.5</v>
       </c>
       <c r="L53" t="n">
-        <v>43.79</v>
+        <v>108.53</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-65.48999999999999</v>
+        <v>-58.63</v>
       </c>
       <c r="K54" t="n">
-        <v>371.04</v>
+        <v>332.15</v>
       </c>
       <c r="L54" t="n">
-        <v>376.77</v>
+        <v>337.29</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-373.43</v>
+        <v>-360.88</v>
       </c>
       <c r="K55" t="n">
-        <v>282.93</v>
+        <v>273.43</v>
       </c>
       <c r="L55" t="n">
-        <v>468.51</v>
+        <v>452.76</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>119</v>
+        <v>249.23</v>
       </c>
       <c r="K56" t="n">
-        <v>22.02</v>
+        <v>46.12</v>
       </c>
       <c r="L56" t="n">
-        <v>121.02</v>
+        <v>253.46</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-350.66</v>
+        <v>-394.04</v>
       </c>
       <c r="K57" t="n">
-        <v>-123.42</v>
+        <v>-138.69</v>
       </c>
       <c r="L57" t="n">
-        <v>371.75</v>
+        <v>417.74</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-334.63</v>
+        <v>-388.3</v>
       </c>
       <c r="K58" t="n">
-        <v>-355.17</v>
+        <v>-412.13</v>
       </c>
       <c r="L58" t="n">
-        <v>487.98</v>
+        <v>566.24</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-117.13</v>
+        <v>-111.96</v>
       </c>
       <c r="K59" t="n">
-        <v>-47.52</v>
+        <v>-45.43</v>
       </c>
       <c r="L59" t="n">
-        <v>126.4</v>
+        <v>120.83</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>104.18</v>
+        <v>85.69</v>
       </c>
       <c r="K60" t="n">
-        <v>122.47</v>
+        <v>100.74</v>
       </c>
       <c r="L60" t="n">
-        <v>160.79</v>
+        <v>132.25</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>94.16</v>
+        <v>64.77</v>
       </c>
       <c r="K61" t="n">
-        <v>-43.36</v>
+        <v>-29.83</v>
       </c>
       <c r="L61" t="n">
-        <v>103.66</v>
+        <v>71.31</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>90.63</v>
+        <v>82.7</v>
       </c>
       <c r="K62" t="n">
-        <v>-80.84</v>
+        <v>-73.76000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>121.44</v>
+        <v>110.81</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>7.74</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>96.29000000000001</v>
+        <v>105.28</v>
       </c>
       <c r="L63" t="n">
-        <v>96.59999999999999</v>
+        <v>105.62</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-124.78</v>
+        <v>-108.95</v>
       </c>
       <c r="K64" t="n">
-        <v>21.91</v>
+        <v>19.13</v>
       </c>
       <c r="L64" t="n">
-        <v>126.69</v>
+        <v>110.62</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-57.18</v>
+        <v>-81.95999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-73.20999999999999</v>
+        <v>-104.93</v>
       </c>
       <c r="L65" t="n">
-        <v>92.89</v>
+        <v>133.14</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-99.79000000000001</v>
+        <v>-104.85</v>
       </c>
       <c r="K66" t="n">
-        <v>187.41</v>
+        <v>196.91</v>
       </c>
       <c r="L66" t="n">
-        <v>212.32</v>
+        <v>223.08</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-131.21</v>
+        <v>-133.04</v>
       </c>
       <c r="K67" t="n">
-        <v>-134.24</v>
+        <v>-136.12</v>
       </c>
       <c r="L67" t="n">
-        <v>187.71</v>
+        <v>190.33</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-200.37</v>
+        <v>-280.09</v>
       </c>
       <c r="K68" t="n">
-        <v>101.47</v>
+        <v>141.84</v>
       </c>
       <c r="L68" t="n">
-        <v>224.6</v>
+        <v>313.96</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>239.47</v>
+        <v>223.55</v>
       </c>
       <c r="K69" t="n">
-        <v>400.15</v>
+        <v>373.55</v>
       </c>
       <c r="L69" t="n">
-        <v>466.34</v>
+        <v>435.33</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>212.64</v>
+        <v>208.97</v>
       </c>
       <c r="K70" t="n">
-        <v>222.65</v>
+        <v>218.81</v>
       </c>
       <c r="L70" t="n">
-        <v>307.88</v>
+        <v>302.57</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-189.62</v>
+        <v>-205.02</v>
       </c>
       <c r="K71" t="n">
-        <v>-412.84</v>
+        <v>-446.37</v>
       </c>
       <c r="L71" t="n">
-        <v>454.3</v>
+        <v>491.21</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-484.87</v>
+        <v>-447.27</v>
       </c>
       <c r="K72" t="n">
-        <v>155.31</v>
+        <v>143.27</v>
       </c>
       <c r="L72" t="n">
-        <v>509.14</v>
+        <v>469.65</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-511.69</v>
+        <v>-591.9</v>
       </c>
       <c r="K73" t="n">
-        <v>-290.75</v>
+        <v>-336.32</v>
       </c>
       <c r="L73" t="n">
-        <v>588.53</v>
+        <v>680.78</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>27.64</v>
+        <v>30.37</v>
       </c>
       <c r="K74" t="n">
-        <v>-51.48</v>
+        <v>-56.59</v>
       </c>
       <c r="L74" t="n">
-        <v>58.43</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-63.64</v>
+        <v>-79.64</v>
       </c>
       <c r="K75" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="L75" t="n">
-        <v>63.65</v>
+        <v>79.64</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>26.8</v>
+        <v>22.53</v>
       </c>
       <c r="K76" t="n">
-        <v>-228.05</v>
+        <v>-191.67</v>
       </c>
       <c r="L76" t="n">
-        <v>229.62</v>
+        <v>192.99</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>72.14</v>
+        <v>66.72</v>
       </c>
       <c r="K77" t="n">
-        <v>44.76</v>
+        <v>41.39</v>
       </c>
       <c r="L77" t="n">
-        <v>84.89</v>
+        <v>78.52</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-92.37</v>
+        <v>-85.84999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>134.56</v>
+        <v>125.06</v>
       </c>
       <c r="L78" t="n">
-        <v>163.21</v>
+        <v>151.69</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>153.26</v>
+        <v>148.28</v>
       </c>
       <c r="K79" t="n">
-        <v>-125.75</v>
+        <v>-121.66</v>
       </c>
       <c r="L79" t="n">
-        <v>198.25</v>
+        <v>191.8</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>223.37</v>
+        <v>254.27</v>
       </c>
       <c r="K80" t="n">
-        <v>-170.14</v>
+        <v>-193.68</v>
       </c>
       <c r="L80" t="n">
-        <v>280.79</v>
+        <v>319.64</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.16</v>
+        <v>-9.59</v>
       </c>
       <c r="K81" t="n">
-        <v>-186.69</v>
+        <v>-176.36</v>
       </c>
       <c r="L81" t="n">
-        <v>186.97</v>
+        <v>176.62</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-199.16</v>
+        <v>-201.06</v>
       </c>
       <c r="K82" t="n">
-        <v>187.99</v>
+        <v>189.78</v>
       </c>
       <c r="L82" t="n">
-        <v>273.87</v>
+        <v>276.48</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>130.84</v>
+        <v>158.91</v>
       </c>
       <c r="K83" t="n">
-        <v>272.1</v>
+        <v>330.46</v>
       </c>
       <c r="L83" t="n">
-        <v>301.93</v>
+        <v>366.68</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-262.63</v>
+        <v>-241.42</v>
       </c>
       <c r="K84" t="n">
-        <v>175.78</v>
+        <v>161.59</v>
       </c>
       <c r="L84" t="n">
-        <v>316.02</v>
+        <v>290.51</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-95.33</v>
+        <v>-94.86</v>
       </c>
       <c r="K85" t="n">
-        <v>-308.88</v>
+        <v>-307.38</v>
       </c>
       <c r="L85" t="n">
-        <v>323.26</v>
+        <v>321.68</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>556.8099999999999</v>
+        <v>658.51</v>
       </c>
       <c r="K86" t="n">
-        <v>-315.98</v>
+        <v>-373.69</v>
       </c>
       <c r="L86" t="n">
-        <v>640.21</v>
+        <v>757.15</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-92.68000000000001</v>
+        <v>-104.28</v>
       </c>
       <c r="K87" t="n">
-        <v>-434.84</v>
+        <v>-489.25</v>
       </c>
       <c r="L87" t="n">
-        <v>444.6</v>
+        <v>500.24</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-419.13</v>
+        <v>-520</v>
       </c>
       <c r="K88" t="n">
-        <v>67.7</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>424.56</v>
+        <v>526.74</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-22.xlsx
+++ b/output/2025-04-22.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>38.09</v>
+        <v>38.37</v>
       </c>
       <c r="K14" t="n">
-        <v>-91.84</v>
+        <v>-92.51000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>99.42</v>
+        <v>100.15</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>21.14</v>
+        <v>15.8</v>
       </c>
       <c r="K15" t="n">
-        <v>-120.1</v>
+        <v>-89.78</v>
       </c>
       <c r="L15" t="n">
-        <v>121.94</v>
+        <v>91.16</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>51.09</v>
+        <v>38.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>51.09</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>38.77</v>
+        <v>29.18</v>
       </c>
       <c r="K17" t="n">
-        <v>111.05</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>117.62</v>
+        <v>88.52</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>139.04</v>
+        <v>107.24</v>
       </c>
       <c r="K18" t="n">
-        <v>144.37</v>
+        <v>111.36</v>
       </c>
       <c r="L18" t="n">
-        <v>200.43</v>
+        <v>154.6</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-72.2</v>
+        <v>-64.75</v>
       </c>
       <c r="K19" t="n">
-        <v>26.14</v>
+        <v>23.44</v>
       </c>
       <c r="L19" t="n">
-        <v>76.79000000000001</v>
+        <v>68.86</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>187.8</v>
+        <v>127.12</v>
       </c>
       <c r="K20" t="n">
-        <v>11.4</v>
+        <v>7.71</v>
       </c>
       <c r="L20" t="n">
-        <v>188.15</v>
+        <v>127.35</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>27.34</v>
+        <v>17.62</v>
       </c>
       <c r="K21" t="n">
-        <v>291.99</v>
+        <v>188.16</v>
       </c>
       <c r="L21" t="n">
-        <v>293.27</v>
+        <v>188.98</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-92.70999999999999</v>
+        <v>-62.69</v>
       </c>
       <c r="K22" t="n">
-        <v>142.3</v>
+        <v>96.22</v>
       </c>
       <c r="L22" t="n">
-        <v>169.84</v>
+        <v>114.84</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>290.93</v>
+        <v>151.49</v>
       </c>
       <c r="K23" t="n">
-        <v>216.2</v>
+        <v>112.58</v>
       </c>
       <c r="L23" t="n">
-        <v>362.47</v>
+        <v>188.74</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-306.16</v>
+        <v>-170.68</v>
       </c>
       <c r="K24" t="n">
-        <v>19.22</v>
+        <v>10.71</v>
       </c>
       <c r="L24" t="n">
-        <v>306.76</v>
+        <v>171.02</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-279.74</v>
+        <v>-168.53</v>
       </c>
       <c r="K25" t="n">
-        <v>248.04</v>
+        <v>149.43</v>
       </c>
       <c r="L25" t="n">
-        <v>373.87</v>
+        <v>225.23</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-609.71</v>
+        <v>-328.49</v>
       </c>
       <c r="K26" t="n">
-        <v>-268.27</v>
+        <v>-144.53</v>
       </c>
       <c r="L26" t="n">
-        <v>666.12</v>
+        <v>358.88</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>435.14</v>
+        <v>234.44</v>
       </c>
       <c r="K27" t="n">
-        <v>-236.33</v>
+        <v>-127.32</v>
       </c>
       <c r="L27" t="n">
-        <v>495.17</v>
+        <v>266.78</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-297.89</v>
+        <v>-160.93</v>
       </c>
       <c r="K28" t="n">
-        <v>-17.74</v>
+        <v>-9.58</v>
       </c>
       <c r="L28" t="n">
-        <v>298.41</v>
+        <v>161.21</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="K29" t="n">
-        <v>159.3</v>
+        <v>133.58</v>
       </c>
       <c r="L29" t="n">
-        <v>159.31</v>
+        <v>133.58</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-32.19</v>
+        <v>-28.24</v>
       </c>
       <c r="K30" t="n">
-        <v>-108.34</v>
+        <v>-95.05</v>
       </c>
       <c r="L30" t="n">
-        <v>113.02</v>
+        <v>99.16</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>33.67</v>
+        <v>30.26</v>
       </c>
       <c r="K31" t="n">
-        <v>-96.68000000000001</v>
+        <v>-86.90000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>102.37</v>
+        <v>92.02</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>80.42</v>
+        <v>62.96</v>
       </c>
       <c r="K32" t="n">
-        <v>-72.38</v>
+        <v>-56.66</v>
       </c>
       <c r="L32" t="n">
-        <v>108.2</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>84.59999999999999</v>
+        <v>73.88</v>
       </c>
       <c r="K33" t="n">
-        <v>33.27</v>
+        <v>29.05</v>
       </c>
       <c r="L33" t="n">
-        <v>90.90000000000001</v>
+        <v>79.38</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-90.95999999999999</v>
+        <v>-65.16</v>
       </c>
       <c r="K34" t="n">
-        <v>-75.26000000000001</v>
+        <v>-53.91</v>
       </c>
       <c r="L34" t="n">
-        <v>118.06</v>
+        <v>84.56999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-26.19</v>
+        <v>-18.26</v>
       </c>
       <c r="K35" t="n">
-        <v>163.93</v>
+        <v>114.32</v>
       </c>
       <c r="L35" t="n">
-        <v>166.01</v>
+        <v>115.77</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>146.06</v>
+        <v>115.91</v>
       </c>
       <c r="K36" t="n">
-        <v>-35.49</v>
+        <v>-28.16</v>
       </c>
       <c r="L36" t="n">
-        <v>150.31</v>
+        <v>119.29</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-29.78</v>
+        <v>-19.08</v>
       </c>
       <c r="K37" t="n">
-        <v>-247.03</v>
+        <v>-158.25</v>
       </c>
       <c r="L37" t="n">
-        <v>248.82</v>
+        <v>159.4</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>365.13</v>
+        <v>193.66</v>
       </c>
       <c r="K38" t="n">
-        <v>21.58</v>
+        <v>11.45</v>
       </c>
       <c r="L38" t="n">
-        <v>365.77</v>
+        <v>193.99</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-246.4</v>
+        <v>-147.65</v>
       </c>
       <c r="K39" t="n">
-        <v>-163.3</v>
+        <v>-97.84999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>295.6</v>
+        <v>177.13</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>359.13</v>
+        <v>219.13</v>
       </c>
       <c r="K40" t="n">
-        <v>321.44</v>
+        <v>196.13</v>
       </c>
       <c r="L40" t="n">
-        <v>481.97</v>
+        <v>294.08</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-43.58</v>
+        <v>-22.95</v>
       </c>
       <c r="K41" t="n">
-        <v>574.63</v>
+        <v>302.61</v>
       </c>
       <c r="L41" t="n">
-        <v>576.28</v>
+        <v>303.48</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>456.12</v>
+        <v>258.23</v>
       </c>
       <c r="K42" t="n">
-        <v>-114.26</v>
+        <v>-64.69</v>
       </c>
       <c r="L42" t="n">
-        <v>470.22</v>
+        <v>266.21</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-285.53</v>
+        <v>-156.26</v>
       </c>
       <c r="K43" t="n">
-        <v>393.22</v>
+        <v>215.2</v>
       </c>
       <c r="L43" t="n">
-        <v>485.95</v>
+        <v>265.95</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>89.8</v>
+        <v>73.58</v>
       </c>
       <c r="K44" t="n">
-        <v>-41.49</v>
+        <v>-33.99</v>
       </c>
       <c r="L44" t="n">
-        <v>98.92</v>
+        <v>81.05</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-125.46</v>
+        <v>-105.82</v>
       </c>
       <c r="K45" t="n">
-        <v>-32.78</v>
+        <v>-27.65</v>
       </c>
       <c r="L45" t="n">
-        <v>129.68</v>
+        <v>109.37</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>29.18</v>
+        <v>25.73</v>
       </c>
       <c r="K46" t="n">
-        <v>46.76</v>
+        <v>41.23</v>
       </c>
       <c r="L46" t="n">
-        <v>55.12</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-186.98</v>
+        <v>-135.57</v>
       </c>
       <c r="K47" t="n">
-        <v>57.78</v>
+        <v>41.89</v>
       </c>
       <c r="L47" t="n">
-        <v>195.71</v>
+        <v>141.9</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>82.18000000000001</v>
+        <v>66.27</v>
       </c>
       <c r="K48" t="n">
-        <v>146.1</v>
+        <v>117.82</v>
       </c>
       <c r="L48" t="n">
-        <v>167.63</v>
+        <v>135.18</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>42.14</v>
+        <v>32.58</v>
       </c>
       <c r="K49" t="n">
-        <v>68.79000000000001</v>
+        <v>53.19</v>
       </c>
       <c r="L49" t="n">
-        <v>80.68000000000001</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-56.71</v>
+        <v>-43.86</v>
       </c>
       <c r="K50" t="n">
-        <v>135.77</v>
+        <v>105</v>
       </c>
       <c r="L50" t="n">
-        <v>147.14</v>
+        <v>113.8</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-241.68</v>
+        <v>-162.08</v>
       </c>
       <c r="K51" t="n">
-        <v>-86.86</v>
+        <v>-58.25</v>
       </c>
       <c r="L51" t="n">
-        <v>256.82</v>
+        <v>172.23</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-209.34</v>
+        <v>-130.14</v>
       </c>
       <c r="K52" t="n">
-        <v>-461.72</v>
+        <v>-287.03</v>
       </c>
       <c r="L52" t="n">
-        <v>506.96</v>
+        <v>315.15</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>88.01000000000001</v>
+        <v>59.73</v>
       </c>
       <c r="K53" t="n">
-        <v>-63.5</v>
+        <v>-43.09</v>
       </c>
       <c r="L53" t="n">
-        <v>108.53</v>
+        <v>73.65000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-58.63</v>
+        <v>-38.66</v>
       </c>
       <c r="K54" t="n">
-        <v>332.15</v>
+        <v>219.01</v>
       </c>
       <c r="L54" t="n">
-        <v>337.29</v>
+        <v>222.39</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-360.88</v>
+        <v>-231.14</v>
       </c>
       <c r="K55" t="n">
-        <v>273.43</v>
+        <v>175.13</v>
       </c>
       <c r="L55" t="n">
-        <v>452.76</v>
+        <v>289.99</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>249.23</v>
+        <v>127.18</v>
       </c>
       <c r="K56" t="n">
-        <v>46.12</v>
+        <v>23.54</v>
       </c>
       <c r="L56" t="n">
-        <v>253.46</v>
+        <v>129.34</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-394.04</v>
+        <v>-220.16</v>
       </c>
       <c r="K57" t="n">
-        <v>-138.69</v>
+        <v>-77.48999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>417.74</v>
+        <v>233.4</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-388.3</v>
+        <v>-202.89</v>
       </c>
       <c r="K58" t="n">
-        <v>-412.13</v>
+        <v>-215.34</v>
       </c>
       <c r="L58" t="n">
-        <v>566.24</v>
+        <v>295.86</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-111.96</v>
+        <v>-87.34999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-45.43</v>
+        <v>-35.44</v>
       </c>
       <c r="L59" t="n">
-        <v>120.83</v>
+        <v>94.27</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>85.69</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>100.74</v>
+        <v>79.66</v>
       </c>
       <c r="L60" t="n">
-        <v>132.25</v>
+        <v>104.59</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>64.77</v>
+        <v>66.3</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.83</v>
+        <v>-30.54</v>
       </c>
       <c r="L61" t="n">
-        <v>71.31</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>82.7</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-73.76000000000001</v>
+        <v>-61.54</v>
       </c>
       <c r="L62" t="n">
-        <v>110.81</v>
+        <v>92.44</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>8.460000000000001</v>
+        <v>6.83</v>
       </c>
       <c r="K63" t="n">
-        <v>105.28</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>105.62</v>
+        <v>85.26000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-108.95</v>
+        <v>-89.15000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>19.13</v>
+        <v>15.66</v>
       </c>
       <c r="L64" t="n">
-        <v>110.62</v>
+        <v>90.51000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-81.95999999999999</v>
+        <v>-57.89</v>
       </c>
       <c r="K65" t="n">
-        <v>-104.93</v>
+        <v>-74.11</v>
       </c>
       <c r="L65" t="n">
-        <v>133.14</v>
+        <v>94.04000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-104.85</v>
+        <v>-68.23999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>196.91</v>
+        <v>128.15</v>
       </c>
       <c r="L66" t="n">
-        <v>223.08</v>
+        <v>145.19</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-133.04</v>
+        <v>-99.34999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>-136.12</v>
+        <v>-101.65</v>
       </c>
       <c r="L67" t="n">
-        <v>190.33</v>
+        <v>142.14</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-280.09</v>
+        <v>-156.58</v>
       </c>
       <c r="K68" t="n">
-        <v>141.84</v>
+        <v>79.3</v>
       </c>
       <c r="L68" t="n">
-        <v>313.96</v>
+        <v>175.52</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>223.55</v>
+        <v>138.28</v>
       </c>
       <c r="K69" t="n">
-        <v>373.55</v>
+        <v>231.06</v>
       </c>
       <c r="L69" t="n">
-        <v>435.33</v>
+        <v>269.28</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>208.97</v>
+        <v>124.78</v>
       </c>
       <c r="K70" t="n">
-        <v>218.81</v>
+        <v>130.65</v>
       </c>
       <c r="L70" t="n">
-        <v>302.57</v>
+        <v>180.67</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-205.02</v>
+        <v>-110.48</v>
       </c>
       <c r="K71" t="n">
-        <v>-446.37</v>
+        <v>-240.54</v>
       </c>
       <c r="L71" t="n">
-        <v>491.21</v>
+        <v>264.7</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-447.27</v>
+        <v>-278.17</v>
       </c>
       <c r="K72" t="n">
-        <v>143.27</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>469.65</v>
+        <v>292.09</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-591.9</v>
+        <v>-302.85</v>
       </c>
       <c r="K73" t="n">
-        <v>-336.32</v>
+        <v>-172.08</v>
       </c>
       <c r="L73" t="n">
-        <v>680.78</v>
+        <v>348.32</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>30.37</v>
+        <v>23.13</v>
       </c>
       <c r="K74" t="n">
-        <v>-56.59</v>
+        <v>-43.08</v>
       </c>
       <c r="L74" t="n">
-        <v>64.22</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-79.64</v>
+        <v>-63.25</v>
       </c>
       <c r="K75" t="n">
-        <v>0.75</v>
+        <v>0.59</v>
       </c>
       <c r="L75" t="n">
-        <v>79.64</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>22.53</v>
+        <v>17.58</v>
       </c>
       <c r="K76" t="n">
-        <v>-191.67</v>
+        <v>-149.56</v>
       </c>
       <c r="L76" t="n">
-        <v>192.99</v>
+        <v>150.59</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>66.72</v>
+        <v>57.98</v>
       </c>
       <c r="K77" t="n">
-        <v>41.39</v>
+        <v>35.97</v>
       </c>
       <c r="L77" t="n">
-        <v>78.52</v>
+        <v>68.23</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-85.84999999999999</v>
+        <v>-63.43</v>
       </c>
       <c r="K78" t="n">
-        <v>125.06</v>
+        <v>92.41</v>
       </c>
       <c r="L78" t="n">
-        <v>151.69</v>
+        <v>112.08</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>148.28</v>
+        <v>105.09</v>
       </c>
       <c r="K79" t="n">
-        <v>-121.66</v>
+        <v>-86.22</v>
       </c>
       <c r="L79" t="n">
-        <v>191.8</v>
+        <v>135.93</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>254.27</v>
+        <v>161.83</v>
       </c>
       <c r="K80" t="n">
-        <v>-193.68</v>
+        <v>-123.26</v>
       </c>
       <c r="L80" t="n">
-        <v>319.64</v>
+        <v>203.43</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.59</v>
+        <v>-6.87</v>
       </c>
       <c r="K81" t="n">
-        <v>-176.36</v>
+        <v>-126.31</v>
       </c>
       <c r="L81" t="n">
-        <v>176.62</v>
+        <v>126.5</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-201.06</v>
+        <v>-133.97</v>
       </c>
       <c r="K82" t="n">
-        <v>189.78</v>
+        <v>126.46</v>
       </c>
       <c r="L82" t="n">
-        <v>276.48</v>
+        <v>184.23</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>158.91</v>
+        <v>86.47</v>
       </c>
       <c r="K83" t="n">
-        <v>330.46</v>
+        <v>179.82</v>
       </c>
       <c r="L83" t="n">
-        <v>366.68</v>
+        <v>199.53</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-241.42</v>
+        <v>-164.84</v>
       </c>
       <c r="K84" t="n">
-        <v>161.59</v>
+        <v>110.33</v>
       </c>
       <c r="L84" t="n">
-        <v>290.51</v>
+        <v>198.36</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-94.86</v>
+        <v>-58.47</v>
       </c>
       <c r="K85" t="n">
-        <v>-307.38</v>
+        <v>-189.44</v>
       </c>
       <c r="L85" t="n">
-        <v>321.68</v>
+        <v>198.25</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>658.51</v>
+        <v>356.26</v>
       </c>
       <c r="K86" t="n">
-        <v>-373.69</v>
+        <v>-202.17</v>
       </c>
       <c r="L86" t="n">
-        <v>757.15</v>
+        <v>409.63</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-104.28</v>
+        <v>-58.23</v>
       </c>
       <c r="K87" t="n">
-        <v>-489.25</v>
+        <v>-273.22</v>
       </c>
       <c r="L87" t="n">
-        <v>500.24</v>
+        <v>279.35</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-520</v>
+        <v>-264.9</v>
       </c>
       <c r="K88" t="n">
-        <v>83.98999999999999</v>
+        <v>42.79</v>
       </c>
       <c r="L88" t="n">
-        <v>526.74</v>
+        <v>268.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-22.xlsx
+++ b/output/2025-04-22.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>38.37</v>
+        <v>36.81</v>
       </c>
       <c r="K14" t="n">
-        <v>-92.51000000000001</v>
+        <v>-88.73999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>100.15</v>
+        <v>96.06999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>15.8</v>
+        <v>15.35</v>
       </c>
       <c r="K15" t="n">
-        <v>-89.78</v>
+        <v>-87.19</v>
       </c>
       <c r="L15" t="n">
-        <v>91.16</v>
+        <v>88.53</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>38.2</v>
+        <v>36.98</v>
       </c>
       <c r="K16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>38.2</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>29.18</v>
+        <v>29.29</v>
       </c>
       <c r="K17" t="n">
-        <v>83.56999999999999</v>
+        <v>83.89</v>
       </c>
       <c r="L17" t="n">
-        <v>88.52</v>
+        <v>88.86</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>107.24</v>
+        <v>107.05</v>
       </c>
       <c r="K18" t="n">
-        <v>111.36</v>
+        <v>111.16</v>
       </c>
       <c r="L18" t="n">
-        <v>154.6</v>
+        <v>154.33</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-64.75</v>
+        <v>-63.14</v>
       </c>
       <c r="K19" t="n">
-        <v>23.44</v>
+        <v>22.86</v>
       </c>
       <c r="L19" t="n">
-        <v>68.86</v>
+        <v>67.15000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>127.12</v>
+        <v>134.19</v>
       </c>
       <c r="K20" t="n">
-        <v>7.71</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>127.35</v>
+        <v>134.44</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>17.62</v>
+        <v>18.68</v>
       </c>
       <c r="K21" t="n">
-        <v>188.16</v>
+        <v>199.52</v>
       </c>
       <c r="L21" t="n">
-        <v>188.98</v>
+        <v>200.39</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-62.69</v>
+        <v>-65.59</v>
       </c>
       <c r="K22" t="n">
-        <v>96.22</v>
+        <v>100.68</v>
       </c>
       <c r="L22" t="n">
-        <v>114.84</v>
+        <v>120.16</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>151.49</v>
+        <v>166.09</v>
       </c>
       <c r="K23" t="n">
-        <v>112.58</v>
+        <v>123.43</v>
       </c>
       <c r="L23" t="n">
-        <v>188.74</v>
+        <v>206.93</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-170.68</v>
+        <v>-186.27</v>
       </c>
       <c r="K24" t="n">
-        <v>10.71</v>
+        <v>11.69</v>
       </c>
       <c r="L24" t="n">
-        <v>171.02</v>
+        <v>186.64</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-168.53</v>
+        <v>-181.79</v>
       </c>
       <c r="K25" t="n">
-        <v>149.43</v>
+        <v>161.19</v>
       </c>
       <c r="L25" t="n">
-        <v>225.23</v>
+        <v>242.96</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-328.49</v>
+        <v>-360.37</v>
       </c>
       <c r="K26" t="n">
-        <v>-144.53</v>
+        <v>-158.56</v>
       </c>
       <c r="L26" t="n">
-        <v>358.88</v>
+        <v>393.71</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>234.44</v>
+        <v>256.03</v>
       </c>
       <c r="K27" t="n">
-        <v>-127.32</v>
+        <v>-139.05</v>
       </c>
       <c r="L27" t="n">
-        <v>266.78</v>
+        <v>291.35</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-160.93</v>
+        <v>-174.32</v>
       </c>
       <c r="K28" t="n">
-        <v>-9.58</v>
+        <v>-10.38</v>
       </c>
       <c r="L28" t="n">
-        <v>161.21</v>
+        <v>174.63</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="K29" t="n">
-        <v>133.58</v>
+        <v>128.05</v>
       </c>
       <c r="L29" t="n">
-        <v>133.58</v>
+        <v>128.05</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-28.24</v>
+        <v>-27.78</v>
       </c>
       <c r="K30" t="n">
-        <v>-95.05</v>
+        <v>-93.48</v>
       </c>
       <c r="L30" t="n">
-        <v>99.16</v>
+        <v>97.52</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>30.26</v>
+        <v>29.35</v>
       </c>
       <c r="K31" t="n">
-        <v>-86.90000000000001</v>
+        <v>-84.27</v>
       </c>
       <c r="L31" t="n">
-        <v>92.02</v>
+        <v>89.23999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>62.96</v>
+        <v>62.74</v>
       </c>
       <c r="K32" t="n">
-        <v>-56.66</v>
+        <v>-56.47</v>
       </c>
       <c r="L32" t="n">
-        <v>84.7</v>
+        <v>84.41</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>73.88</v>
+        <v>72.95</v>
       </c>
       <c r="K33" t="n">
-        <v>29.05</v>
+        <v>28.69</v>
       </c>
       <c r="L33" t="n">
-        <v>79.38</v>
+        <v>78.39</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-65.16</v>
+        <v>-65.09</v>
       </c>
       <c r="K34" t="n">
-        <v>-53.91</v>
+        <v>-53.85</v>
       </c>
       <c r="L34" t="n">
-        <v>84.56999999999999</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-18.26</v>
+        <v>-18.97</v>
       </c>
       <c r="K35" t="n">
-        <v>114.32</v>
+        <v>118.74</v>
       </c>
       <c r="L35" t="n">
-        <v>115.77</v>
+        <v>120.25</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>115.91</v>
+        <v>119.22</v>
       </c>
       <c r="K36" t="n">
-        <v>-28.16</v>
+        <v>-28.97</v>
       </c>
       <c r="L36" t="n">
-        <v>119.29</v>
+        <v>122.69</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-19.08</v>
+        <v>-19.93</v>
       </c>
       <c r="K37" t="n">
-        <v>-158.25</v>
+        <v>-165.35</v>
       </c>
       <c r="L37" t="n">
-        <v>159.4</v>
+        <v>166.55</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>193.66</v>
+        <v>209.14</v>
       </c>
       <c r="K38" t="n">
-        <v>11.45</v>
+        <v>12.36</v>
       </c>
       <c r="L38" t="n">
-        <v>193.99</v>
+        <v>209.51</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-147.65</v>
+        <v>-156.95</v>
       </c>
       <c r="K39" t="n">
-        <v>-97.84999999999999</v>
+        <v>-104.01</v>
       </c>
       <c r="L39" t="n">
-        <v>177.13</v>
+        <v>188.28</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>219.13</v>
+        <v>235.83</v>
       </c>
       <c r="K40" t="n">
-        <v>196.13</v>
+        <v>211.09</v>
       </c>
       <c r="L40" t="n">
-        <v>294.08</v>
+        <v>316.5</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-22.95</v>
+        <v>-24.81</v>
       </c>
       <c r="K41" t="n">
-        <v>302.61</v>
+        <v>327.19</v>
       </c>
       <c r="L41" t="n">
-        <v>303.48</v>
+        <v>328.13</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>258.23</v>
+        <v>279.25</v>
       </c>
       <c r="K42" t="n">
-        <v>-64.69</v>
+        <v>-69.95999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>266.21</v>
+        <v>287.88</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-156.26</v>
+        <v>-168.2</v>
       </c>
       <c r="K43" t="n">
-        <v>215.2</v>
+        <v>231.64</v>
       </c>
       <c r="L43" t="n">
-        <v>265.95</v>
+        <v>286.26</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>73.58</v>
+        <v>71.78</v>
       </c>
       <c r="K44" t="n">
-        <v>-33.99</v>
+        <v>-33.16</v>
       </c>
       <c r="L44" t="n">
-        <v>81.05</v>
+        <v>79.06999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-105.82</v>
+        <v>-101.69</v>
       </c>
       <c r="K45" t="n">
-        <v>-27.65</v>
+        <v>-26.57</v>
       </c>
       <c r="L45" t="n">
-        <v>109.37</v>
+        <v>105.1</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>25.73</v>
+        <v>24.83</v>
       </c>
       <c r="K46" t="n">
-        <v>41.23</v>
+        <v>39.79</v>
       </c>
       <c r="L46" t="n">
-        <v>48.6</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-135.57</v>
+        <v>-137.44</v>
       </c>
       <c r="K47" t="n">
-        <v>41.89</v>
+        <v>42.47</v>
       </c>
       <c r="L47" t="n">
-        <v>141.9</v>
+        <v>143.85</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>66.27</v>
+        <v>66.56</v>
       </c>
       <c r="K48" t="n">
-        <v>117.82</v>
+        <v>118.32</v>
       </c>
       <c r="L48" t="n">
-        <v>135.18</v>
+        <v>135.76</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>32.58</v>
+        <v>32.56</v>
       </c>
       <c r="K49" t="n">
-        <v>53.19</v>
+        <v>53.15</v>
       </c>
       <c r="L49" t="n">
-        <v>62.37</v>
+        <v>62.33</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-43.86</v>
+        <v>-44.95</v>
       </c>
       <c r="K50" t="n">
-        <v>105</v>
+        <v>107.62</v>
       </c>
       <c r="L50" t="n">
-        <v>113.8</v>
+        <v>116.63</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-162.08</v>
+        <v>-169.76</v>
       </c>
       <c r="K51" t="n">
-        <v>-58.25</v>
+        <v>-61.01</v>
       </c>
       <c r="L51" t="n">
-        <v>172.23</v>
+        <v>180.39</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-130.14</v>
+        <v>-136.94</v>
       </c>
       <c r="K52" t="n">
-        <v>-287.03</v>
+        <v>-302.02</v>
       </c>
       <c r="L52" t="n">
-        <v>315.15</v>
+        <v>331.62</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>59.73</v>
+        <v>63.88</v>
       </c>
       <c r="K53" t="n">
-        <v>-43.09</v>
+        <v>-46.09</v>
       </c>
       <c r="L53" t="n">
-        <v>73.65000000000001</v>
+        <v>78.77</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-38.66</v>
+        <v>-41.18</v>
       </c>
       <c r="K54" t="n">
-        <v>219.01</v>
+        <v>233.31</v>
       </c>
       <c r="L54" t="n">
-        <v>222.39</v>
+        <v>236.92</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-231.14</v>
+        <v>-240.05</v>
       </c>
       <c r="K55" t="n">
-        <v>175.13</v>
+        <v>181.88</v>
       </c>
       <c r="L55" t="n">
-        <v>289.99</v>
+        <v>301.17</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>127.18</v>
+        <v>139.87</v>
       </c>
       <c r="K56" t="n">
-        <v>23.54</v>
+        <v>25.88</v>
       </c>
       <c r="L56" t="n">
-        <v>129.34</v>
+        <v>142.24</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-220.16</v>
+        <v>-240.64</v>
       </c>
       <c r="K57" t="n">
-        <v>-77.48999999999999</v>
+        <v>-84.7</v>
       </c>
       <c r="L57" t="n">
-        <v>233.4</v>
+        <v>255.11</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-202.89</v>
+        <v>-223.85</v>
       </c>
       <c r="K58" t="n">
-        <v>-215.34</v>
+        <v>-237.59</v>
       </c>
       <c r="L58" t="n">
-        <v>295.86</v>
+        <v>326.43</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-87.34999999999999</v>
+        <v>-86.01000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-35.44</v>
+        <v>-34.9</v>
       </c>
       <c r="L59" t="n">
-        <v>94.27</v>
+        <v>92.81999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>67.76000000000001</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>79.66</v>
+        <v>77.42</v>
       </c>
       <c r="L60" t="n">
-        <v>104.59</v>
+        <v>101.64</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>66.3</v>
+        <v>63.19</v>
       </c>
       <c r="K61" t="n">
-        <v>-30.54</v>
+        <v>-29.1</v>
       </c>
       <c r="L61" t="n">
-        <v>73</v>
+        <v>69.56999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>68.98999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="K62" t="n">
-        <v>-61.54</v>
+        <v>-61.18</v>
       </c>
       <c r="L62" t="n">
-        <v>92.44</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>6.83</v>
+        <v>6.87</v>
       </c>
       <c r="K63" t="n">
-        <v>84.98999999999999</v>
+        <v>85.53</v>
       </c>
       <c r="L63" t="n">
-        <v>85.26000000000001</v>
+        <v>85.81</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-89.15000000000001</v>
+        <v>-88.59</v>
       </c>
       <c r="K64" t="n">
-        <v>15.66</v>
+        <v>15.56</v>
       </c>
       <c r="L64" t="n">
-        <v>90.51000000000001</v>
+        <v>89.95</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-57.89</v>
+        <v>-59.76</v>
       </c>
       <c r="K65" t="n">
-        <v>-74.11</v>
+        <v>-76.51000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>94.04000000000001</v>
+        <v>97.09</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-68.23999999999999</v>
+        <v>-71.11</v>
       </c>
       <c r="K66" t="n">
-        <v>128.15</v>
+        <v>133.54</v>
       </c>
       <c r="L66" t="n">
-        <v>145.19</v>
+        <v>151.29</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-99.34999999999999</v>
+        <v>-102.43</v>
       </c>
       <c r="K67" t="n">
-        <v>-101.65</v>
+        <v>-104.8</v>
       </c>
       <c r="L67" t="n">
-        <v>142.14</v>
+        <v>146.54</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-156.58</v>
+        <v>-167.17</v>
       </c>
       <c r="K68" t="n">
-        <v>79.3</v>
+        <v>84.66</v>
       </c>
       <c r="L68" t="n">
-        <v>175.52</v>
+        <v>187.38</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>138.28</v>
+        <v>148.05</v>
       </c>
       <c r="K69" t="n">
-        <v>231.06</v>
+        <v>247.4</v>
       </c>
       <c r="L69" t="n">
-        <v>269.28</v>
+        <v>288.31</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>124.78</v>
+        <v>135.24</v>
       </c>
       <c r="K70" t="n">
-        <v>130.65</v>
+        <v>141.6</v>
       </c>
       <c r="L70" t="n">
-        <v>180.67</v>
+        <v>195.81</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-110.48</v>
+        <v>-121.65</v>
       </c>
       <c r="K71" t="n">
-        <v>-240.54</v>
+        <v>-264.85</v>
       </c>
       <c r="L71" t="n">
-        <v>264.7</v>
+        <v>291.46</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-278.17</v>
+        <v>-296.9</v>
       </c>
       <c r="K72" t="n">
-        <v>89.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>292.09</v>
+        <v>311.75</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-302.85</v>
+        <v>-327.24</v>
       </c>
       <c r="K73" t="n">
-        <v>-172.08</v>
+        <v>-185.94</v>
       </c>
       <c r="L73" t="n">
-        <v>348.32</v>
+        <v>376.38</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>23.13</v>
+        <v>22.77</v>
       </c>
       <c r="K74" t="n">
-        <v>-43.08</v>
+        <v>-42.41</v>
       </c>
       <c r="L74" t="n">
-        <v>48.9</v>
+        <v>48.14</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-63.25</v>
+        <v>-61.68</v>
       </c>
       <c r="K75" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="L75" t="n">
-        <v>63.25</v>
+        <v>61.69</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>17.58</v>
+        <v>17.06</v>
       </c>
       <c r="K76" t="n">
-        <v>-149.56</v>
+        <v>-145.2</v>
       </c>
       <c r="L76" t="n">
-        <v>150.59</v>
+        <v>146.2</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>57.98</v>
+        <v>55.82</v>
       </c>
       <c r="K77" t="n">
-        <v>35.97</v>
+        <v>34.63</v>
       </c>
       <c r="L77" t="n">
-        <v>68.23</v>
+        <v>65.69</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-63.43</v>
+        <v>-64.40000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>92.41</v>
+        <v>93.81</v>
       </c>
       <c r="L78" t="n">
-        <v>112.08</v>
+        <v>113.79</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>105.09</v>
+        <v>106.25</v>
       </c>
       <c r="K79" t="n">
-        <v>-86.22</v>
+        <v>-87.17</v>
       </c>
       <c r="L79" t="n">
-        <v>135.93</v>
+        <v>137.43</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>161.83</v>
+        <v>169.03</v>
       </c>
       <c r="K80" t="n">
-        <v>-123.26</v>
+        <v>-128.75</v>
       </c>
       <c r="L80" t="n">
-        <v>203.43</v>
+        <v>212.48</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.87</v>
+        <v>-7.21</v>
       </c>
       <c r="K81" t="n">
-        <v>-126.31</v>
+        <v>-132.61</v>
       </c>
       <c r="L81" t="n">
-        <v>126.5</v>
+        <v>132.8</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-133.97</v>
+        <v>-140.43</v>
       </c>
       <c r="K82" t="n">
-        <v>126.46</v>
+        <v>132.56</v>
       </c>
       <c r="L82" t="n">
-        <v>184.23</v>
+        <v>193.11</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>86.47</v>
+        <v>93.02</v>
       </c>
       <c r="K83" t="n">
-        <v>179.82</v>
+        <v>193.44</v>
       </c>
       <c r="L83" t="n">
-        <v>199.53</v>
+        <v>214.64</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-164.84</v>
+        <v>-176.05</v>
       </c>
       <c r="K84" t="n">
-        <v>110.33</v>
+        <v>117.83</v>
       </c>
       <c r="L84" t="n">
-        <v>198.36</v>
+        <v>211.85</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-58.47</v>
+        <v>-62.81</v>
       </c>
       <c r="K85" t="n">
-        <v>-189.44</v>
+        <v>-203.52</v>
       </c>
       <c r="L85" t="n">
-        <v>198.25</v>
+        <v>213</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>356.26</v>
+        <v>383.62</v>
       </c>
       <c r="K86" t="n">
-        <v>-202.17</v>
+        <v>-217.7</v>
       </c>
       <c r="L86" t="n">
-        <v>409.63</v>
+        <v>441.09</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-58.23</v>
+        <v>-63.02</v>
       </c>
       <c r="K87" t="n">
-        <v>-273.22</v>
+        <v>-295.65</v>
       </c>
       <c r="L87" t="n">
-        <v>279.35</v>
+        <v>302.29</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-264.9</v>
+        <v>-286.09</v>
       </c>
       <c r="K88" t="n">
-        <v>42.79</v>
+        <v>46.21</v>
       </c>
       <c r="L88" t="n">
-        <v>268.34</v>
+        <v>289.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-22.xlsx
+++ b/output/2025-04-22.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>36.81</v>
+        <v>24.59</v>
       </c>
       <c r="K14" t="n">
-        <v>-88.73999999999999</v>
+        <v>-59.29</v>
       </c>
       <c r="L14" t="n">
-        <v>96.06999999999999</v>
+        <v>64.19</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>15.35</v>
+        <v>11.51</v>
       </c>
       <c r="K15" t="n">
-        <v>-87.19</v>
+        <v>-65.39</v>
       </c>
       <c r="L15" t="n">
-        <v>88.53</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>36.98</v>
+        <v>27.74</v>
       </c>
       <c r="K16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="L16" t="n">
-        <v>36.98</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>29.29</v>
+        <v>21.97</v>
       </c>
       <c r="K17" t="n">
-        <v>83.89</v>
+        <v>62.92</v>
       </c>
       <c r="L17" t="n">
-        <v>88.86</v>
+        <v>66.65000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>107.05</v>
+        <v>68.62</v>
       </c>
       <c r="K18" t="n">
-        <v>111.16</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>154.33</v>
+        <v>98.93000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-63.14</v>
+        <v>-41.29</v>
       </c>
       <c r="K19" t="n">
-        <v>22.86</v>
+        <v>14.95</v>
       </c>
       <c r="L19" t="n">
-        <v>67.15000000000001</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>134.19</v>
+        <v>91.03</v>
       </c>
       <c r="K20" t="n">
-        <v>8.140000000000001</v>
+        <v>5.52</v>
       </c>
       <c r="L20" t="n">
-        <v>134.44</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>18.68</v>
+        <v>12.17</v>
       </c>
       <c r="K21" t="n">
-        <v>199.52</v>
+        <v>130.03</v>
       </c>
       <c r="L21" t="n">
-        <v>200.39</v>
+        <v>130.6</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-65.59</v>
+        <v>-41.88</v>
       </c>
       <c r="K22" t="n">
-        <v>100.68</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>120.16</v>
+        <v>76.73</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>166.09</v>
+        <v>124.57</v>
       </c>
       <c r="K23" t="n">
-        <v>123.43</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>206.93</v>
+        <v>155.2</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-186.27</v>
+        <v>-136.22</v>
       </c>
       <c r="K24" t="n">
-        <v>11.69</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>186.64</v>
+        <v>136.49</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-181.79</v>
+        <v>-131.66</v>
       </c>
       <c r="K25" t="n">
-        <v>161.19</v>
+        <v>116.74</v>
       </c>
       <c r="L25" t="n">
-        <v>242.96</v>
+        <v>175.97</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-360.37</v>
+        <v>-250.82</v>
       </c>
       <c r="K26" t="n">
-        <v>-158.56</v>
+        <v>-110.36</v>
       </c>
       <c r="L26" t="n">
-        <v>393.71</v>
+        <v>274.02</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>256.03</v>
+        <v>178.19</v>
       </c>
       <c r="K27" t="n">
-        <v>-139.05</v>
+        <v>-96.78</v>
       </c>
       <c r="L27" t="n">
-        <v>291.35</v>
+        <v>202.78</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-174.32</v>
+        <v>-112.96</v>
       </c>
       <c r="K28" t="n">
-        <v>-10.38</v>
+        <v>-6.73</v>
       </c>
       <c r="L28" t="n">
-        <v>174.63</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="K29" t="n">
-        <v>128.05</v>
+        <v>74.86</v>
       </c>
       <c r="L29" t="n">
-        <v>128.05</v>
+        <v>74.86</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-27.78</v>
+        <v>-18.61</v>
       </c>
       <c r="K30" t="n">
-        <v>-93.48</v>
+        <v>-62.64</v>
       </c>
       <c r="L30" t="n">
-        <v>97.52</v>
+        <v>65.34999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>29.35</v>
+        <v>19.5</v>
       </c>
       <c r="K31" t="n">
-        <v>-84.27</v>
+        <v>-56</v>
       </c>
       <c r="L31" t="n">
-        <v>89.23999999999999</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>62.74</v>
+        <v>38.82</v>
       </c>
       <c r="K32" t="n">
-        <v>-56.47</v>
+        <v>-34.94</v>
       </c>
       <c r="L32" t="n">
-        <v>84.41</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>72.95</v>
+        <v>48.85</v>
       </c>
       <c r="K33" t="n">
-        <v>28.69</v>
+        <v>19.21</v>
       </c>
       <c r="L33" t="n">
-        <v>78.39</v>
+        <v>52.49</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-65.09</v>
+        <v>-48.82</v>
       </c>
       <c r="K34" t="n">
-        <v>-53.85</v>
+        <v>-40.39</v>
       </c>
       <c r="L34" t="n">
-        <v>84.48</v>
+        <v>63.36</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-18.97</v>
+        <v>-11.23</v>
       </c>
       <c r="K35" t="n">
-        <v>118.74</v>
+        <v>70.33</v>
       </c>
       <c r="L35" t="n">
-        <v>120.25</v>
+        <v>71.22</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>119.22</v>
+        <v>79.13</v>
       </c>
       <c r="K36" t="n">
-        <v>-28.97</v>
+        <v>-19.22</v>
       </c>
       <c r="L36" t="n">
-        <v>122.69</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-19.93</v>
+        <v>-12.84</v>
       </c>
       <c r="K37" t="n">
-        <v>-165.35</v>
+        <v>-106.51</v>
       </c>
       <c r="L37" t="n">
-        <v>166.55</v>
+        <v>107.28</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>209.14</v>
+        <v>127.41</v>
       </c>
       <c r="K38" t="n">
-        <v>12.36</v>
+        <v>7.53</v>
       </c>
       <c r="L38" t="n">
-        <v>209.51</v>
+        <v>127.63</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-156.95</v>
+        <v>-101.19</v>
       </c>
       <c r="K39" t="n">
-        <v>-104.01</v>
+        <v>-67.06</v>
       </c>
       <c r="L39" t="n">
-        <v>188.28</v>
+        <v>121.39</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>235.83</v>
+        <v>156.67</v>
       </c>
       <c r="K40" t="n">
-        <v>211.09</v>
+        <v>140.23</v>
       </c>
       <c r="L40" t="n">
-        <v>316.5</v>
+        <v>210.26</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-24.81</v>
+        <v>-16.34</v>
       </c>
       <c r="K41" t="n">
-        <v>327.19</v>
+        <v>215.46</v>
       </c>
       <c r="L41" t="n">
-        <v>328.13</v>
+        <v>216.08</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>279.25</v>
+        <v>186.96</v>
       </c>
       <c r="K42" t="n">
-        <v>-69.95999999999999</v>
+        <v>-46.84</v>
       </c>
       <c r="L42" t="n">
-        <v>287.88</v>
+        <v>192.74</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-168.2</v>
+        <v>-112.61</v>
       </c>
       <c r="K43" t="n">
-        <v>231.64</v>
+        <v>155.09</v>
       </c>
       <c r="L43" t="n">
-        <v>286.26</v>
+        <v>191.66</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>71.78</v>
+        <v>47.56</v>
       </c>
       <c r="K44" t="n">
-        <v>-33.16</v>
+        <v>-21.97</v>
       </c>
       <c r="L44" t="n">
-        <v>79.06999999999999</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-101.69</v>
+        <v>-62.67</v>
       </c>
       <c r="K45" t="n">
-        <v>-26.57</v>
+        <v>-16.37</v>
       </c>
       <c r="L45" t="n">
-        <v>105.1</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>24.83</v>
+        <v>15.51</v>
       </c>
       <c r="K46" t="n">
-        <v>39.79</v>
+        <v>24.85</v>
       </c>
       <c r="L46" t="n">
-        <v>46.9</v>
+        <v>29.29</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-137.44</v>
+        <v>-87.45999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>42.47</v>
+        <v>27.03</v>
       </c>
       <c r="L47" t="n">
-        <v>143.85</v>
+        <v>91.54000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>66.56</v>
+        <v>40.81</v>
       </c>
       <c r="K48" t="n">
-        <v>118.32</v>
+        <v>72.56</v>
       </c>
       <c r="L48" t="n">
-        <v>135.76</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>32.56</v>
+        <v>22.22</v>
       </c>
       <c r="K49" t="n">
-        <v>53.15</v>
+        <v>36.28</v>
       </c>
       <c r="L49" t="n">
-        <v>62.33</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-44.95</v>
+        <v>-32.16</v>
       </c>
       <c r="K50" t="n">
-        <v>107.62</v>
+        <v>77</v>
       </c>
       <c r="L50" t="n">
-        <v>116.63</v>
+        <v>83.45</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-169.76</v>
+        <v>-106.57</v>
       </c>
       <c r="K51" t="n">
-        <v>-61.01</v>
+        <v>-38.3</v>
       </c>
       <c r="L51" t="n">
-        <v>180.39</v>
+        <v>113.25</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-136.94</v>
+        <v>-82.78</v>
       </c>
       <c r="K52" t="n">
-        <v>-302.02</v>
+        <v>-182.58</v>
       </c>
       <c r="L52" t="n">
-        <v>331.62</v>
+        <v>200.47</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>63.88</v>
+        <v>11.52</v>
       </c>
       <c r="K53" t="n">
-        <v>-46.09</v>
+        <v>-8.31</v>
       </c>
       <c r="L53" t="n">
-        <v>78.77</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-41.18</v>
+        <v>-27.69</v>
       </c>
       <c r="K54" t="n">
-        <v>233.31</v>
+        <v>156.84</v>
       </c>
       <c r="L54" t="n">
-        <v>236.92</v>
+        <v>159.27</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-240.05</v>
+        <v>-143.41</v>
       </c>
       <c r="K55" t="n">
-        <v>181.88</v>
+        <v>108.66</v>
       </c>
       <c r="L55" t="n">
-        <v>301.17</v>
+        <v>179.93</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>139.87</v>
+        <v>101.43</v>
       </c>
       <c r="K56" t="n">
-        <v>25.88</v>
+        <v>18.77</v>
       </c>
       <c r="L56" t="n">
-        <v>142.24</v>
+        <v>103.15</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-240.64</v>
+        <v>-169.36</v>
       </c>
       <c r="K57" t="n">
-        <v>-84.7</v>
+        <v>-59.61</v>
       </c>
       <c r="L57" t="n">
-        <v>255.11</v>
+        <v>179.55</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-223.85</v>
+        <v>-144.47</v>
       </c>
       <c r="K58" t="n">
-        <v>-237.59</v>
+        <v>-153.34</v>
       </c>
       <c r="L58" t="n">
-        <v>326.43</v>
+        <v>210.68</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-86.01000000000001</v>
+        <v>-51.92</v>
       </c>
       <c r="K59" t="n">
-        <v>-34.9</v>
+        <v>-21.06</v>
       </c>
       <c r="L59" t="n">
-        <v>92.81999999999999</v>
+        <v>56.03</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>65.84999999999999</v>
+        <v>41.89</v>
       </c>
       <c r="K60" t="n">
-        <v>77.42</v>
+        <v>49.25</v>
       </c>
       <c r="L60" t="n">
-        <v>101.64</v>
+        <v>64.65000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>63.19</v>
+        <v>42.96</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.1</v>
+        <v>-19.78</v>
       </c>
       <c r="L61" t="n">
-        <v>69.56999999999999</v>
+        <v>47.29</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>68.58</v>
+        <v>45.08</v>
       </c>
       <c r="K62" t="n">
-        <v>-61.18</v>
+        <v>-40.21</v>
       </c>
       <c r="L62" t="n">
-        <v>91.90000000000001</v>
+        <v>60.41</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>6.87</v>
+        <v>4.22</v>
       </c>
       <c r="K63" t="n">
-        <v>85.53</v>
+        <v>52.57</v>
       </c>
       <c r="L63" t="n">
-        <v>85.81</v>
+        <v>52.74</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-88.59</v>
+        <v>-62.04</v>
       </c>
       <c r="K64" t="n">
-        <v>15.56</v>
+        <v>10.89</v>
       </c>
       <c r="L64" t="n">
-        <v>89.95</v>
+        <v>62.98</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-59.76</v>
+        <v>-36.41</v>
       </c>
       <c r="K65" t="n">
-        <v>-76.51000000000001</v>
+        <v>-46.62</v>
       </c>
       <c r="L65" t="n">
-        <v>97.09</v>
+        <v>59.16</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-71.11</v>
+        <v>-44.64</v>
       </c>
       <c r="K66" t="n">
-        <v>133.54</v>
+        <v>83.83</v>
       </c>
       <c r="L66" t="n">
-        <v>151.29</v>
+        <v>94.98</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-102.43</v>
+        <v>-59.77</v>
       </c>
       <c r="K67" t="n">
-        <v>-104.8</v>
+        <v>-61.15</v>
       </c>
       <c r="L67" t="n">
-        <v>146.54</v>
+        <v>85.51000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-167.17</v>
+        <v>-100.76</v>
       </c>
       <c r="K68" t="n">
-        <v>84.66</v>
+        <v>51.03</v>
       </c>
       <c r="L68" t="n">
-        <v>187.38</v>
+        <v>112.94</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>148.05</v>
+        <v>95.11</v>
       </c>
       <c r="K69" t="n">
-        <v>247.4</v>
+        <v>158.93</v>
       </c>
       <c r="L69" t="n">
-        <v>288.31</v>
+        <v>185.22</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>135.24</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>141.6</v>
+        <v>101.11</v>
       </c>
       <c r="L70" t="n">
-        <v>195.81</v>
+        <v>139.82</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-121.65</v>
+        <v>-86.01000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-264.85</v>
+        <v>-187.25</v>
       </c>
       <c r="L71" t="n">
-        <v>291.46</v>
+        <v>206.06</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-296.9</v>
+        <v>-208.02</v>
       </c>
       <c r="K72" t="n">
-        <v>95.09999999999999</v>
+        <v>66.63</v>
       </c>
       <c r="L72" t="n">
-        <v>311.75</v>
+        <v>218.43</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-327.24</v>
+        <v>-199.49</v>
       </c>
       <c r="K73" t="n">
-        <v>-185.94</v>
+        <v>-113.36</v>
       </c>
       <c r="L73" t="n">
-        <v>376.38</v>
+        <v>229.45</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>22.77</v>
+        <v>16.57</v>
       </c>
       <c r="K74" t="n">
-        <v>-42.41</v>
+        <v>-30.87</v>
       </c>
       <c r="L74" t="n">
-        <v>48.14</v>
+        <v>35.04</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-61.68</v>
+        <v>-38.09</v>
       </c>
       <c r="K75" t="n">
-        <v>0.58</v>
+        <v>0.36</v>
       </c>
       <c r="L75" t="n">
-        <v>61.69</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>17.06</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-145.2</v>
+        <v>-84.15000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>146.2</v>
+        <v>84.73</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>55.82</v>
+        <v>41.86</v>
       </c>
       <c r="K77" t="n">
-        <v>34.63</v>
+        <v>25.97</v>
       </c>
       <c r="L77" t="n">
-        <v>65.69</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-64.40000000000001</v>
+        <v>-42.55</v>
       </c>
       <c r="K78" t="n">
-        <v>93.81</v>
+        <v>61.99</v>
       </c>
       <c r="L78" t="n">
-        <v>113.79</v>
+        <v>75.19</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>106.25</v>
+        <v>64.44</v>
       </c>
       <c r="K79" t="n">
-        <v>-87.17</v>
+        <v>-52.87</v>
       </c>
       <c r="L79" t="n">
-        <v>137.43</v>
+        <v>83.34999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>169.03</v>
+        <v>86.92</v>
       </c>
       <c r="K80" t="n">
-        <v>-128.75</v>
+        <v>-66.20999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>212.48</v>
+        <v>109.26</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.21</v>
+        <v>-4.97</v>
       </c>
       <c r="K81" t="n">
-        <v>-132.61</v>
+        <v>-91.42</v>
       </c>
       <c r="L81" t="n">
-        <v>132.8</v>
+        <v>91.56</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-140.43</v>
+        <v>-80.95999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>132.56</v>
+        <v>76.42</v>
       </c>
       <c r="L82" t="n">
-        <v>193.11</v>
+        <v>111.33</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>93.02</v>
+        <v>59.34</v>
       </c>
       <c r="K83" t="n">
-        <v>193.44</v>
+        <v>123.4</v>
       </c>
       <c r="L83" t="n">
-        <v>214.64</v>
+        <v>136.92</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-176.05</v>
+        <v>-117.65</v>
       </c>
       <c r="K84" t="n">
-        <v>117.83</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>211.85</v>
+        <v>141.57</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-62.81</v>
+        <v>-42.4</v>
       </c>
       <c r="K85" t="n">
-        <v>-203.52</v>
+        <v>-137.37</v>
       </c>
       <c r="L85" t="n">
-        <v>213</v>
+        <v>143.76</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>383.62</v>
+        <v>211.13</v>
       </c>
       <c r="K86" t="n">
-        <v>-217.7</v>
+        <v>-119.81</v>
       </c>
       <c r="L86" t="n">
-        <v>441.09</v>
+        <v>242.75</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-63.02</v>
+        <v>-40.75</v>
       </c>
       <c r="K87" t="n">
-        <v>-295.65</v>
+        <v>-191.19</v>
       </c>
       <c r="L87" t="n">
-        <v>302.29</v>
+        <v>195.49</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-286.09</v>
+        <v>-186.88</v>
       </c>
       <c r="K88" t="n">
-        <v>46.21</v>
+        <v>30.18</v>
       </c>
       <c r="L88" t="n">
-        <v>289.8</v>
+        <v>189.3</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-22.xlsx
+++ b/output/2025-04-22.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>24.59</v>
+        <v>23.85</v>
       </c>
       <c r="K14" t="n">
-        <v>-59.29</v>
+        <v>-57.49</v>
       </c>
       <c r="L14" t="n">
-        <v>64.19</v>
+        <v>62.24</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>11.51</v>
+        <v>11.1</v>
       </c>
       <c r="K15" t="n">
-        <v>-65.39</v>
+        <v>-63.06</v>
       </c>
       <c r="L15" t="n">
-        <v>66.40000000000001</v>
+        <v>64.03</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>27.74</v>
+        <v>30.1</v>
       </c>
       <c r="K16" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L16" t="n">
-        <v>27.74</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="17">
@@ -772,7 +772,7 @@
         <v>62.92</v>
       </c>
       <c r="L17" t="n">
-        <v>66.65000000000001</v>
+        <v>66.64</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>68.62</v>
+        <v>66.2</v>
       </c>
       <c r="K18" t="n">
-        <v>71.26000000000001</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>98.93000000000001</v>
+        <v>95.44</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-41.29</v>
+        <v>-43.65</v>
       </c>
       <c r="K19" t="n">
-        <v>14.95</v>
+        <v>15.8</v>
       </c>
       <c r="L19" t="n">
-        <v>43.92</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>91.03</v>
+        <v>92.11</v>
       </c>
       <c r="K20" t="n">
-        <v>5.52</v>
+        <v>5.59</v>
       </c>
       <c r="L20" t="n">
-        <v>91.2</v>
+        <v>92.28</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>12.17</v>
+        <v>11.86</v>
       </c>
       <c r="K21" t="n">
-        <v>130.03</v>
+        <v>126.69</v>
       </c>
       <c r="L21" t="n">
-        <v>130.6</v>
+        <v>127.25</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-41.88</v>
+        <v>-43.43</v>
       </c>
       <c r="K22" t="n">
-        <v>64.29000000000001</v>
+        <v>66.66</v>
       </c>
       <c r="L22" t="n">
-        <v>76.73</v>
+        <v>79.56</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>124.57</v>
+        <v>121.73</v>
       </c>
       <c r="K23" t="n">
-        <v>92.56999999999999</v>
+        <v>90.47</v>
       </c>
       <c r="L23" t="n">
-        <v>155.2</v>
+        <v>151.67</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-136.22</v>
+        <v>-135.07</v>
       </c>
       <c r="K24" t="n">
-        <v>8.550000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="L24" t="n">
-        <v>136.49</v>
+        <v>135.34</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-131.66</v>
+        <v>-126.8</v>
       </c>
       <c r="K25" t="n">
-        <v>116.74</v>
+        <v>112.43</v>
       </c>
       <c r="L25" t="n">
-        <v>175.97</v>
+        <v>169.46</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-250.82</v>
+        <v>-241.39</v>
       </c>
       <c r="K26" t="n">
-        <v>-110.36</v>
+        <v>-106.21</v>
       </c>
       <c r="L26" t="n">
-        <v>274.02</v>
+        <v>263.73</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>178.19</v>
+        <v>176.74</v>
       </c>
       <c r="K27" t="n">
-        <v>-96.78</v>
+        <v>-95.98999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>202.78</v>
+        <v>201.13</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-112.96</v>
+        <v>-122.41</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.73</v>
+        <v>-7.29</v>
       </c>
       <c r="L28" t="n">
-        <v>113.16</v>
+        <v>122.62</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="K29" t="n">
-        <v>74.86</v>
+        <v>72.62</v>
       </c>
       <c r="L29" t="n">
-        <v>74.86</v>
+        <v>72.62</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-18.61</v>
+        <v>-18.1</v>
       </c>
       <c r="K30" t="n">
-        <v>-62.64</v>
+        <v>-60.92</v>
       </c>
       <c r="L30" t="n">
-        <v>65.34999999999999</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>19.5</v>
+        <v>19.11</v>
       </c>
       <c r="K31" t="n">
-        <v>-56</v>
+        <v>-54.89</v>
       </c>
       <c r="L31" t="n">
-        <v>59.3</v>
+        <v>58.12</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>38.82</v>
+        <v>40.29</v>
       </c>
       <c r="K32" t="n">
-        <v>-34.94</v>
+        <v>-36.26</v>
       </c>
       <c r="L32" t="n">
-        <v>52.23</v>
+        <v>54.21</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>48.85</v>
+        <v>50.09</v>
       </c>
       <c r="K33" t="n">
-        <v>19.21</v>
+        <v>19.7</v>
       </c>
       <c r="L33" t="n">
-        <v>52.49</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-48.82</v>
+        <v>-48.9</v>
       </c>
       <c r="K34" t="n">
-        <v>-40.39</v>
+        <v>-40.45</v>
       </c>
       <c r="L34" t="n">
-        <v>63.36</v>
+        <v>63.46</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.23</v>
+        <v>-11.71</v>
       </c>
       <c r="K35" t="n">
-        <v>70.33</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>71.22</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>79.13</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-19.22</v>
+        <v>-19.42</v>
       </c>
       <c r="L36" t="n">
-        <v>81.43000000000001</v>
+        <v>82.26000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-12.84</v>
+        <v>-12.72</v>
       </c>
       <c r="K37" t="n">
-        <v>-106.51</v>
+        <v>-105.49</v>
       </c>
       <c r="L37" t="n">
-        <v>107.28</v>
+        <v>106.26</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>127.41</v>
+        <v>129.77</v>
       </c>
       <c r="K38" t="n">
-        <v>7.53</v>
+        <v>7.67</v>
       </c>
       <c r="L38" t="n">
-        <v>127.63</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-101.19</v>
+        <v>-102.12</v>
       </c>
       <c r="K39" t="n">
-        <v>-67.06</v>
+        <v>-67.67</v>
       </c>
       <c r="L39" t="n">
-        <v>121.39</v>
+        <v>122.51</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>156.67</v>
+        <v>149.17</v>
       </c>
       <c r="K40" t="n">
-        <v>140.23</v>
+        <v>133.52</v>
       </c>
       <c r="L40" t="n">
-        <v>210.26</v>
+        <v>200.2</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.34</v>
+        <v>-16.05</v>
       </c>
       <c r="K41" t="n">
-        <v>215.46</v>
+        <v>211.7</v>
       </c>
       <c r="L41" t="n">
-        <v>216.08</v>
+        <v>212.31</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>186.96</v>
+        <v>185.31</v>
       </c>
       <c r="K42" t="n">
-        <v>-46.84</v>
+        <v>-46.42</v>
       </c>
       <c r="L42" t="n">
-        <v>192.74</v>
+        <v>191.03</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-112.61</v>
+        <v>-111.82</v>
       </c>
       <c r="K43" t="n">
-        <v>155.09</v>
+        <v>154</v>
       </c>
       <c r="L43" t="n">
-        <v>191.66</v>
+        <v>190.31</v>
       </c>
     </row>
     <row r="44">
@@ -1900,10 +1900,10 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>47.56</v>
+        <v>47.57</v>
       </c>
       <c r="K44" t="n">
-        <v>-21.97</v>
+        <v>-21.98</v>
       </c>
       <c r="L44" t="n">
         <v>52.4</v>
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-62.67</v>
+        <v>-61.36</v>
       </c>
       <c r="K45" t="n">
-        <v>-16.37</v>
+        <v>-16.03</v>
       </c>
       <c r="L45" t="n">
-        <v>64.77</v>
+        <v>63.42</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>15.51</v>
+        <v>17.01</v>
       </c>
       <c r="K46" t="n">
-        <v>24.85</v>
+        <v>27.25</v>
       </c>
       <c r="L46" t="n">
-        <v>29.29</v>
+        <v>32.12</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-87.45999999999999</v>
+        <v>-85.13</v>
       </c>
       <c r="K47" t="n">
-        <v>27.03</v>
+        <v>26.31</v>
       </c>
       <c r="L47" t="n">
-        <v>91.54000000000001</v>
+        <v>89.11</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>40.81</v>
+        <v>39.91</v>
       </c>
       <c r="K48" t="n">
-        <v>72.56</v>
+        <v>70.95</v>
       </c>
       <c r="L48" t="n">
-        <v>83.25</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>22.22</v>
+        <v>23.83</v>
       </c>
       <c r="K49" t="n">
-        <v>36.28</v>
+        <v>38.9</v>
       </c>
       <c r="L49" t="n">
-        <v>42.54</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-32.16</v>
+        <v>-32.27</v>
       </c>
       <c r="K50" t="n">
-        <v>77</v>
+        <v>77.27</v>
       </c>
       <c r="L50" t="n">
-        <v>83.45</v>
+        <v>83.73999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-106.57</v>
+        <v>-104.75</v>
       </c>
       <c r="K51" t="n">
-        <v>-38.3</v>
+        <v>-37.65</v>
       </c>
       <c r="L51" t="n">
-        <v>113.25</v>
+        <v>111.31</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-82.78</v>
+        <v>-77.8</v>
       </c>
       <c r="K52" t="n">
-        <v>-182.58</v>
+        <v>-171.59</v>
       </c>
       <c r="L52" t="n">
-        <v>200.47</v>
+        <v>188.4</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>11.52</v>
+        <v>11.34</v>
       </c>
       <c r="K53" t="n">
-        <v>-8.31</v>
+        <v>-8.18</v>
       </c>
       <c r="L53" t="n">
-        <v>14.21</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-27.69</v>
+        <v>-26.89</v>
       </c>
       <c r="K54" t="n">
-        <v>156.84</v>
+        <v>152.34</v>
       </c>
       <c r="L54" t="n">
-        <v>159.27</v>
+        <v>154.69</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-143.41</v>
+        <v>-138.75</v>
       </c>
       <c r="K55" t="n">
-        <v>108.66</v>
+        <v>105.13</v>
       </c>
       <c r="L55" t="n">
-        <v>179.93</v>
+        <v>174.08</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>101.43</v>
+        <v>111.28</v>
       </c>
       <c r="K56" t="n">
-        <v>18.77</v>
+        <v>20.59</v>
       </c>
       <c r="L56" t="n">
-        <v>103.15</v>
+        <v>113.17</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-169.36</v>
+        <v>-169.45</v>
       </c>
       <c r="K57" t="n">
-        <v>-59.61</v>
+        <v>-59.64</v>
       </c>
       <c r="L57" t="n">
-        <v>179.55</v>
+        <v>179.64</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-144.47</v>
+        <v>-142.81</v>
       </c>
       <c r="K58" t="n">
-        <v>-153.34</v>
+        <v>-151.57</v>
       </c>
       <c r="L58" t="n">
-        <v>210.68</v>
+        <v>208.25</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-51.92</v>
+        <v>-52</v>
       </c>
       <c r="K59" t="n">
-        <v>-21.06</v>
+        <v>-21.1</v>
       </c>
       <c r="L59" t="n">
-        <v>56.03</v>
+        <v>56.12</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>41.89</v>
+        <v>40.99</v>
       </c>
       <c r="K60" t="n">
-        <v>49.25</v>
+        <v>48.18</v>
       </c>
       <c r="L60" t="n">
-        <v>64.65000000000001</v>
+        <v>63.26</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>42.96</v>
+        <v>42.65</v>
       </c>
       <c r="K61" t="n">
-        <v>-19.78</v>
+        <v>-19.64</v>
       </c>
       <c r="L61" t="n">
-        <v>47.29</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>45.08</v>
+        <v>45.39</v>
       </c>
       <c r="K62" t="n">
-        <v>-40.21</v>
+        <v>-40.48</v>
       </c>
       <c r="L62" t="n">
-        <v>60.41</v>
+        <v>60.82</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>4.22</v>
+        <v>4.36</v>
       </c>
       <c r="K63" t="n">
-        <v>52.57</v>
+        <v>54.26</v>
       </c>
       <c r="L63" t="n">
-        <v>52.74</v>
+        <v>54.43</v>
       </c>
     </row>
     <row r="64">
@@ -2740,7 +2740,7 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-62.04</v>
+        <v>-62.03</v>
       </c>
       <c r="K64" t="n">
         <v>10.89</v>
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-36.41</v>
+        <v>-38.89</v>
       </c>
       <c r="K65" t="n">
-        <v>-46.62</v>
+        <v>-49.79</v>
       </c>
       <c r="L65" t="n">
-        <v>59.16</v>
+        <v>63.18</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-44.64</v>
+        <v>-44.69</v>
       </c>
       <c r="K66" t="n">
-        <v>83.83</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>94.98</v>
+        <v>95.09</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-59.77</v>
+        <v>-60.21</v>
       </c>
       <c r="K67" t="n">
-        <v>-61.15</v>
+        <v>-61.61</v>
       </c>
       <c r="L67" t="n">
-        <v>85.51000000000001</v>
+        <v>86.14</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-100.76</v>
+        <v>-103.65</v>
       </c>
       <c r="K68" t="n">
-        <v>51.03</v>
+        <v>52.49</v>
       </c>
       <c r="L68" t="n">
-        <v>112.94</v>
+        <v>116.18</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>95.11</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>158.93</v>
+        <v>152.78</v>
       </c>
       <c r="L69" t="n">
-        <v>185.22</v>
+        <v>178.04</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>96.56999999999999</v>
+        <v>94.88</v>
       </c>
       <c r="K70" t="n">
-        <v>101.11</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>139.82</v>
+        <v>137.37</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-86.01000000000001</v>
+        <v>-84.64</v>
       </c>
       <c r="K71" t="n">
-        <v>-187.25</v>
+        <v>-184.27</v>
       </c>
       <c r="L71" t="n">
-        <v>206.06</v>
+        <v>202.77</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-208.02</v>
+        <v>-201.68</v>
       </c>
       <c r="K72" t="n">
-        <v>66.63</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>218.43</v>
+        <v>211.78</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-199.49</v>
+        <v>-194.92</v>
       </c>
       <c r="K73" t="n">
-        <v>-113.36</v>
+        <v>-110.75</v>
       </c>
       <c r="L73" t="n">
-        <v>229.45</v>
+        <v>224.18</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>16.57</v>
+        <v>17.4</v>
       </c>
       <c r="K74" t="n">
-        <v>-30.87</v>
+        <v>-32.42</v>
       </c>
       <c r="L74" t="n">
-        <v>35.04</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-38.09</v>
+        <v>-40.44</v>
       </c>
       <c r="K75" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="L75" t="n">
-        <v>38.1</v>
+        <v>40.44</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>9.890000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-84.15000000000001</v>
+        <v>-81.26000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>84.73</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>41.86</v>
+        <v>42.87</v>
       </c>
       <c r="K77" t="n">
-        <v>25.97</v>
+        <v>26.6</v>
       </c>
       <c r="L77" t="n">
-        <v>49.26</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-42.55</v>
+        <v>-42.33</v>
       </c>
       <c r="K78" t="n">
-        <v>61.99</v>
+        <v>61.67</v>
       </c>
       <c r="L78" t="n">
-        <v>75.19</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>64.44</v>
+        <v>63.62</v>
       </c>
       <c r="K79" t="n">
-        <v>-52.87</v>
+        <v>-52.2</v>
       </c>
       <c r="L79" t="n">
-        <v>83.34999999999999</v>
+        <v>82.29000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>86.92</v>
+        <v>86.69</v>
       </c>
       <c r="K80" t="n">
-        <v>-66.20999999999999</v>
+        <v>-66.03</v>
       </c>
       <c r="L80" t="n">
-        <v>109.26</v>
+        <v>108.97</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-4.97</v>
+        <v>-5</v>
       </c>
       <c r="K81" t="n">
-        <v>-91.42</v>
+        <v>-91.84999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>91.56</v>
+        <v>91.98</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-80.95999999999999</v>
+        <v>-80.09</v>
       </c>
       <c r="K82" t="n">
-        <v>76.42</v>
+        <v>75.59</v>
       </c>
       <c r="L82" t="n">
-        <v>111.33</v>
+        <v>110.13</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>59.34</v>
+        <v>59.63</v>
       </c>
       <c r="K83" t="n">
-        <v>123.4</v>
+        <v>124.01</v>
       </c>
       <c r="L83" t="n">
-        <v>136.92</v>
+        <v>137.6</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-117.65</v>
+        <v>-115.82</v>
       </c>
       <c r="K84" t="n">
-        <v>78.73999999999999</v>
+        <v>77.52</v>
       </c>
       <c r="L84" t="n">
-        <v>141.57</v>
+        <v>139.37</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-42.4</v>
+        <v>-41.86</v>
       </c>
       <c r="K85" t="n">
-        <v>-137.37</v>
+        <v>-135.63</v>
       </c>
       <c r="L85" t="n">
-        <v>143.76</v>
+        <v>141.94</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>211.13</v>
+        <v>213.65</v>
       </c>
       <c r="K86" t="n">
-        <v>-119.81</v>
+        <v>-121.24</v>
       </c>
       <c r="L86" t="n">
-        <v>242.75</v>
+        <v>245.65</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-40.75</v>
+        <v>-40.49</v>
       </c>
       <c r="K87" t="n">
-        <v>-191.19</v>
+        <v>-189.98</v>
       </c>
       <c r="L87" t="n">
-        <v>195.49</v>
+        <v>194.25</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-186.88</v>
+        <v>-187.28</v>
       </c>
       <c r="K88" t="n">
-        <v>30.18</v>
+        <v>30.25</v>
       </c>
       <c r="L88" t="n">
-        <v>189.3</v>
+        <v>189.71</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-22.xlsx
+++ b/output/2025-04-22.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>23.85</v>
+        <v>22.99</v>
       </c>
       <c r="K14" t="n">
-        <v>-57.49</v>
+        <v>-55.43</v>
       </c>
       <c r="L14" t="n">
-        <v>62.24</v>
+        <v>60.01</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>11.1</v>
+        <v>10.63</v>
       </c>
       <c r="K15" t="n">
-        <v>-63.06</v>
+        <v>-60.4</v>
       </c>
       <c r="L15" t="n">
-        <v>64.03</v>
+        <v>61.33</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>30.1</v>
+        <v>32.79</v>
       </c>
       <c r="K16" t="n">
         <v>0.06</v>
       </c>
       <c r="L16" t="n">
-        <v>30.1</v>
+        <v>32.79</v>
       </c>
     </row>
     <row r="17">
@@ -769,7 +769,7 @@
         <v>21.97</v>
       </c>
       <c r="K17" t="n">
-        <v>62.92</v>
+        <v>62.91</v>
       </c>
       <c r="L17" t="n">
         <v>66.64</v>
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>66.2</v>
+        <v>63.44</v>
       </c>
       <c r="K18" t="n">
-        <v>68.73999999999999</v>
+        <v>65.87</v>
       </c>
       <c r="L18" t="n">
-        <v>95.44</v>
+        <v>91.45</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-43.65</v>
+        <v>-46.34</v>
       </c>
       <c r="K19" t="n">
-        <v>15.8</v>
+        <v>16.78</v>
       </c>
       <c r="L19" t="n">
-        <v>46.42</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>92.11</v>
+        <v>93.33</v>
       </c>
       <c r="K20" t="n">
-        <v>5.59</v>
+        <v>5.66</v>
       </c>
       <c r="L20" t="n">
-        <v>92.28</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>11.86</v>
+        <v>11.5</v>
       </c>
       <c r="K21" t="n">
-        <v>126.69</v>
+        <v>122.88</v>
       </c>
       <c r="L21" t="n">
-        <v>127.25</v>
+        <v>123.41</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-43.43</v>
+        <v>-45.2</v>
       </c>
       <c r="K22" t="n">
-        <v>66.66</v>
+        <v>69.37</v>
       </c>
       <c r="L22" t="n">
-        <v>79.56</v>
+        <v>82.79000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>121.73</v>
+        <v>118.5</v>
       </c>
       <c r="K23" t="n">
-        <v>90.47</v>
+        <v>88.06</v>
       </c>
       <c r="L23" t="n">
-        <v>151.67</v>
+        <v>147.63</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-135.07</v>
+        <v>-133.76</v>
       </c>
       <c r="K24" t="n">
-        <v>8.48</v>
+        <v>8.4</v>
       </c>
       <c r="L24" t="n">
-        <v>135.34</v>
+        <v>134.02</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-126.8</v>
+        <v>-121.24</v>
       </c>
       <c r="K25" t="n">
-        <v>112.43</v>
+        <v>107.5</v>
       </c>
       <c r="L25" t="n">
-        <v>169.46</v>
+        <v>162.03</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-241.39</v>
+        <v>-230.62</v>
       </c>
       <c r="K26" t="n">
-        <v>-106.21</v>
+        <v>-101.47</v>
       </c>
       <c r="L26" t="n">
-        <v>263.73</v>
+        <v>251.96</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>176.74</v>
+        <v>175.08</v>
       </c>
       <c r="K27" t="n">
-        <v>-95.98999999999999</v>
+        <v>-95.09</v>
       </c>
       <c r="L27" t="n">
-        <v>201.13</v>
+        <v>199.24</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-122.41</v>
+        <v>-133.2</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.29</v>
+        <v>-7.93</v>
       </c>
       <c r="L28" t="n">
-        <v>122.62</v>
+        <v>133.44</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="K29" t="n">
-        <v>72.62</v>
+        <v>70.05</v>
       </c>
       <c r="L29" t="n">
-        <v>72.62</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-18.1</v>
+        <v>-17.52</v>
       </c>
       <c r="K30" t="n">
-        <v>-60.92</v>
+        <v>-58.96</v>
       </c>
       <c r="L30" t="n">
-        <v>63.55</v>
+        <v>61.51</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>19.11</v>
+        <v>18.67</v>
       </c>
       <c r="K31" t="n">
-        <v>-54.89</v>
+        <v>-53.62</v>
       </c>
       <c r="L31" t="n">
-        <v>58.12</v>
+        <v>56.78</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>40.29</v>
+        <v>41.97</v>
       </c>
       <c r="K32" t="n">
-        <v>-36.26</v>
+        <v>-37.77</v>
       </c>
       <c r="L32" t="n">
-        <v>54.21</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>50.09</v>
+        <v>51.51</v>
       </c>
       <c r="K33" t="n">
-        <v>19.7</v>
+        <v>20.26</v>
       </c>
       <c r="L33" t="n">
-        <v>53.82</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-48.9</v>
+        <v>-48.99</v>
       </c>
       <c r="K34" t="n">
-        <v>-40.45</v>
+        <v>-40.53</v>
       </c>
       <c r="L34" t="n">
-        <v>63.46</v>
+        <v>63.58</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.71</v>
+        <v>-12.26</v>
       </c>
       <c r="K35" t="n">
-        <v>73.31999999999999</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>74.25</v>
+        <v>77.70999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>79.93000000000001</v>
+        <v>80.86</v>
       </c>
       <c r="K36" t="n">
-        <v>-19.42</v>
+        <v>-19.64</v>
       </c>
       <c r="L36" t="n">
-        <v>82.26000000000001</v>
+        <v>83.20999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-12.72</v>
+        <v>-12.58</v>
       </c>
       <c r="K37" t="n">
-        <v>-105.49</v>
+        <v>-104.33</v>
       </c>
       <c r="L37" t="n">
-        <v>106.26</v>
+        <v>105.09</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>129.77</v>
+        <v>132.47</v>
       </c>
       <c r="K38" t="n">
-        <v>7.67</v>
+        <v>7.83</v>
       </c>
       <c r="L38" t="n">
-        <v>130</v>
+        <v>132.7</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-102.12</v>
+        <v>-103.18</v>
       </c>
       <c r="K39" t="n">
-        <v>-67.67</v>
+        <v>-68.38</v>
       </c>
       <c r="L39" t="n">
-        <v>122.51</v>
+        <v>123.78</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>149.17</v>
+        <v>140.6</v>
       </c>
       <c r="K40" t="n">
-        <v>133.52</v>
+        <v>125.84</v>
       </c>
       <c r="L40" t="n">
-        <v>200.2</v>
+        <v>188.69</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.05</v>
+        <v>-15.73</v>
       </c>
       <c r="K41" t="n">
-        <v>211.7</v>
+        <v>207.41</v>
       </c>
       <c r="L41" t="n">
-        <v>212.31</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>185.31</v>
+        <v>183.42</v>
       </c>
       <c r="K42" t="n">
-        <v>-46.42</v>
+        <v>-45.95</v>
       </c>
       <c r="L42" t="n">
-        <v>191.03</v>
+        <v>189.08</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-111.82</v>
+        <v>-110.92</v>
       </c>
       <c r="K43" t="n">
-        <v>154</v>
+        <v>152.75</v>
       </c>
       <c r="L43" t="n">
-        <v>190.31</v>
+        <v>188.77</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>47.57</v>
+        <v>47.58</v>
       </c>
       <c r="K44" t="n">
         <v>-21.98</v>
       </c>
       <c r="L44" t="n">
-        <v>52.4</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-61.36</v>
+        <v>-59.87</v>
       </c>
       <c r="K45" t="n">
-        <v>-16.03</v>
+        <v>-15.64</v>
       </c>
       <c r="L45" t="n">
-        <v>63.42</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>17.01</v>
+        <v>18.72</v>
       </c>
       <c r="K46" t="n">
-        <v>27.25</v>
+        <v>30</v>
       </c>
       <c r="L46" t="n">
-        <v>32.12</v>
+        <v>35.36</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-85.13</v>
+        <v>-82.47</v>
       </c>
       <c r="K47" t="n">
-        <v>26.31</v>
+        <v>25.48</v>
       </c>
       <c r="L47" t="n">
-        <v>89.11</v>
+        <v>86.31999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>39.91</v>
+        <v>38.87</v>
       </c>
       <c r="K48" t="n">
-        <v>70.95</v>
+        <v>69.11</v>
       </c>
       <c r="L48" t="n">
-        <v>81.40000000000001</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>23.83</v>
+        <v>25.66</v>
       </c>
       <c r="K49" t="n">
-        <v>38.9</v>
+        <v>41.89</v>
       </c>
       <c r="L49" t="n">
-        <v>45.62</v>
+        <v>49.13</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-32.27</v>
+        <v>-32.4</v>
       </c>
       <c r="K50" t="n">
-        <v>77.27</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>83.73999999999999</v>
+        <v>84.06999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-104.75</v>
+        <v>-102.66</v>
       </c>
       <c r="K51" t="n">
-        <v>-37.65</v>
+        <v>-36.9</v>
       </c>
       <c r="L51" t="n">
-        <v>111.31</v>
+        <v>109.09</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-77.8</v>
+        <v>-72.11</v>
       </c>
       <c r="K52" t="n">
-        <v>-171.59</v>
+        <v>-159.04</v>
       </c>
       <c r="L52" t="n">
-        <v>188.4</v>
+        <v>174.62</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>11.34</v>
+        <v>12.07</v>
       </c>
       <c r="K53" t="n">
-        <v>-8.18</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>13.98</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-26.89</v>
+        <v>-25.98</v>
       </c>
       <c r="K54" t="n">
-        <v>152.34</v>
+        <v>147.19</v>
       </c>
       <c r="L54" t="n">
-        <v>154.69</v>
+        <v>149.47</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-138.75</v>
+        <v>-133.42</v>
       </c>
       <c r="K55" t="n">
-        <v>105.13</v>
+        <v>101.09</v>
       </c>
       <c r="L55" t="n">
-        <v>174.08</v>
+        <v>167.39</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>111.28</v>
+        <v>122.54</v>
       </c>
       <c r="K56" t="n">
-        <v>20.59</v>
+        <v>22.68</v>
       </c>
       <c r="L56" t="n">
-        <v>113.17</v>
+        <v>124.62</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-169.45</v>
+        <v>-169.54</v>
       </c>
       <c r="K57" t="n">
-        <v>-59.64</v>
+        <v>-59.67</v>
       </c>
       <c r="L57" t="n">
-        <v>179.64</v>
+        <v>179.74</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-142.81</v>
+        <v>-140.91</v>
       </c>
       <c r="K58" t="n">
-        <v>-151.57</v>
+        <v>-149.56</v>
       </c>
       <c r="L58" t="n">
-        <v>208.25</v>
+        <v>205.48</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-52</v>
+        <v>-52.1</v>
       </c>
       <c r="K59" t="n">
-        <v>-21.1</v>
+        <v>-21.14</v>
       </c>
       <c r="L59" t="n">
-        <v>56.12</v>
+        <v>56.22</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>40.99</v>
+        <v>39.95</v>
       </c>
       <c r="K60" t="n">
-        <v>48.18</v>
+        <v>46.97</v>
       </c>
       <c r="L60" t="n">
-        <v>63.26</v>
+        <v>61.66</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>42.65</v>
+        <v>42.29</v>
       </c>
       <c r="K61" t="n">
-        <v>-19.64</v>
+        <v>-19.48</v>
       </c>
       <c r="L61" t="n">
-        <v>46.95</v>
+        <v>46.56</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>45.39</v>
+        <v>45.73</v>
       </c>
       <c r="K62" t="n">
-        <v>-40.48</v>
+        <v>-40.79</v>
       </c>
       <c r="L62" t="n">
-        <v>60.82</v>
+        <v>61.28</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>4.36</v>
+        <v>4.52</v>
       </c>
       <c r="K63" t="n">
-        <v>54.26</v>
+        <v>56.19</v>
       </c>
       <c r="L63" t="n">
-        <v>54.43</v>
+        <v>56.37</v>
       </c>
     </row>
     <row r="64">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-38.89</v>
+        <v>-41.73</v>
       </c>
       <c r="K65" t="n">
-        <v>-49.79</v>
+        <v>-53.42</v>
       </c>
       <c r="L65" t="n">
-        <v>63.18</v>
+        <v>67.79000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-44.69</v>
+        <v>-44.75</v>
       </c>
       <c r="K66" t="n">
-        <v>83.93000000000001</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>95.09</v>
+        <v>95.20999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-60.21</v>
+        <v>-60.72</v>
       </c>
       <c r="K67" t="n">
-        <v>-61.61</v>
+        <v>-62.12</v>
       </c>
       <c r="L67" t="n">
-        <v>86.14</v>
+        <v>86.87</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-103.65</v>
+        <v>-106.95</v>
       </c>
       <c r="K68" t="n">
-        <v>52.49</v>
+        <v>54.16</v>
       </c>
       <c r="L68" t="n">
-        <v>116.18</v>
+        <v>119.89</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>91.43000000000001</v>
+        <v>87.22</v>
       </c>
       <c r="K69" t="n">
-        <v>152.78</v>
+        <v>145.74</v>
       </c>
       <c r="L69" t="n">
-        <v>178.04</v>
+        <v>169.84</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>94.88</v>
+        <v>92.95</v>
       </c>
       <c r="K70" t="n">
-        <v>99.34999999999999</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>137.37</v>
+        <v>134.58</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-84.64</v>
+        <v>-83.06999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>-184.27</v>
+        <v>-180.86</v>
       </c>
       <c r="L71" t="n">
-        <v>202.77</v>
+        <v>199.02</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-201.68</v>
+        <v>-194.44</v>
       </c>
       <c r="K72" t="n">
-        <v>64.59999999999999</v>
+        <v>62.28</v>
       </c>
       <c r="L72" t="n">
-        <v>211.78</v>
+        <v>204.17</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-194.92</v>
+        <v>-189.68</v>
       </c>
       <c r="K73" t="n">
-        <v>-110.75</v>
+        <v>-107.78</v>
       </c>
       <c r="L73" t="n">
-        <v>224.18</v>
+        <v>218.17</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>17.4</v>
+        <v>18.35</v>
       </c>
       <c r="K74" t="n">
-        <v>-32.42</v>
+        <v>-34.19</v>
       </c>
       <c r="L74" t="n">
-        <v>36.8</v>
+        <v>38.81</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-40.44</v>
+        <v>-43.12</v>
       </c>
       <c r="K75" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="L75" t="n">
-        <v>40.44</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>9.550000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="K76" t="n">
-        <v>-81.26000000000001</v>
+        <v>-77.95999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>81.81999999999999</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>42.87</v>
+        <v>44.02</v>
       </c>
       <c r="K77" t="n">
-        <v>26.6</v>
+        <v>27.31</v>
       </c>
       <c r="L77" t="n">
-        <v>50.45</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-42.33</v>
+        <v>-42.09</v>
       </c>
       <c r="K78" t="n">
-        <v>61.67</v>
+        <v>61.31</v>
       </c>
       <c r="L78" t="n">
-        <v>74.8</v>
+        <v>74.36</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>63.62</v>
+        <v>62.68</v>
       </c>
       <c r="K79" t="n">
-        <v>-52.2</v>
+        <v>-51.43</v>
       </c>
       <c r="L79" t="n">
-        <v>82.29000000000001</v>
+        <v>81.08</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>86.69</v>
+        <v>86.47</v>
       </c>
       <c r="K80" t="n">
-        <v>-66.03</v>
+        <v>-65.87</v>
       </c>
       <c r="L80" t="n">
-        <v>108.97</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-5</v>
+        <v>-5.02</v>
       </c>
       <c r="K81" t="n">
-        <v>-91.84999999999999</v>
+        <v>-92.33</v>
       </c>
       <c r="L81" t="n">
-        <v>91.98</v>
+        <v>92.47</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-80.09</v>
+        <v>-79.09</v>
       </c>
       <c r="K82" t="n">
-        <v>75.59</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>110.13</v>
+        <v>108.75</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>59.63</v>
+        <v>59.96</v>
       </c>
       <c r="K83" t="n">
-        <v>124.01</v>
+        <v>124.7</v>
       </c>
       <c r="L83" t="n">
-        <v>137.6</v>
+        <v>138.37</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-115.82</v>
+        <v>-113.73</v>
       </c>
       <c r="K84" t="n">
-        <v>77.52</v>
+        <v>76.12</v>
       </c>
       <c r="L84" t="n">
-        <v>139.37</v>
+        <v>136.85</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-41.86</v>
+        <v>-41.25</v>
       </c>
       <c r="K85" t="n">
-        <v>-135.63</v>
+        <v>-133.64</v>
       </c>
       <c r="L85" t="n">
-        <v>141.94</v>
+        <v>139.86</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>213.65</v>
+        <v>209.88</v>
       </c>
       <c r="K86" t="n">
-        <v>-121.24</v>
+        <v>-119.1</v>
       </c>
       <c r="L86" t="n">
-        <v>245.65</v>
+        <v>241.32</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-40.49</v>
+        <v>-40.2</v>
       </c>
       <c r="K87" t="n">
-        <v>-189.98</v>
+        <v>-188.6</v>
       </c>
       <c r="L87" t="n">
-        <v>194.25</v>
+        <v>192.84</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-187.28</v>
+        <v>-187.74</v>
       </c>
       <c r="K88" t="n">
-        <v>30.25</v>
+        <v>30.32</v>
       </c>
       <c r="L88" t="n">
-        <v>189.71</v>
+        <v>190.17</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-22.xlsx
+++ b/output/2025-04-22.xlsx
@@ -628,25 +628,25 @@
         <v>2.2</v>
       </c>
       <c r="F14" t="n">
-        <v>7.73</v>
+        <v>8.49</v>
       </c>
       <c r="G14" t="n">
-        <v>337.2</v>
+        <v>337.5</v>
       </c>
       <c r="H14" t="n">
-        <v>38.4</v>
+        <v>37.5</v>
       </c>
       <c r="I14" t="n">
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>22.99</v>
+        <v>27.64</v>
       </c>
       <c r="K14" t="n">
-        <v>-55.43</v>
+        <v>-66.63</v>
       </c>
       <c r="L14" t="n">
-        <v>60.01</v>
+        <v>72.13</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>1.81</v>
       </c>
       <c r="F15" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="G15" t="n">
-        <v>325.9</v>
+        <v>331</v>
       </c>
       <c r="H15" t="n">
-        <v>31.2</v>
+        <v>31.8</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>10.63</v>
+        <v>12.9</v>
       </c>
       <c r="K15" t="n">
-        <v>-60.4</v>
+        <v>-73.73</v>
       </c>
       <c r="L15" t="n">
-        <v>61.33</v>
+        <v>74.84999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>1.8</v>
       </c>
       <c r="F16" t="n">
-        <v>7.42</v>
+        <v>2.97</v>
       </c>
       <c r="G16" t="n">
-        <v>341.3</v>
+        <v>331.3</v>
       </c>
       <c r="H16" t="n">
-        <v>29.3</v>
+        <v>39.5</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>32.79</v>
+        <v>34.73</v>
       </c>
       <c r="K16" t="n">
-        <v>0.06</v>
+        <v>0.84</v>
       </c>
       <c r="L16" t="n">
-        <v>32.79</v>
+        <v>34.74</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>1.85</v>
       </c>
       <c r="F17" t="n">
-        <v>7.24</v>
+        <v>6.35</v>
       </c>
       <c r="G17" t="n">
-        <v>337.5</v>
+        <v>327.7</v>
       </c>
       <c r="H17" t="n">
-        <v>42.6</v>
+        <v>37.6</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>21.97</v>
+        <v>23.92</v>
       </c>
       <c r="K17" t="n">
-        <v>62.91</v>
+        <v>72.33</v>
       </c>
       <c r="L17" t="n">
-        <v>66.64</v>
+        <v>76.19</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>2.4</v>
       </c>
       <c r="F18" t="n">
-        <v>6.94</v>
+        <v>4.83</v>
       </c>
       <c r="G18" t="n">
-        <v>316.1</v>
+        <v>321.8</v>
       </c>
       <c r="H18" t="n">
-        <v>29.4</v>
+        <v>26.9</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>63.44</v>
+        <v>58.9</v>
       </c>
       <c r="K18" t="n">
-        <v>65.87</v>
+        <v>62.89</v>
       </c>
       <c r="L18" t="n">
-        <v>91.45</v>
+        <v>86.16</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>2.32</v>
       </c>
       <c r="F19" t="n">
-        <v>6.59</v>
+        <v>5.57</v>
       </c>
       <c r="G19" t="n">
-        <v>322.8</v>
+        <v>314.6</v>
       </c>
       <c r="H19" t="n">
-        <v>28.2</v>
+        <v>30.3</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-46.34</v>
+        <v>-59.37</v>
       </c>
       <c r="K19" t="n">
-        <v>16.78</v>
+        <v>22.5</v>
       </c>
       <c r="L19" t="n">
-        <v>49.28</v>
+        <v>63.49</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>2.14</v>
       </c>
       <c r="F20" t="n">
-        <v>7.4</v>
+        <v>7.49</v>
       </c>
       <c r="G20" t="n">
-        <v>325.5</v>
+        <v>331</v>
       </c>
       <c r="H20" t="n">
-        <v>36.6</v>
+        <v>31.6</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>93.33</v>
+        <v>106.24</v>
       </c>
       <c r="K20" t="n">
-        <v>5.66</v>
+        <v>14.1</v>
       </c>
       <c r="L20" t="n">
-        <v>93.5</v>
+        <v>107.17</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>2.27</v>
       </c>
       <c r="F21" t="n">
-        <v>7.87</v>
+        <v>7.14</v>
       </c>
       <c r="G21" t="n">
-        <v>314.5</v>
+        <v>340.2</v>
       </c>
       <c r="H21" t="n">
-        <v>36.6</v>
+        <v>26.1</v>
       </c>
       <c r="I21" t="n">
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>11.5</v>
+        <v>12.06</v>
       </c>
       <c r="K21" t="n">
-        <v>122.88</v>
+        <v>141.5</v>
       </c>
       <c r="L21" t="n">
-        <v>123.41</v>
+        <v>142.02</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>2.34</v>
       </c>
       <c r="F22" t="n">
-        <v>7.07</v>
+        <v>6.69</v>
       </c>
       <c r="G22" t="n">
-        <v>340.8</v>
+        <v>324.4</v>
       </c>
       <c r="H22" t="n">
-        <v>33.6</v>
+        <v>39.2</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-45.2</v>
+        <v>-53.38</v>
       </c>
       <c r="K22" t="n">
-        <v>69.37</v>
+        <v>77.75</v>
       </c>
       <c r="L22" t="n">
-        <v>82.79000000000001</v>
+        <v>94.31</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>1.77</v>
       </c>
       <c r="F23" t="n">
-        <v>7.64</v>
+        <v>4.14</v>
       </c>
       <c r="G23" t="n">
-        <v>329.1</v>
+        <v>335.7</v>
       </c>
       <c r="H23" t="n">
-        <v>34.3</v>
+        <v>33.4</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>118.5</v>
+        <v>118.68</v>
       </c>
       <c r="K23" t="n">
-        <v>88.06</v>
+        <v>100.68</v>
       </c>
       <c r="L23" t="n">
-        <v>147.63</v>
+        <v>155.63</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>1.95</v>
       </c>
       <c r="F24" t="n">
-        <v>7.74</v>
+        <v>6.5</v>
       </c>
       <c r="G24" t="n">
-        <v>332.3</v>
+        <v>337.7</v>
       </c>
       <c r="H24" t="n">
-        <v>35.6</v>
+        <v>35</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-133.76</v>
+        <v>-161.29</v>
       </c>
       <c r="K24" t="n">
-        <v>8.4</v>
+        <v>23.59</v>
       </c>
       <c r="L24" t="n">
-        <v>134.02</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>1.99</v>
       </c>
       <c r="F25" t="n">
-        <v>7.89</v>
+        <v>4.55</v>
       </c>
       <c r="G25" t="n">
-        <v>332.4</v>
+        <v>340.8</v>
       </c>
       <c r="H25" t="n">
-        <v>34.5</v>
+        <v>35.1</v>
       </c>
       <c r="I25" t="n">
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-121.24</v>
+        <v>-126.63</v>
       </c>
       <c r="K25" t="n">
-        <v>107.5</v>
+        <v>119.85</v>
       </c>
       <c r="L25" t="n">
-        <v>162.03</v>
+        <v>174.36</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>2.17</v>
       </c>
       <c r="F26" t="n">
-        <v>7.25</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>339.1</v>
+        <v>327.9</v>
       </c>
       <c r="H26" t="n">
-        <v>37.7</v>
+        <v>38.4</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-230.62</v>
+        <v>-301.04</v>
       </c>
       <c r="K26" t="n">
-        <v>-101.47</v>
+        <v>-99.33</v>
       </c>
       <c r="L26" t="n">
-        <v>251.96</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>2.17</v>
       </c>
       <c r="F27" t="n">
-        <v>7.38</v>
+        <v>4.4</v>
       </c>
       <c r="G27" t="n">
-        <v>341.6</v>
+        <v>330.5</v>
       </c>
       <c r="H27" t="n">
-        <v>34.5</v>
+        <v>39.7</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>175.08</v>
+        <v>185.13</v>
       </c>
       <c r="K27" t="n">
-        <v>-95.09</v>
+        <v>-81.34</v>
       </c>
       <c r="L27" t="n">
-        <v>199.24</v>
+        <v>202.21</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>2.51</v>
       </c>
       <c r="F28" t="n">
-        <v>6.86</v>
+        <v>7.83</v>
       </c>
       <c r="G28" t="n">
-        <v>343.4</v>
+        <v>320.1</v>
       </c>
       <c r="H28" t="n">
-        <v>34.7</v>
+        <v>40.5</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-133.2</v>
+        <v>-176.61</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.93</v>
+        <v>47</v>
       </c>
       <c r="L28" t="n">
-        <v>133.44</v>
+        <v>182.76</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>2.8</v>
       </c>
       <c r="F29" t="n">
-        <v>7.6</v>
+        <v>6.07</v>
       </c>
       <c r="G29" t="n">
-        <v>332.8</v>
+        <v>334.8</v>
       </c>
       <c r="H29" t="n">
-        <v>30.6</v>
+        <v>35.2</v>
       </c>
       <c r="I29" t="n">
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="K29" t="n">
-        <v>70.05</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>70.05</v>
+        <v>73.76000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>2.19</v>
       </c>
       <c r="F30" t="n">
-        <v>7.09</v>
+        <v>8.51</v>
       </c>
       <c r="G30" t="n">
-        <v>325.3</v>
+        <v>324.8</v>
       </c>
       <c r="H30" t="n">
-        <v>41.9</v>
+        <v>31.5</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.52</v>
+        <v>-20.03</v>
       </c>
       <c r="K30" t="n">
-        <v>-58.96</v>
+        <v>-66.17</v>
       </c>
       <c r="L30" t="n">
-        <v>61.51</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>2.22</v>
       </c>
       <c r="F31" t="n">
-        <v>6.87</v>
+        <v>6.46</v>
       </c>
       <c r="G31" t="n">
-        <v>333</v>
+        <v>320.4</v>
       </c>
       <c r="H31" t="n">
         <v>35.3</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>18.67</v>
+        <v>19.44</v>
       </c>
       <c r="K31" t="n">
-        <v>-53.62</v>
+        <v>-56.67</v>
       </c>
       <c r="L31" t="n">
-        <v>56.78</v>
+        <v>59.91</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>2.55</v>
       </c>
       <c r="F32" t="n">
-        <v>7.61</v>
+        <v>5.67</v>
       </c>
       <c r="G32" t="n">
-        <v>332.5</v>
+        <v>335.2</v>
       </c>
       <c r="H32" t="n">
-        <v>29.7</v>
+        <v>35.1</v>
       </c>
       <c r="I32" t="n">
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>41.97</v>
+        <v>46.84</v>
       </c>
       <c r="K32" t="n">
-        <v>-37.77</v>
+        <v>-40.49</v>
       </c>
       <c r="L32" t="n">
-        <v>56.47</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>2.23</v>
       </c>
       <c r="F33" t="n">
-        <v>7.26</v>
+        <v>7.21</v>
       </c>
       <c r="G33" t="n">
-        <v>326.9</v>
+        <v>328.1</v>
       </c>
       <c r="H33" t="n">
-        <v>34.6</v>
+        <v>32.3</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>51.51</v>
+        <v>66.55</v>
       </c>
       <c r="K33" t="n">
-        <v>20.26</v>
+        <v>28.67</v>
       </c>
       <c r="L33" t="n">
-        <v>55.35</v>
+        <v>72.47</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>1.66</v>
       </c>
       <c r="F34" t="n">
-        <v>6.99</v>
+        <v>5.02</v>
       </c>
       <c r="G34" t="n">
-        <v>323.4</v>
+        <v>322.7</v>
       </c>
       <c r="H34" t="n">
-        <v>34.1</v>
+        <v>30.6</v>
       </c>
       <c r="I34" t="n">
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-48.99</v>
+        <v>-57.02</v>
       </c>
       <c r="K34" t="n">
-        <v>-40.53</v>
+        <v>-45.55</v>
       </c>
       <c r="L34" t="n">
-        <v>63.58</v>
+        <v>72.98</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>2.62</v>
       </c>
       <c r="F35" t="n">
-        <v>7.05</v>
+        <v>8.51</v>
       </c>
       <c r="G35" t="n">
-        <v>335.5</v>
+        <v>323.9</v>
       </c>
       <c r="H35" t="n">
-        <v>35.2</v>
+        <v>36.6</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.26</v>
+        <v>-21.74</v>
       </c>
       <c r="K35" t="n">
-        <v>76.73999999999999</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>77.70999999999999</v>
+        <v>94.87</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>2.21</v>
       </c>
       <c r="F36" t="n">
-        <v>7.24</v>
+        <v>7.46</v>
       </c>
       <c r="G36" t="n">
-        <v>328.5</v>
+        <v>327.7</v>
       </c>
       <c r="H36" t="n">
-        <v>35.6</v>
+        <v>33.1</v>
       </c>
       <c r="I36" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>80.86</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-19.64</v>
+        <v>-18.52</v>
       </c>
       <c r="L36" t="n">
-        <v>83.20999999999999</v>
+        <v>101.45</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>2.31</v>
       </c>
       <c r="F37" t="n">
-        <v>6.9</v>
+        <v>8.51</v>
       </c>
       <c r="G37" t="n">
-        <v>333.3</v>
+        <v>320.9</v>
       </c>
       <c r="H37" t="n">
-        <v>26.3</v>
+        <v>35.5</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-12.58</v>
+        <v>-19.21</v>
       </c>
       <c r="K37" t="n">
-        <v>-104.33</v>
+        <v>-111.29</v>
       </c>
       <c r="L37" t="n">
-        <v>105.09</v>
+        <v>112.94</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>2.89</v>
       </c>
       <c r="F38" t="n">
-        <v>7.87</v>
+        <v>8.51</v>
       </c>
       <c r="G38" t="n">
-        <v>332.2</v>
+        <v>340.3</v>
       </c>
       <c r="H38" t="n">
-        <v>33.9</v>
+        <v>34.9</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>132.47</v>
+        <v>139.5</v>
       </c>
       <c r="K38" t="n">
-        <v>7.83</v>
+        <v>37.68</v>
       </c>
       <c r="L38" t="n">
-        <v>132.7</v>
+        <v>144.49</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>2.55</v>
       </c>
       <c r="F39" t="n">
-        <v>7.08</v>
+        <v>6.68</v>
       </c>
       <c r="G39" t="n">
-        <v>330.6</v>
+        <v>324.6</v>
       </c>
       <c r="H39" t="n">
-        <v>29.9</v>
+        <v>34.2</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-103.18</v>
+        <v>-132.66</v>
       </c>
       <c r="K39" t="n">
-        <v>-68.38</v>
+        <v>-61.25</v>
       </c>
       <c r="L39" t="n">
-        <v>123.78</v>
+        <v>146.12</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>2.39</v>
       </c>
       <c r="F40" t="n">
-        <v>7.37</v>
+        <v>8.51</v>
       </c>
       <c r="G40" t="n">
-        <v>339.4</v>
+        <v>330.3</v>
       </c>
       <c r="H40" t="n">
-        <v>37.2</v>
+        <v>38.5</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>140.6</v>
+        <v>146.01</v>
       </c>
       <c r="K40" t="n">
-        <v>125.84</v>
+        <v>147.43</v>
       </c>
       <c r="L40" t="n">
-        <v>188.69</v>
+        <v>207.49</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>2.43</v>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>8.51</v>
       </c>
       <c r="G41" t="n">
-        <v>330.6</v>
+        <v>342.9</v>
       </c>
       <c r="H41" t="n">
-        <v>29.5</v>
+        <v>34.1</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.73</v>
+        <v>-24.81</v>
       </c>
       <c r="K41" t="n">
-        <v>207.41</v>
+        <v>268.58</v>
       </c>
       <c r="L41" t="n">
-        <v>208</v>
+        <v>269.72</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>2.35</v>
       </c>
       <c r="F42" t="n">
-        <v>7.65</v>
+        <v>8.1</v>
       </c>
       <c r="G42" t="n">
-        <v>335.2</v>
+        <v>335.8</v>
       </c>
       <c r="H42" t="n">
-        <v>35.8</v>
+        <v>36.5</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>183.42</v>
+        <v>232.38</v>
       </c>
       <c r="K42" t="n">
-        <v>-45.95</v>
+        <v>-22.86</v>
       </c>
       <c r="L42" t="n">
-        <v>189.08</v>
+        <v>233.5</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>2.35</v>
       </c>
       <c r="F43" t="n">
-        <v>7.06</v>
+        <v>7.14</v>
       </c>
       <c r="G43" t="n">
-        <v>323.6</v>
+        <v>324.2</v>
       </c>
       <c r="H43" t="n">
-        <v>29.1</v>
+        <v>30.7</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-110.92</v>
+        <v>-128.1</v>
       </c>
       <c r="K43" t="n">
-        <v>152.75</v>
+        <v>176.86</v>
       </c>
       <c r="L43" t="n">
-        <v>188.77</v>
+        <v>218.38</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>2.23</v>
       </c>
       <c r="F44" t="n">
-        <v>7.44</v>
+        <v>4.9</v>
       </c>
       <c r="G44" t="n">
-        <v>328.1</v>
+        <v>331.7</v>
       </c>
       <c r="H44" t="n">
-        <v>29.8</v>
+        <v>32.9</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>47.58</v>
+        <v>47.36</v>
       </c>
       <c r="K44" t="n">
-        <v>-21.98</v>
+        <v>-21.5</v>
       </c>
       <c r="L44" t="n">
-        <v>52.41</v>
+        <v>52.01</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>2.53</v>
       </c>
       <c r="F45" t="n">
-        <v>7.85</v>
+        <v>8.51</v>
       </c>
       <c r="G45" t="n">
-        <v>334.5</v>
+        <v>339.9</v>
       </c>
       <c r="H45" t="n">
-        <v>28.9</v>
+        <v>36.1</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-59.87</v>
+        <v>-74.95</v>
       </c>
       <c r="K45" t="n">
-        <v>-15.64</v>
+        <v>-18.92</v>
       </c>
       <c r="L45" t="n">
-        <v>61.88</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>2.47</v>
       </c>
       <c r="F46" t="n">
-        <v>7.88</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>313.3</v>
+        <v>340.5</v>
       </c>
       <c r="H46" t="n">
-        <v>35.4</v>
+        <v>25.5</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>18.72</v>
+        <v>22.93</v>
       </c>
       <c r="K46" t="n">
-        <v>30</v>
+        <v>38.72</v>
       </c>
       <c r="L46" t="n">
-        <v>35.36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>2.43</v>
       </c>
       <c r="F47" t="n">
-        <v>7.4</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>334</v>
+        <v>330.8</v>
       </c>
       <c r="H47" t="n">
-        <v>33.5</v>
+        <v>35.8</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-82.47</v>
+        <v>-93.01000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>25.48</v>
+        <v>29.83</v>
       </c>
       <c r="L47" t="n">
-        <v>86.31999999999999</v>
+        <v>97.67</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>2.59</v>
       </c>
       <c r="F48" t="n">
-        <v>7.46</v>
+        <v>8.51</v>
       </c>
       <c r="G48" t="n">
-        <v>330.5</v>
+        <v>332.1</v>
       </c>
       <c r="H48" t="n">
-        <v>38.1</v>
+        <v>34.1</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>38.87</v>
+        <v>47.28</v>
       </c>
       <c r="K48" t="n">
-        <v>69.11</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>79.3</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>2.16</v>
       </c>
       <c r="F49" t="n">
-        <v>7.59</v>
+        <v>6.26</v>
       </c>
       <c r="G49" t="n">
-        <v>320.3</v>
+        <v>334.6</v>
       </c>
       <c r="H49" t="n">
-        <v>30.5</v>
+        <v>29</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>25.66</v>
+        <v>26.92</v>
       </c>
       <c r="K49" t="n">
-        <v>41.89</v>
+        <v>48.57</v>
       </c>
       <c r="L49" t="n">
-        <v>49.13</v>
+        <v>55.53</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>1.98</v>
       </c>
       <c r="F50" t="n">
-        <v>6.82</v>
+        <v>5.77</v>
       </c>
       <c r="G50" t="n">
-        <v>331.3</v>
+        <v>319.2</v>
       </c>
       <c r="H50" t="n">
-        <v>33.1</v>
+        <v>34.5</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-32.4</v>
+        <v>-44.44</v>
       </c>
       <c r="K50" t="n">
-        <v>77.56999999999999</v>
+        <v>99.08</v>
       </c>
       <c r="L50" t="n">
-        <v>84.06999999999999</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>2.4</v>
       </c>
       <c r="F51" t="n">
-        <v>7.33</v>
+        <v>7.46</v>
       </c>
       <c r="G51" t="n">
-        <v>334.9</v>
+        <v>329.5</v>
       </c>
       <c r="H51" t="n">
-        <v>34.3</v>
+        <v>36.3</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-102.66</v>
+        <v>-111.55</v>
       </c>
       <c r="K51" t="n">
-        <v>-36.9</v>
+        <v>-33.55</v>
       </c>
       <c r="L51" t="n">
-        <v>109.09</v>
+        <v>116.49</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>2.54</v>
       </c>
       <c r="F52" t="n">
-        <v>7.77</v>
+        <v>6.67</v>
       </c>
       <c r="G52" t="n">
-        <v>317</v>
+        <v>338.3</v>
       </c>
       <c r="H52" t="n">
-        <v>31.2</v>
+        <v>27.4</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-72.11</v>
+        <v>-76.01000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-159.04</v>
+        <v>-160.45</v>
       </c>
       <c r="L52" t="n">
-        <v>174.62</v>
+        <v>177.54</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>2.12</v>
       </c>
       <c r="F53" t="n">
-        <v>7.4</v>
+        <v>4.61</v>
       </c>
       <c r="G53" t="n">
-        <v>324.4</v>
+        <v>331</v>
       </c>
       <c r="H53" t="n">
-        <v>37.1</v>
+        <v>31</v>
       </c>
       <c r="I53" t="n">
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>12.07</v>
+        <v>1.81</v>
       </c>
       <c r="K53" t="n">
-        <v>-8.710000000000001</v>
+        <v>13.63</v>
       </c>
       <c r="L53" t="n">
-        <v>14.88</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>2.33</v>
       </c>
       <c r="F54" t="n">
-        <v>7.24</v>
+        <v>8.51</v>
       </c>
       <c r="G54" t="n">
-        <v>322.9</v>
+        <v>327.6</v>
       </c>
       <c r="H54" t="n">
-        <v>36.5</v>
+        <v>30.3</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-25.98</v>
+        <v>-38.57</v>
       </c>
       <c r="K54" t="n">
-        <v>147.19</v>
+        <v>189.85</v>
       </c>
       <c r="L54" t="n">
-        <v>149.47</v>
+        <v>193.73</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>3.02</v>
       </c>
       <c r="F55" t="n">
-        <v>7.34</v>
+        <v>8.51</v>
       </c>
       <c r="G55" t="n">
-        <v>344.2</v>
+        <v>317.8</v>
       </c>
       <c r="H55" t="n">
-        <v>27.7</v>
+        <v>36.2</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>-133.42</v>
+        <v>-34.94</v>
       </c>
       <c r="K55" t="n">
-        <v>101.09</v>
+        <v>-192.14</v>
       </c>
       <c r="L55" t="n">
-        <v>167.39</v>
+        <v>195.29</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>1.99</v>
       </c>
       <c r="F56" t="n">
-        <v>7.3</v>
+        <v>3.4</v>
       </c>
       <c r="G56" t="n">
-        <v>336.6</v>
+        <v>331.5</v>
       </c>
       <c r="H56" t="n">
-        <v>34.6</v>
+        <v>39.7</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>122.54</v>
+        <v>-75.23999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>22.68</v>
+        <v>148.04</v>
       </c>
       <c r="L56" t="n">
-        <v>124.62</v>
+        <v>166.06</v>
       </c>
     </row>
     <row r="57">
@@ -2431,28 +2431,28 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="F57" t="n">
-        <v>7.59</v>
+        <v>5.85</v>
       </c>
       <c r="G57" t="n">
-        <v>332.5</v>
+        <v>338.4</v>
       </c>
       <c r="H57" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I57" t="n">
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-169.54</v>
+        <v>36.96</v>
       </c>
       <c r="K57" t="n">
-        <v>-59.67</v>
+        <v>-256.06</v>
       </c>
       <c r="L57" t="n">
-        <v>179.74</v>
+        <v>258.71</v>
       </c>
     </row>
     <row r="58">
@@ -2473,28 +2473,28 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.53</v>
+        <v>2.11</v>
       </c>
       <c r="F58" t="n">
-        <v>6.99</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>328.8</v>
+        <v>351.3</v>
       </c>
       <c r="H58" t="n">
-        <v>44.5</v>
+        <v>30.5</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-140.91</v>
+        <v>-214.9</v>
       </c>
       <c r="K58" t="n">
-        <v>-149.56</v>
+        <v>26.08</v>
       </c>
       <c r="L58" t="n">
-        <v>205.48</v>
+        <v>216.48</v>
       </c>
     </row>
     <row r="59">
@@ -2515,28 +2515,28 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.63</v>
+        <v>2.17</v>
       </c>
       <c r="F59" t="n">
-        <v>6.97</v>
+        <v>8.51</v>
       </c>
       <c r="G59" t="n">
-        <v>334.8</v>
+        <v>341.1</v>
       </c>
       <c r="H59" t="n">
-        <v>39.4</v>
+        <v>36.4</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-52.1</v>
+        <v>-46.94</v>
       </c>
       <c r="K59" t="n">
-        <v>-21.14</v>
+        <v>32.05</v>
       </c>
       <c r="L59" t="n">
-        <v>56.22</v>
+        <v>56.84</v>
       </c>
     </row>
     <row r="60">
@@ -2557,28 +2557,28 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="F60" t="n">
-        <v>7.39</v>
+        <v>6.86</v>
       </c>
       <c r="G60" t="n">
-        <v>323.2</v>
+        <v>316.6</v>
       </c>
       <c r="H60" t="n">
-        <v>27.1</v>
+        <v>33.7</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>39.95</v>
+        <v>-3.17</v>
       </c>
       <c r="K60" t="n">
-        <v>46.97</v>
+        <v>-45.25</v>
       </c>
       <c r="L60" t="n">
-        <v>61.66</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="61">
@@ -2599,28 +2599,28 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.14</v>
+        <v>2.67</v>
       </c>
       <c r="F61" t="n">
-        <v>7.74</v>
+        <v>6.57</v>
       </c>
       <c r="G61" t="n">
-        <v>327.6</v>
+        <v>329.8</v>
       </c>
       <c r="H61" t="n">
-        <v>33.8</v>
+        <v>40.6</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>42.29</v>
+        <v>-10.35</v>
       </c>
       <c r="K61" t="n">
-        <v>-19.48</v>
+        <v>56.62</v>
       </c>
       <c r="L61" t="n">
-        <v>46.56</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="62">
@@ -2641,28 +2641,28 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="F62" t="n">
-        <v>6.64</v>
+        <v>6.55</v>
       </c>
       <c r="G62" t="n">
-        <v>331.8</v>
+        <v>337.2</v>
       </c>
       <c r="H62" t="n">
-        <v>34.7</v>
+        <v>32.4</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>45.73</v>
+        <v>4</v>
       </c>
       <c r="K62" t="n">
-        <v>-40.79</v>
+        <v>-86.61</v>
       </c>
       <c r="L62" t="n">
-        <v>61.28</v>
+        <v>86.70999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2683,28 +2683,28 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.58</v>
+        <v>2.33</v>
       </c>
       <c r="F63" t="n">
-        <v>7.29</v>
+        <v>6.14</v>
       </c>
       <c r="G63" t="n">
-        <v>328.2</v>
+        <v>329.3</v>
       </c>
       <c r="H63" t="n">
-        <v>39.7</v>
+        <v>35.4</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>4.52</v>
+        <v>-50.07</v>
       </c>
       <c r="K63" t="n">
-        <v>56.19</v>
+        <v>-29.82</v>
       </c>
       <c r="L63" t="n">
-        <v>56.37</v>
+        <v>58.28</v>
       </c>
     </row>
     <row r="64">
@@ -2725,28 +2725,28 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.07</v>
+        <v>2.37</v>
       </c>
       <c r="F64" t="n">
-        <v>8.359999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="G64" t="n">
-        <v>335.3</v>
+        <v>337.8</v>
       </c>
       <c r="H64" t="n">
-        <v>34.6</v>
+        <v>28.4</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-62.03</v>
+        <v>21.95</v>
       </c>
       <c r="K64" t="n">
-        <v>10.89</v>
+        <v>101.02</v>
       </c>
       <c r="L64" t="n">
-        <v>62.98</v>
+        <v>103.37</v>
       </c>
     </row>
     <row r="65">
@@ -2767,28 +2767,28 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.51</v>
+        <v>2.31</v>
       </c>
       <c r="F65" t="n">
-        <v>6.85</v>
+        <v>7.97</v>
       </c>
       <c r="G65" t="n">
-        <v>318.6</v>
+        <v>326.6</v>
       </c>
       <c r="H65" t="n">
-        <v>31</v>
+        <v>37.8</v>
       </c>
       <c r="I65" t="n">
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-41.73</v>
+        <v>-105.76</v>
       </c>
       <c r="K65" t="n">
-        <v>-53.42</v>
+        <v>-81.97</v>
       </c>
       <c r="L65" t="n">
-        <v>67.79000000000001</v>
+        <v>133.81</v>
       </c>
     </row>
     <row r="66">
@@ -2809,28 +2809,28 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.4</v>
+        <v>3.09</v>
       </c>
       <c r="F66" t="n">
-        <v>7.11</v>
+        <v>6.93</v>
       </c>
       <c r="G66" t="n">
-        <v>333.6</v>
+        <v>325.1</v>
       </c>
       <c r="H66" t="n">
-        <v>27.5</v>
+        <v>35.6</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-44.75</v>
+        <v>-53.96</v>
       </c>
       <c r="K66" t="n">
-        <v>84.04000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>95.20999999999999</v>
+        <v>111.08</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>2.68</v>
       </c>
       <c r="F67" t="n">
-        <v>7.38</v>
+        <v>8.51</v>
       </c>
       <c r="G67" t="n">
-        <v>342</v>
+        <v>330.6</v>
       </c>
       <c r="H67" t="n">
-        <v>37.3</v>
+        <v>39.9</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-60.72</v>
+        <v>-85.59</v>
       </c>
       <c r="K67" t="n">
-        <v>-62.12</v>
+        <v>-73.17</v>
       </c>
       <c r="L67" t="n">
-        <v>86.87</v>
+        <v>112.6</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>2.96</v>
       </c>
       <c r="F68" t="n">
-        <v>7.06</v>
+        <v>8.51</v>
       </c>
       <c r="G68" t="n">
-        <v>315.7</v>
+        <v>324.1</v>
       </c>
       <c r="H68" t="n">
-        <v>32.6</v>
+        <v>26.7</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-106.95</v>
+        <v>-113.22</v>
       </c>
       <c r="K68" t="n">
-        <v>54.16</v>
+        <v>73.13</v>
       </c>
       <c r="L68" t="n">
-        <v>119.89</v>
+        <v>134.79</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>2.57</v>
       </c>
       <c r="F69" t="n">
-        <v>7.9</v>
+        <v>6.98</v>
       </c>
       <c r="G69" t="n">
-        <v>344.5</v>
+        <v>340.9</v>
       </c>
       <c r="H69" t="n">
-        <v>38.6</v>
+        <v>41.1</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>87.22</v>
+        <v>84.55</v>
       </c>
       <c r="K69" t="n">
-        <v>145.74</v>
+        <v>161.69</v>
       </c>
       <c r="L69" t="n">
-        <v>169.84</v>
+        <v>182.46</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>2.05</v>
       </c>
       <c r="F70" t="n">
-        <v>7.44</v>
+        <v>7.22</v>
       </c>
       <c r="G70" t="n">
-        <v>328.3</v>
+        <v>331.7</v>
       </c>
       <c r="H70" t="n">
-        <v>35.2</v>
+        <v>33</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>92.95</v>
+        <v>96.17</v>
       </c>
       <c r="K70" t="n">
-        <v>97.31999999999999</v>
+        <v>117.83</v>
       </c>
       <c r="L70" t="n">
-        <v>134.58</v>
+        <v>152.09</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>2.1</v>
       </c>
       <c r="F71" t="n">
-        <v>8.029999999999999</v>
+        <v>7.14</v>
       </c>
       <c r="G71" t="n">
-        <v>331.6</v>
+        <v>326</v>
       </c>
       <c r="H71" t="n">
-        <v>39.7</v>
+        <v>23.4</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-83.06999999999999</v>
+        <v>-186.01</v>
       </c>
       <c r="K71" t="n">
-        <v>-180.86</v>
+        <v>150.21</v>
       </c>
       <c r="L71" t="n">
-        <v>199.02</v>
+        <v>239.09</v>
       </c>
     </row>
     <row r="72">
@@ -3061,28 +3061,28 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="F72" t="n">
-        <v>7.34</v>
+        <v>7.43</v>
       </c>
       <c r="G72" t="n">
-        <v>312.2</v>
+        <v>316.4</v>
       </c>
       <c r="H72" t="n">
-        <v>32.2</v>
+        <v>42.4</v>
       </c>
       <c r="I72" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>-194.44</v>
+        <v>216.72</v>
       </c>
       <c r="K72" t="n">
-        <v>62.28</v>
+        <v>33.75</v>
       </c>
       <c r="L72" t="n">
-        <v>204.17</v>
+        <v>219.33</v>
       </c>
     </row>
     <row r="73">
@@ -3103,28 +3103,28 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="F73" t="n">
-        <v>7.88</v>
+        <v>8.51</v>
       </c>
       <c r="G73" t="n">
-        <v>342.5</v>
+        <v>319</v>
       </c>
       <c r="H73" t="n">
-        <v>31.7</v>
+        <v>34.2</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-189.68</v>
+        <v>-304.89</v>
       </c>
       <c r="K73" t="n">
-        <v>-107.78</v>
+        <v>104.81</v>
       </c>
       <c r="L73" t="n">
-        <v>218.17</v>
+        <v>322.41</v>
       </c>
     </row>
     <row r="74">
@@ -3145,28 +3145,28 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.93</v>
+        <v>2.6</v>
       </c>
       <c r="F74" t="n">
-        <v>7.35</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>331.5</v>
+        <v>333.3</v>
       </c>
       <c r="H74" t="n">
-        <v>36.2</v>
+        <v>39.7</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>18.35</v>
+        <v>4.96</v>
       </c>
       <c r="K74" t="n">
-        <v>-34.19</v>
+        <v>78</v>
       </c>
       <c r="L74" t="n">
-        <v>38.81</v>
+        <v>78.16</v>
       </c>
     </row>
     <row r="75">
@@ -3187,28 +3187,28 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="F75" t="n">
-        <v>7.59</v>
+        <v>8.51</v>
       </c>
       <c r="G75" t="n">
-        <v>330.5</v>
+        <v>326.8</v>
       </c>
       <c r="H75" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-43.12</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>0.41</v>
+        <v>41.36</v>
       </c>
       <c r="L75" t="n">
-        <v>43.13</v>
+        <v>86.29000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3229,28 +3229,28 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.85</v>
+        <v>2.39</v>
       </c>
       <c r="F76" t="n">
-        <v>7.4</v>
+        <v>8.01</v>
       </c>
       <c r="G76" t="n">
-        <v>337.9</v>
+        <v>332.9</v>
       </c>
       <c r="H76" t="n">
-        <v>32.7</v>
+        <v>35.7</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>9.16</v>
+        <v>-93.08</v>
       </c>
       <c r="K76" t="n">
-        <v>-77.95999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="L76" t="n">
-        <v>78.5</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3271,28 +3271,28 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="F77" t="n">
-        <v>7.77</v>
+        <v>6.14</v>
       </c>
       <c r="G77" t="n">
-        <v>324.3</v>
+        <v>337.1</v>
       </c>
       <c r="H77" t="n">
-        <v>27.7</v>
+        <v>35.7</v>
       </c>
       <c r="I77" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>44.02</v>
+        <v>-58.24</v>
       </c>
       <c r="K77" t="n">
-        <v>27.31</v>
+        <v>51.33</v>
       </c>
       <c r="L77" t="n">
-        <v>51.8</v>
+        <v>77.64</v>
       </c>
     </row>
     <row r="78">
@@ -3313,28 +3313,28 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.28</v>
+        <v>2.64</v>
       </c>
       <c r="F78" t="n">
-        <v>7.42</v>
+        <v>8.51</v>
       </c>
       <c r="G78" t="n">
-        <v>330</v>
+        <v>324.9</v>
       </c>
       <c r="H78" t="n">
-        <v>36.6</v>
+        <v>37.5</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>-42.09</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>61.31</v>
+        <v>7.26</v>
       </c>
       <c r="L78" t="n">
-        <v>74.36</v>
+        <v>68.45</v>
       </c>
     </row>
     <row r="79">
@@ -3355,28 +3355,28 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.64</v>
+        <v>2.87</v>
       </c>
       <c r="F79" t="n">
-        <v>7.13</v>
+        <v>8.51</v>
       </c>
       <c r="G79" t="n">
-        <v>327.2</v>
+        <v>340.4</v>
       </c>
       <c r="H79" t="n">
-        <v>29.1</v>
+        <v>35.7</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>62.68</v>
+        <v>128.37</v>
       </c>
       <c r="K79" t="n">
-        <v>-51.43</v>
+        <v>-23.28</v>
       </c>
       <c r="L79" t="n">
-        <v>81.08</v>
+        <v>130.47</v>
       </c>
     </row>
     <row r="80">
@@ -3397,28 +3397,28 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="F80" t="n">
-        <v>7.42</v>
+        <v>8.51</v>
       </c>
       <c r="G80" t="n">
-        <v>330.9</v>
+        <v>339.4</v>
       </c>
       <c r="H80" t="n">
-        <v>35.7</v>
+        <v>31.1</v>
       </c>
       <c r="I80" t="n">
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>86.47</v>
+        <v>-127.82</v>
       </c>
       <c r="K80" t="n">
-        <v>-65.87</v>
+        <v>-68.14</v>
       </c>
       <c r="L80" t="n">
-        <v>108.7</v>
+        <v>144.85</v>
       </c>
     </row>
     <row r="81">
@@ -3439,28 +3439,28 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.09</v>
+        <v>2.85</v>
       </c>
       <c r="F81" t="n">
-        <v>7.73</v>
+        <v>5.75</v>
       </c>
       <c r="G81" t="n">
-        <v>314.8</v>
+        <v>330.7</v>
       </c>
       <c r="H81" t="n">
-        <v>39.3</v>
+        <v>26.4</v>
       </c>
       <c r="I81" t="n">
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-5.02</v>
+        <v>75.56</v>
       </c>
       <c r="K81" t="n">
-        <v>-92.33</v>
+        <v>66.42</v>
       </c>
       <c r="L81" t="n">
-        <v>92.47</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="82">
@@ -3481,28 +3481,28 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="F82" t="n">
-        <v>7.32</v>
+        <v>8.51</v>
       </c>
       <c r="G82" t="n">
-        <v>328.5</v>
+        <v>322.7</v>
       </c>
       <c r="H82" t="n">
-        <v>38.2</v>
+        <v>28.3</v>
       </c>
       <c r="I82" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-79.09</v>
+        <v>62.24</v>
       </c>
       <c r="K82" t="n">
-        <v>74.65000000000001</v>
+        <v>56.18</v>
       </c>
       <c r="L82" t="n">
-        <v>108.75</v>
+        <v>83.84999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -3523,28 +3523,28 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="F83" t="n">
-        <v>6.93</v>
+        <v>8.51</v>
       </c>
       <c r="G83" t="n">
-        <v>336.7</v>
+        <v>335.3</v>
       </c>
       <c r="H83" t="n">
-        <v>29.1</v>
+        <v>40.2</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>59.96</v>
+        <v>-73.81999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>124.7</v>
+        <v>219.29</v>
       </c>
       <c r="L83" t="n">
-        <v>138.37</v>
+        <v>231.39</v>
       </c>
     </row>
     <row r="84">
@@ -3565,28 +3565,28 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="F84" t="n">
-        <v>7.87</v>
+        <v>8.51</v>
       </c>
       <c r="G84" t="n">
-        <v>334.3</v>
+        <v>320.8</v>
       </c>
       <c r="H84" t="n">
-        <v>42.3</v>
+        <v>33.1</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-113.73</v>
+        <v>-114</v>
       </c>
       <c r="K84" t="n">
-        <v>76.12</v>
+        <v>158.46</v>
       </c>
       <c r="L84" t="n">
-        <v>136.85</v>
+        <v>195.2</v>
       </c>
     </row>
     <row r="85">
@@ -3607,28 +3607,28 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.31</v>
+        <v>2.77</v>
       </c>
       <c r="F85" t="n">
-        <v>7.8</v>
+        <v>8.51</v>
       </c>
       <c r="G85" t="n">
-        <v>332.3</v>
+        <v>327.7</v>
       </c>
       <c r="H85" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="I85" t="n">
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-41.25</v>
+        <v>119.24</v>
       </c>
       <c r="K85" t="n">
-        <v>-133.64</v>
+        <v>90.48</v>
       </c>
       <c r="L85" t="n">
-        <v>139.86</v>
+        <v>149.68</v>
       </c>
     </row>
     <row r="86">
@@ -3649,10 +3649,10 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.79</v>
+        <v>3.18</v>
       </c>
       <c r="F86" t="n">
-        <v>7.53</v>
+        <v>8.51</v>
       </c>
       <c r="G86" t="n">
         <v>333.3</v>
@@ -3661,16 +3661,16 @@
         <v>33.9</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>209.88</v>
+        <v>113.11</v>
       </c>
       <c r="K86" t="n">
-        <v>-119.1</v>
+        <v>-146.37</v>
       </c>
       <c r="L86" t="n">
-        <v>241.32</v>
+        <v>184.99</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>2.52</v>
       </c>
       <c r="F87" t="n">
-        <v>7.56</v>
+        <v>7.9</v>
       </c>
       <c r="G87" t="n">
-        <v>331.7</v>
+        <v>334.1</v>
       </c>
       <c r="H87" t="n">
-        <v>37.5</v>
+        <v>34.7</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-40.2</v>
+        <v>-71.76000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-188.6</v>
+        <v>-201.81</v>
       </c>
       <c r="L87" t="n">
-        <v>192.84</v>
+        <v>214.19</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>2.47</v>
       </c>
       <c r="F88" t="n">
-        <v>7.48</v>
+        <v>4.3</v>
       </c>
       <c r="G88" t="n">
-        <v>330</v>
+        <v>332.5</v>
       </c>
       <c r="H88" t="n">
-        <v>25.8</v>
+        <v>33.9</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-187.74</v>
+        <v>-193.29</v>
       </c>
       <c r="K88" t="n">
-        <v>30.32</v>
+        <v>61.95</v>
       </c>
       <c r="L88" t="n">
-        <v>190.17</v>
+        <v>202.98</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-22.xlsx
+++ b/output/2025-04-22.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>27.64</v>
+        <v>26.49</v>
       </c>
       <c r="K14" t="n">
-        <v>-66.63</v>
+        <v>-63.85</v>
       </c>
       <c r="L14" t="n">
-        <v>72.13</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="K15" t="n">
-        <v>-73.73</v>
+        <v>-76.56</v>
       </c>
       <c r="L15" t="n">
-        <v>74.84999999999999</v>
+        <v>77.73</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>34.73</v>
+        <v>36.07</v>
       </c>
       <c r="K16" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="L16" t="n">
-        <v>34.74</v>
+        <v>36.08</v>
       </c>
     </row>
     <row r="17">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>58.9</v>
+        <v>56.44</v>
       </c>
       <c r="K18" t="n">
-        <v>62.89</v>
+        <v>60.27</v>
       </c>
       <c r="L18" t="n">
-        <v>86.16</v>
+        <v>82.56999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-59.37</v>
+        <v>-63.76</v>
       </c>
       <c r="K19" t="n">
-        <v>22.5</v>
+        <v>24.17</v>
       </c>
       <c r="L19" t="n">
-        <v>63.49</v>
+        <v>68.19</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>106.24</v>
+        <v>108.32</v>
       </c>
       <c r="K20" t="n">
-        <v>14.1</v>
+        <v>14.38</v>
       </c>
       <c r="L20" t="n">
-        <v>107.17</v>
+        <v>109.27</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>12.06</v>
+        <v>12.95</v>
       </c>
       <c r="K21" t="n">
-        <v>141.5</v>
+        <v>151.99</v>
       </c>
       <c r="L21" t="n">
-        <v>142.02</v>
+        <v>152.54</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-53.38</v>
+        <v>-52.29</v>
       </c>
       <c r="K22" t="n">
-        <v>77.75</v>
+        <v>76.17</v>
       </c>
       <c r="L22" t="n">
-        <v>94.31</v>
+        <v>92.39</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>118.68</v>
+        <v>125.39</v>
       </c>
       <c r="K23" t="n">
-        <v>100.68</v>
+        <v>106.38</v>
       </c>
       <c r="L23" t="n">
-        <v>155.63</v>
+        <v>164.44</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-161.29</v>
+        <v>-173.23</v>
       </c>
       <c r="K24" t="n">
-        <v>23.59</v>
+        <v>25.33</v>
       </c>
       <c r="L24" t="n">
-        <v>163</v>
+        <v>175.08</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-126.63</v>
+        <v>-129.12</v>
       </c>
       <c r="K25" t="n">
-        <v>119.85</v>
+        <v>122.2</v>
       </c>
       <c r="L25" t="n">
-        <v>174.36</v>
+        <v>177.78</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-301.04</v>
+        <v>-323.34</v>
       </c>
       <c r="K26" t="n">
-        <v>-99.33</v>
+        <v>-106.69</v>
       </c>
       <c r="L26" t="n">
-        <v>317</v>
+        <v>340.48</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>185.13</v>
+        <v>195.61</v>
       </c>
       <c r="K27" t="n">
-        <v>-81.34</v>
+        <v>-85.95</v>
       </c>
       <c r="L27" t="n">
-        <v>202.21</v>
+        <v>213.66</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-176.61</v>
+        <v>-183.41</v>
       </c>
       <c r="K28" t="n">
-        <v>47</v>
+        <v>48.8</v>
       </c>
       <c r="L28" t="n">
-        <v>182.76</v>
+        <v>189.79</v>
       </c>
     </row>
     <row r="29">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-20.03</v>
+        <v>-19.62</v>
       </c>
       <c r="K30" t="n">
-        <v>-66.17</v>
+        <v>-64.81999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>69.13</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>19.44</v>
+        <v>18.63</v>
       </c>
       <c r="K31" t="n">
-        <v>-56.67</v>
+        <v>-54.31</v>
       </c>
       <c r="L31" t="n">
-        <v>59.91</v>
+        <v>57.41</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>46.84</v>
+        <v>47.76</v>
       </c>
       <c r="K32" t="n">
-        <v>-40.49</v>
+        <v>-41.28</v>
       </c>
       <c r="L32" t="n">
-        <v>61.91</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>66.55</v>
+        <v>71.48</v>
       </c>
       <c r="K33" t="n">
-        <v>28.67</v>
+        <v>30.79</v>
       </c>
       <c r="L33" t="n">
-        <v>72.47</v>
+        <v>77.83</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-57.02</v>
+        <v>-61.24</v>
       </c>
       <c r="K34" t="n">
-        <v>-45.55</v>
+        <v>-48.92</v>
       </c>
       <c r="L34" t="n">
-        <v>72.98</v>
+        <v>78.38</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-21.74</v>
+        <v>-21.3</v>
       </c>
       <c r="K35" t="n">
-        <v>92.34999999999999</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>94.87</v>
+        <v>92.94</v>
       </c>
     </row>
     <row r="36">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-19.21</v>
+        <v>-18.41</v>
       </c>
       <c r="K37" t="n">
-        <v>-111.29</v>
+        <v>-106.65</v>
       </c>
       <c r="L37" t="n">
-        <v>112.94</v>
+        <v>108.23</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>139.5</v>
+        <v>142.23</v>
       </c>
       <c r="K38" t="n">
-        <v>37.68</v>
+        <v>38.42</v>
       </c>
       <c r="L38" t="n">
-        <v>144.49</v>
+        <v>147.33</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-132.66</v>
+        <v>-140.17</v>
       </c>
       <c r="K39" t="n">
-        <v>-61.25</v>
+        <v>-64.72</v>
       </c>
       <c r="L39" t="n">
-        <v>146.12</v>
+        <v>154.39</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>146.01</v>
+        <v>139.92</v>
       </c>
       <c r="K40" t="n">
-        <v>147.43</v>
+        <v>141.29</v>
       </c>
       <c r="L40" t="n">
-        <v>207.49</v>
+        <v>198.85</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-24.81</v>
+        <v>-26.21</v>
       </c>
       <c r="K41" t="n">
-        <v>268.58</v>
+        <v>283.78</v>
       </c>
       <c r="L41" t="n">
-        <v>269.72</v>
+        <v>284.99</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>232.38</v>
+        <v>249.6</v>
       </c>
       <c r="K42" t="n">
-        <v>-22.86</v>
+        <v>-24.55</v>
       </c>
       <c r="L42" t="n">
-        <v>233.5</v>
+        <v>250.8</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-128.1</v>
+        <v>-122.76</v>
       </c>
       <c r="K43" t="n">
-        <v>176.86</v>
+        <v>169.49</v>
       </c>
       <c r="L43" t="n">
-        <v>218.38</v>
+        <v>209.28</v>
       </c>
     </row>
     <row r="44">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-74.95</v>
+        <v>-80.5</v>
       </c>
       <c r="K45" t="n">
-        <v>-18.92</v>
+        <v>-20.32</v>
       </c>
       <c r="L45" t="n">
-        <v>77.3</v>
+        <v>83.03</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>22.93</v>
+        <v>23.38</v>
       </c>
       <c r="K46" t="n">
-        <v>38.72</v>
+        <v>39.48</v>
       </c>
       <c r="L46" t="n">
-        <v>45</v>
+        <v>45.88</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-93.01000000000001</v>
+        <v>-96.58</v>
       </c>
       <c r="K47" t="n">
-        <v>29.83</v>
+        <v>30.98</v>
       </c>
       <c r="L47" t="n">
-        <v>97.67</v>
+        <v>101.43</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>47.28</v>
+        <v>50.78</v>
       </c>
       <c r="K48" t="n">
-        <v>87.18000000000001</v>
+        <v>93.63</v>
       </c>
       <c r="L48" t="n">
-        <v>99.17</v>
+        <v>106.52</v>
       </c>
     </row>
     <row r="49">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-44.44</v>
+        <v>-46.96</v>
       </c>
       <c r="K50" t="n">
-        <v>99.08</v>
+        <v>104.69</v>
       </c>
       <c r="L50" t="n">
-        <v>108.59</v>
+        <v>114.74</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-111.55</v>
+        <v>-106.9</v>
       </c>
       <c r="K51" t="n">
-        <v>-33.55</v>
+        <v>-32.16</v>
       </c>
       <c r="L51" t="n">
-        <v>116.49</v>
+        <v>111.64</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-76.01000000000001</v>
+        <v>-80.31</v>
       </c>
       <c r="K52" t="n">
-        <v>-160.45</v>
+        <v>-169.53</v>
       </c>
       <c r="L52" t="n">
-        <v>177.54</v>
+        <v>187.59</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="K53" t="n">
-        <v>13.63</v>
+        <v>13.36</v>
       </c>
       <c r="L53" t="n">
-        <v>13.75</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-38.57</v>
+        <v>-40.06</v>
       </c>
       <c r="K54" t="n">
-        <v>189.85</v>
+        <v>197.15</v>
       </c>
       <c r="L54" t="n">
-        <v>193.73</v>
+        <v>201.18</v>
       </c>
     </row>
     <row r="55">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-75.23999999999999</v>
+        <v>-78.13</v>
       </c>
       <c r="K56" t="n">
-        <v>148.04</v>
+        <v>153.73</v>
       </c>
       <c r="L56" t="n">
-        <v>166.06</v>
+        <v>172.45</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>36.96</v>
+        <v>37.68</v>
       </c>
       <c r="K57" t="n">
-        <v>-256.06</v>
+        <v>-261.08</v>
       </c>
       <c r="L57" t="n">
-        <v>258.71</v>
+        <v>263.79</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-214.9</v>
+        <v>-227.06</v>
       </c>
       <c r="K58" t="n">
-        <v>26.08</v>
+        <v>27.56</v>
       </c>
       <c r="L58" t="n">
-        <v>216.48</v>
+        <v>228.73</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-46.94</v>
+        <v>-44.98</v>
       </c>
       <c r="K59" t="n">
-        <v>32.05</v>
+        <v>30.72</v>
       </c>
       <c r="L59" t="n">
-        <v>56.84</v>
+        <v>54.47</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.17</v>
+        <v>-3.29</v>
       </c>
       <c r="K60" t="n">
-        <v>-45.25</v>
+        <v>-46.99</v>
       </c>
       <c r="L60" t="n">
-        <v>45.36</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.35</v>
+        <v>-11.12</v>
       </c>
       <c r="K61" t="n">
-        <v>56.62</v>
+        <v>60.81</v>
       </c>
       <c r="L61" t="n">
-        <v>57.55</v>
+        <v>61.82</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="K62" t="n">
-        <v>-86.61</v>
+        <v>-88.31</v>
       </c>
       <c r="L62" t="n">
-        <v>86.70999999999999</v>
+        <v>88.41</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-50.07</v>
+        <v>-53.78</v>
       </c>
       <c r="K63" t="n">
-        <v>-29.82</v>
+        <v>-32.03</v>
       </c>
       <c r="L63" t="n">
-        <v>58.28</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>21.95</v>
+        <v>21.5</v>
       </c>
       <c r="K64" t="n">
-        <v>101.02</v>
+        <v>98.95</v>
       </c>
       <c r="L64" t="n">
-        <v>103.37</v>
+        <v>101.26</v>
       </c>
     </row>
     <row r="65">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-53.96</v>
+        <v>-55.02</v>
       </c>
       <c r="K66" t="n">
-        <v>97.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="L66" t="n">
-        <v>111.08</v>
+        <v>113.26</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-85.59</v>
+        <v>-90.43000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-73.17</v>
+        <v>-77.31</v>
       </c>
       <c r="L67" t="n">
-        <v>112.6</v>
+        <v>118.97</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-113.22</v>
+        <v>-108.5</v>
       </c>
       <c r="K68" t="n">
-        <v>73.13</v>
+        <v>70.09</v>
       </c>
       <c r="L68" t="n">
-        <v>134.79</v>
+        <v>129.17</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>84.55</v>
+        <v>81.03</v>
       </c>
       <c r="K69" t="n">
-        <v>161.69</v>
+        <v>154.95</v>
       </c>
       <c r="L69" t="n">
-        <v>182.46</v>
+        <v>174.86</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>96.17</v>
+        <v>94.2</v>
       </c>
       <c r="K70" t="n">
-        <v>117.83</v>
+        <v>115.42</v>
       </c>
       <c r="L70" t="n">
-        <v>152.09</v>
+        <v>148.98</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-186.01</v>
+        <v>-182.21</v>
       </c>
       <c r="K71" t="n">
-        <v>150.21</v>
+        <v>147.15</v>
       </c>
       <c r="L71" t="n">
-        <v>239.09</v>
+        <v>234.21</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>216.72</v>
+        <v>225.05</v>
       </c>
       <c r="K72" t="n">
-        <v>33.75</v>
+        <v>35.05</v>
       </c>
       <c r="L72" t="n">
-        <v>219.33</v>
+        <v>227.76</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-304.89</v>
+        <v>-327.48</v>
       </c>
       <c r="K73" t="n">
-        <v>104.81</v>
+        <v>112.57</v>
       </c>
       <c r="L73" t="n">
-        <v>322.41</v>
+        <v>346.29</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="K74" t="n">
-        <v>78</v>
+        <v>74.75</v>
       </c>
       <c r="L74" t="n">
-        <v>78.16</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>75.73999999999999</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>41.36</v>
+        <v>42.95</v>
       </c>
       <c r="L75" t="n">
-        <v>86.29000000000001</v>
+        <v>89.61</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-93.08</v>
+        <v>-91.18000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>7.72</v>
+        <v>7.56</v>
       </c>
       <c r="L76" t="n">
-        <v>93.40000000000001</v>
+        <v>91.48999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-58.24</v>
+        <v>-60.48</v>
       </c>
       <c r="K77" t="n">
-        <v>51.33</v>
+        <v>53.31</v>
       </c>
       <c r="L77" t="n">
-        <v>77.64</v>
+        <v>80.62</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>68.06999999999999</v>
+        <v>71.92</v>
       </c>
       <c r="K78" t="n">
-        <v>7.26</v>
+        <v>7.67</v>
       </c>
       <c r="L78" t="n">
-        <v>68.45</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>128.37</v>
+        <v>125.75</v>
       </c>
       <c r="K79" t="n">
-        <v>-23.28</v>
+        <v>-22.81</v>
       </c>
       <c r="L79" t="n">
-        <v>130.47</v>
+        <v>127.81</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-127.82</v>
+        <v>-130.33</v>
       </c>
       <c r="K80" t="n">
-        <v>-68.14</v>
+        <v>-69.47</v>
       </c>
       <c r="L80" t="n">
-        <v>144.85</v>
+        <v>147.69</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>75.56</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>66.42</v>
+        <v>67.72</v>
       </c>
       <c r="L81" t="n">
-        <v>100.6</v>
+        <v>102.57</v>
       </c>
     </row>
     <row r="82">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-73.81999999999999</v>
+        <v>-76.66</v>
       </c>
       <c r="K83" t="n">
-        <v>219.29</v>
+        <v>227.73</v>
       </c>
       <c r="L83" t="n">
-        <v>231.39</v>
+        <v>240.28</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-114</v>
+        <v>-116.23</v>
       </c>
       <c r="K84" t="n">
-        <v>158.46</v>
+        <v>161.57</v>
       </c>
       <c r="L84" t="n">
-        <v>195.2</v>
+        <v>199.03</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>119.24</v>
+        <v>121.58</v>
       </c>
       <c r="K85" t="n">
-        <v>90.48</v>
+        <v>92.25</v>
       </c>
       <c r="L85" t="n">
-        <v>149.68</v>
+        <v>152.62</v>
       </c>
     </row>
     <row r="86">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-71.76000000000001</v>
+        <v>-73.17</v>
       </c>
       <c r="K87" t="n">
-        <v>-201.81</v>
+        <v>-205.76</v>
       </c>
       <c r="L87" t="n">
-        <v>214.19</v>
+        <v>218.39</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-193.29</v>
+        <v>-200.73</v>
       </c>
       <c r="K88" t="n">
-        <v>61.95</v>
+        <v>64.33</v>
       </c>
       <c r="L88" t="n">
-        <v>202.98</v>
+        <v>210.79</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-22.xlsx
+++ b/output/2025-04-22.xlsx
@@ -628,31 +628,31 @@
         <v>2.2</v>
       </c>
       <c r="F14" t="n">
-        <v>8.49</v>
+        <v>4.04</v>
       </c>
       <c r="G14" t="n">
-        <v>337.5</v>
+        <v>333.8</v>
       </c>
       <c r="H14" t="n">
-        <v>37.5</v>
+        <v>45.3</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>26.49</v>
+        <v>0.14</v>
       </c>
       <c r="K14" t="n">
-        <v>-63.85</v>
+        <v>37.32</v>
       </c>
       <c r="L14" t="n">
-        <v>69.13</v>
+        <v>37.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:52:09</t>
+          <t>05:52:44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.81</v>
+        <v>2.72</v>
       </c>
       <c r="F15" t="n">
-        <v>7.8</v>
+        <v>5.64</v>
       </c>
       <c r="G15" t="n">
-        <v>331</v>
+        <v>333.9</v>
       </c>
       <c r="H15" t="n">
-        <v>31.8</v>
+        <v>30.9</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J15" t="n">
-        <v>13.4</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-76.56</v>
+        <v>52.32</v>
       </c>
       <c r="L15" t="n">
-        <v>77.73</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:54:19</t>
+          <t>05:54:23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="F16" t="n">
-        <v>2.97</v>
+        <v>5.19</v>
       </c>
       <c r="G16" t="n">
-        <v>331.3</v>
+        <v>337.2</v>
       </c>
       <c r="H16" t="n">
-        <v>39.5</v>
+        <v>28.4</v>
       </c>
       <c r="I16" t="n">
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>36.07</v>
+        <v>2.31</v>
       </c>
       <c r="K16" t="n">
-        <v>0.87</v>
+        <v>34.16</v>
       </c>
       <c r="L16" t="n">
-        <v>36.08</v>
+        <v>34.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:58:19</t>
+          <t>05:59:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="F17" t="n">
-        <v>6.35</v>
+        <v>6.39</v>
       </c>
       <c r="G17" t="n">
-        <v>327.7</v>
+        <v>340.3</v>
       </c>
       <c r="H17" t="n">
-        <v>37.6</v>
+        <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>23.92</v>
+        <v>33.82</v>
       </c>
       <c r="K17" t="n">
-        <v>72.33</v>
+        <v>-30.59</v>
       </c>
       <c r="L17" t="n">
-        <v>76.19</v>
+        <v>45.61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:59:30</t>
+          <t>06:01:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="F18" t="n">
-        <v>4.83</v>
+        <v>2.28</v>
       </c>
       <c r="G18" t="n">
-        <v>321.8</v>
+        <v>330.4</v>
       </c>
       <c r="H18" t="n">
-        <v>26.9</v>
+        <v>40.3</v>
       </c>
       <c r="I18" t="n">
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>56.44</v>
+        <v>51.08</v>
       </c>
       <c r="K18" t="n">
-        <v>60.27</v>
+        <v>36.16</v>
       </c>
       <c r="L18" t="n">
-        <v>82.56999999999999</v>
+        <v>62.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:00:45</t>
+          <t>06:03:20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="F19" t="n">
-        <v>5.57</v>
+        <v>6.16</v>
       </c>
       <c r="G19" t="n">
-        <v>314.6</v>
+        <v>330.3</v>
       </c>
       <c r="H19" t="n">
-        <v>30.3</v>
+        <v>84.5</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-63.76</v>
+        <v>44.07</v>
       </c>
       <c r="K19" t="n">
-        <v>24.17</v>
+        <v>45.55</v>
       </c>
       <c r="L19" t="n">
-        <v>68.19</v>
+        <v>63.38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:05:23</t>
+          <t>06:09:29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="F20" t="n">
-        <v>7.49</v>
+        <v>8.51</v>
       </c>
       <c r="G20" t="n">
-        <v>331</v>
+        <v>331.8</v>
       </c>
       <c r="H20" t="n">
-        <v>31.6</v>
+        <v>5.6</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>108.32</v>
+        <v>-49.74</v>
       </c>
       <c r="K20" t="n">
-        <v>14.38</v>
+        <v>68.59</v>
       </c>
       <c r="L20" t="n">
-        <v>109.27</v>
+        <v>84.73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:07:53</t>
+          <t>06:11:09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="F21" t="n">
-        <v>7.14</v>
+        <v>5.85</v>
       </c>
       <c r="G21" t="n">
-        <v>340.2</v>
+        <v>348.5</v>
       </c>
       <c r="H21" t="n">
-        <v>26.1</v>
+        <v>64.3</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>12.95</v>
+        <v>110.53</v>
       </c>
       <c r="K21" t="n">
-        <v>151.99</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>152.54</v>
+        <v>110.86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:10:05</t>
+          <t>06:12:41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="F22" t="n">
-        <v>6.69</v>
+        <v>6.3</v>
       </c>
       <c r="G22" t="n">
-        <v>324.4</v>
+        <v>341.4</v>
       </c>
       <c r="H22" t="n">
-        <v>39.2</v>
+        <v>30</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-52.29</v>
+        <v>-56.54</v>
       </c>
       <c r="K22" t="n">
-        <v>76.17</v>
+        <v>35.17</v>
       </c>
       <c r="L22" t="n">
-        <v>92.39</v>
+        <v>66.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:15:16</t>
+          <t>06:16:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.77</v>
+        <v>2.49</v>
       </c>
       <c r="F23" t="n">
-        <v>4.14</v>
+        <v>7.94</v>
       </c>
       <c r="G23" t="n">
-        <v>335.7</v>
+        <v>325.8</v>
       </c>
       <c r="H23" t="n">
-        <v>33.4</v>
+        <v>22.4</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>125.39</v>
+        <v>-106.64</v>
       </c>
       <c r="K23" t="n">
-        <v>106.38</v>
+        <v>-35.23</v>
       </c>
       <c r="L23" t="n">
-        <v>164.44</v>
+        <v>112.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:17:49</t>
+          <t>06:16:54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="F24" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="G24" t="n">
-        <v>337.7</v>
+        <v>321.8</v>
       </c>
       <c r="H24" t="n">
-        <v>35</v>
+        <v>84.7</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>-173.23</v>
+        <v>120.3</v>
       </c>
       <c r="K24" t="n">
-        <v>25.33</v>
+        <v>-26.49</v>
       </c>
       <c r="L24" t="n">
-        <v>175.08</v>
+        <v>123.18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:18:43</t>
+          <t>06:18:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.99</v>
+        <v>2.34</v>
       </c>
       <c r="F25" t="n">
-        <v>4.55</v>
+        <v>6.74</v>
       </c>
       <c r="G25" t="n">
-        <v>340.8</v>
+        <v>329.5</v>
       </c>
       <c r="H25" t="n">
-        <v>35.1</v>
+        <v>42.8</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-129.12</v>
+        <v>-68.76000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>122.2</v>
+        <v>-69.13</v>
       </c>
       <c r="L25" t="n">
-        <v>177.78</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:22:30</t>
+          <t>06:21:32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="F26" t="n">
-        <v>8.220000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="G26" t="n">
-        <v>327.9</v>
+        <v>328.3</v>
       </c>
       <c r="H26" t="n">
-        <v>38.4</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-323.34</v>
+        <v>-183.2</v>
       </c>
       <c r="K26" t="n">
-        <v>-106.69</v>
+        <v>-80.25</v>
       </c>
       <c r="L26" t="n">
-        <v>340.48</v>
+        <v>200.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:24:34</t>
+          <t>06:23:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="F27" t="n">
-        <v>4.4</v>
+        <v>4.54</v>
       </c>
       <c r="G27" t="n">
-        <v>330.5</v>
+        <v>329.6</v>
       </c>
       <c r="H27" t="n">
-        <v>39.7</v>
+        <v>37.8</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>195.61</v>
+        <v>82.03</v>
       </c>
       <c r="K27" t="n">
-        <v>-85.95</v>
+        <v>185.51</v>
       </c>
       <c r="L27" t="n">
-        <v>213.66</v>
+        <v>202.83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:26:25</t>
+          <t>06:25:18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1216,31 +1216,31 @@
         <v>2.51</v>
       </c>
       <c r="F28" t="n">
-        <v>7.83</v>
+        <v>6.63</v>
       </c>
       <c r="G28" t="n">
-        <v>320.1</v>
+        <v>323.2</v>
       </c>
       <c r="H28" t="n">
-        <v>40.5</v>
+        <v>36.2</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-183.41</v>
+        <v>-230.68</v>
       </c>
       <c r="K28" t="n">
-        <v>48.8</v>
+        <v>-18.29</v>
       </c>
       <c r="L28" t="n">
-        <v>189.79</v>
+        <v>231.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:35:51</t>
+          <t>06:36:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="F29" t="n">
-        <v>6.07</v>
+        <v>7.34</v>
       </c>
       <c r="G29" t="n">
-        <v>334.8</v>
+        <v>330.4</v>
       </c>
       <c r="H29" t="n">
-        <v>35.2</v>
+        <v>82.8</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>0.21</v>
+        <v>-24.57</v>
       </c>
       <c r="K29" t="n">
-        <v>73.76000000000001</v>
+        <v>24.92</v>
       </c>
       <c r="L29" t="n">
-        <v>73.76000000000001</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:38:06</t>
+          <t>06:37:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="F30" t="n">
-        <v>8.51</v>
+        <v>5.12</v>
       </c>
       <c r="G30" t="n">
-        <v>324.8</v>
+        <v>333</v>
       </c>
       <c r="H30" t="n">
-        <v>31.5</v>
+        <v>51</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-19.62</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-64.81999999999999</v>
+        <v>-28.2</v>
       </c>
       <c r="L30" t="n">
-        <v>67.72</v>
+        <v>29.64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:40:13</t>
+          <t>06:39:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="F31" t="n">
-        <v>6.46</v>
+        <v>5.26</v>
       </c>
       <c r="G31" t="n">
-        <v>320.4</v>
+        <v>331.3</v>
       </c>
       <c r="H31" t="n">
-        <v>35.3</v>
+        <v>58.6</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>18.63</v>
+        <v>-23.04</v>
       </c>
       <c r="K31" t="n">
-        <v>-54.31</v>
+        <v>-29.9</v>
       </c>
       <c r="L31" t="n">
-        <v>57.41</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:44:39</t>
+          <t>06:44:29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="F32" t="n">
-        <v>5.67</v>
+        <v>6.57</v>
       </c>
       <c r="G32" t="n">
-        <v>335.2</v>
+        <v>338.5</v>
       </c>
       <c r="H32" t="n">
-        <v>35.1</v>
+        <v>22.1</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>47.76</v>
+        <v>-35.15</v>
       </c>
       <c r="K32" t="n">
-        <v>-41.28</v>
+        <v>23.05</v>
       </c>
       <c r="L32" t="n">
-        <v>63.13</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:46:57</t>
+          <t>06:46:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.23</v>
+        <v>1.74</v>
       </c>
       <c r="F33" t="n">
-        <v>7.21</v>
+        <v>3.25</v>
       </c>
       <c r="G33" t="n">
-        <v>328.1</v>
+        <v>319.1</v>
       </c>
       <c r="H33" t="n">
-        <v>32.3</v>
+        <v>37.8</v>
       </c>
       <c r="I33" t="n">
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>71.48</v>
+        <v>-45.5</v>
       </c>
       <c r="K33" t="n">
-        <v>30.79</v>
+        <v>-35.44</v>
       </c>
       <c r="L33" t="n">
-        <v>77.83</v>
+        <v>57.67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:48:15</t>
+          <t>06:48:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.66</v>
+        <v>2.08</v>
       </c>
       <c r="F34" t="n">
-        <v>5.02</v>
+        <v>5.74</v>
       </c>
       <c r="G34" t="n">
-        <v>322.7</v>
+        <v>331.3</v>
       </c>
       <c r="H34" t="n">
-        <v>30.6</v>
+        <v>34.4</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>-61.24</v>
+        <v>-35.82</v>
       </c>
       <c r="K34" t="n">
-        <v>-48.92</v>
+        <v>37.64</v>
       </c>
       <c r="L34" t="n">
-        <v>78.38</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:52:48</t>
+          <t>06:53:14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="F35" t="n">
-        <v>8.51</v>
+        <v>7.88</v>
       </c>
       <c r="G35" t="n">
-        <v>323.9</v>
+        <v>332.6</v>
       </c>
       <c r="H35" t="n">
-        <v>36.6</v>
+        <v>28.9</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J35" t="n">
-        <v>-21.3</v>
+        <v>-98.12</v>
       </c>
       <c r="K35" t="n">
-        <v>90.45999999999999</v>
+        <v>28.12</v>
       </c>
       <c r="L35" t="n">
-        <v>92.94</v>
+        <v>102.07</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:55:03</t>
+          <t>06:55:45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="F36" t="n">
-        <v>7.46</v>
+        <v>3.54</v>
       </c>
       <c r="G36" t="n">
-        <v>327.7</v>
+        <v>336.8</v>
       </c>
       <c r="H36" t="n">
-        <v>33.1</v>
+        <v>41.5</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>99.73999999999999</v>
+        <v>-60.08</v>
       </c>
       <c r="K36" t="n">
-        <v>-18.52</v>
+        <v>-51.6</v>
       </c>
       <c r="L36" t="n">
-        <v>101.45</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:57:28</t>
+          <t>06:57:19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="F37" t="n">
-        <v>8.51</v>
+        <v>8.09</v>
       </c>
       <c r="G37" t="n">
-        <v>320.9</v>
+        <v>326.7</v>
       </c>
       <c r="H37" t="n">
-        <v>35.5</v>
+        <v>16.7</v>
       </c>
       <c r="I37" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-18.41</v>
+        <v>-58.8</v>
       </c>
       <c r="K37" t="n">
-        <v>-106.65</v>
+        <v>57.7</v>
       </c>
       <c r="L37" t="n">
-        <v>108.23</v>
+        <v>82.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:03:40</t>
+          <t>07:03:05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.89</v>
+        <v>2.31</v>
       </c>
       <c r="F38" t="n">
-        <v>8.51</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>340.3</v>
+        <v>332.5</v>
       </c>
       <c r="H38" t="n">
-        <v>34.9</v>
+        <v>21.5</v>
       </c>
       <c r="I38" t="n">
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>142.23</v>
+        <v>101.16</v>
       </c>
       <c r="K38" t="n">
-        <v>38.42</v>
+        <v>-78.53</v>
       </c>
       <c r="L38" t="n">
-        <v>147.33</v>
+        <v>128.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:04:31</t>
+          <t>07:04:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="F39" t="n">
-        <v>6.68</v>
+        <v>8.51</v>
       </c>
       <c r="G39" t="n">
-        <v>324.6</v>
+        <v>338</v>
       </c>
       <c r="H39" t="n">
-        <v>34.2</v>
+        <v>42.7</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-140.17</v>
+        <v>22.03</v>
       </c>
       <c r="K39" t="n">
-        <v>-64.72</v>
+        <v>-95.43000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>154.39</v>
+        <v>97.94</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:05:40</t>
+          <t>07:06:07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1720,31 +1720,31 @@
         <v>2.39</v>
       </c>
       <c r="F40" t="n">
-        <v>8.51</v>
+        <v>6.93</v>
       </c>
       <c r="G40" t="n">
-        <v>330.3</v>
+        <v>349.4</v>
       </c>
       <c r="H40" t="n">
-        <v>38.5</v>
+        <v>13.5</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>139.92</v>
+        <v>103.69</v>
       </c>
       <c r="K40" t="n">
-        <v>141.29</v>
+        <v>60.61</v>
       </c>
       <c r="L40" t="n">
-        <v>198.85</v>
+        <v>120.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:12:09</t>
+          <t>07:10:38</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="F41" t="n">
-        <v>8.51</v>
+        <v>6.86</v>
       </c>
       <c r="G41" t="n">
-        <v>342.9</v>
+        <v>328.9</v>
       </c>
       <c r="H41" t="n">
-        <v>34.1</v>
+        <v>37.2</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-26.21</v>
+        <v>-109.94</v>
       </c>
       <c r="K41" t="n">
-        <v>283.78</v>
+        <v>-170.3</v>
       </c>
       <c r="L41" t="n">
-        <v>284.99</v>
+        <v>202.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:14:12</t>
+          <t>07:12:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="F42" t="n">
-        <v>8.1</v>
+        <v>5.76</v>
       </c>
       <c r="G42" t="n">
-        <v>335.8</v>
+        <v>324.5</v>
       </c>
       <c r="H42" t="n">
-        <v>36.5</v>
+        <v>19.2</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>249.6</v>
+        <v>115.33</v>
       </c>
       <c r="K42" t="n">
-        <v>-24.55</v>
+        <v>-92.98999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>250.8</v>
+        <v>148.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:15:51</t>
+          <t>07:13:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="F43" t="n">
-        <v>7.14</v>
+        <v>8.08</v>
       </c>
       <c r="G43" t="n">
-        <v>324.2</v>
+        <v>343.1</v>
       </c>
       <c r="H43" t="n">
-        <v>30.7</v>
+        <v>24.8</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J43" t="n">
-        <v>-122.76</v>
+        <v>-171.94</v>
       </c>
       <c r="K43" t="n">
-        <v>169.49</v>
+        <v>39.38</v>
       </c>
       <c r="L43" t="n">
-        <v>209.28</v>
+        <v>176.39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:26:28</t>
+          <t>07:21:23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.23</v>
+        <v>2.56</v>
       </c>
       <c r="F44" t="n">
-        <v>4.9</v>
+        <v>7.34</v>
       </c>
       <c r="G44" t="n">
-        <v>331.7</v>
+        <v>325.7</v>
       </c>
       <c r="H44" t="n">
-        <v>32.9</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>47.36</v>
+        <v>-31.62</v>
       </c>
       <c r="K44" t="n">
-        <v>-21.5</v>
+        <v>28.01</v>
       </c>
       <c r="L44" t="n">
-        <v>52.01</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:28:35</t>
+          <t>07:22:39</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.53</v>
+        <v>2.11</v>
       </c>
       <c r="F45" t="n">
-        <v>8.51</v>
+        <v>5.86</v>
       </c>
       <c r="G45" t="n">
-        <v>339.9</v>
+        <v>330.3</v>
       </c>
       <c r="H45" t="n">
-        <v>36.1</v>
+        <v>40.7</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-80.5</v>
+        <v>-47.78</v>
       </c>
       <c r="K45" t="n">
-        <v>-20.32</v>
+        <v>-1.59</v>
       </c>
       <c r="L45" t="n">
-        <v>83.03</v>
+        <v>47.81</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:30:51</t>
+          <t>07:24:09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="F46" t="n">
-        <v>8.369999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="G46" t="n">
-        <v>340.5</v>
+        <v>341.1</v>
       </c>
       <c r="H46" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>23.38</v>
+        <v>15.77</v>
       </c>
       <c r="K46" t="n">
-        <v>39.48</v>
+        <v>34.76</v>
       </c>
       <c r="L46" t="n">
-        <v>45.88</v>
+        <v>38.17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:35:24</t>
+          <t>07:29:34</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.43</v>
+        <v>2.02</v>
       </c>
       <c r="F47" t="n">
-        <v>8.220000000000001</v>
+        <v>5.01</v>
       </c>
       <c r="G47" t="n">
-        <v>330.8</v>
+        <v>327.5</v>
       </c>
       <c r="H47" t="n">
-        <v>35.8</v>
+        <v>23.6</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-96.58</v>
+        <v>61.58</v>
       </c>
       <c r="K47" t="n">
-        <v>30.98</v>
+        <v>30.56</v>
       </c>
       <c r="L47" t="n">
-        <v>101.43</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:37:03</t>
+          <t>07:32:03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="F48" t="n">
         <v>8.51</v>
       </c>
       <c r="G48" t="n">
-        <v>332.1</v>
+        <v>326</v>
       </c>
       <c r="H48" t="n">
-        <v>34.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>50.78</v>
+        <v>-25.61</v>
       </c>
       <c r="K48" t="n">
-        <v>93.63</v>
+        <v>66</v>
       </c>
       <c r="L48" t="n">
-        <v>106.52</v>
+        <v>70.79000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:39:26</t>
+          <t>07:34:23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="F49" t="n">
-        <v>6.26</v>
+        <v>8.51</v>
       </c>
       <c r="G49" t="n">
-        <v>334.6</v>
+        <v>331</v>
       </c>
       <c r="H49" t="n">
-        <v>29</v>
+        <v>55.8</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>26.92</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>48.57</v>
+        <v>37.83</v>
       </c>
       <c r="L49" t="n">
-        <v>55.53</v>
+        <v>78.26000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:43:45</t>
+          <t>07:39:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="F50" t="n">
-        <v>5.77</v>
+        <v>6.53</v>
       </c>
       <c r="G50" t="n">
-        <v>319.2</v>
+        <v>330.3</v>
       </c>
       <c r="H50" t="n">
-        <v>34.5</v>
+        <v>54.3</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-46.96</v>
+        <v>-6.03</v>
       </c>
       <c r="K50" t="n">
-        <v>104.69</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>114.74</v>
+        <v>82.43000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:45:52</t>
+          <t>07:41:13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="F51" t="n">
-        <v>7.46</v>
+        <v>8.51</v>
       </c>
       <c r="G51" t="n">
-        <v>329.5</v>
+        <v>331</v>
       </c>
       <c r="H51" t="n">
-        <v>36.3</v>
+        <v>83.2</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J51" t="n">
-        <v>-106.9</v>
+        <v>-95.05</v>
       </c>
       <c r="K51" t="n">
-        <v>-32.16</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>111.64</v>
+        <v>130.38</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:47:06</t>
+          <t>07:42:43</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.54</v>
+        <v>2.07</v>
       </c>
       <c r="F52" t="n">
-        <v>6.67</v>
+        <v>6.19</v>
       </c>
       <c r="G52" t="n">
-        <v>338.3</v>
+        <v>342.8</v>
       </c>
       <c r="H52" t="n">
-        <v>27.4</v>
+        <v>10.8</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-80.31</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-169.53</v>
+        <v>-135.6</v>
       </c>
       <c r="L52" t="n">
-        <v>187.59</v>
+        <v>135.93</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:52:05</t>
+          <t>07:47:58</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="F53" t="n">
-        <v>4.61</v>
+        <v>7.35</v>
       </c>
       <c r="G53" t="n">
-        <v>331</v>
+        <v>328.1</v>
       </c>
       <c r="H53" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="I53" t="n">
         <v>31</v>
       </c>
-      <c r="I53" t="n">
-        <v>25</v>
-      </c>
       <c r="J53" t="n">
-        <v>1.77</v>
+        <v>-63.58</v>
       </c>
       <c r="K53" t="n">
-        <v>13.36</v>
+        <v>127.69</v>
       </c>
       <c r="L53" t="n">
-        <v>13.47</v>
+        <v>142.64</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:54:33</t>
+          <t>07:50:15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="F54" t="n">
-        <v>8.51</v>
+        <v>6.88</v>
       </c>
       <c r="G54" t="n">
-        <v>327.6</v>
+        <v>334.3</v>
       </c>
       <c r="H54" t="n">
-        <v>30.3</v>
+        <v>19.3</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>-40.06</v>
+        <v>-40.53</v>
       </c>
       <c r="K54" t="n">
-        <v>197.15</v>
+        <v>181.62</v>
       </c>
       <c r="L54" t="n">
-        <v>201.18</v>
+        <v>186.09</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:56:42</t>
+          <t>07:50:58</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.02</v>
+        <v>2.13</v>
       </c>
       <c r="F55" t="n">
         <v>8.51</v>
       </c>
       <c r="G55" t="n">
-        <v>317.8</v>
+        <v>337.3</v>
       </c>
       <c r="H55" t="n">
-        <v>36.2</v>
+        <v>42.6</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-34.94</v>
+        <v>89.17</v>
       </c>
       <c r="K55" t="n">
-        <v>-192.14</v>
+        <v>41.82</v>
       </c>
       <c r="L55" t="n">
-        <v>195.29</v>
+        <v>98.48999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:00:20</t>
+          <t>07:56:24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="F56" t="n">
-        <v>3.4</v>
+        <v>7.22</v>
       </c>
       <c r="G56" t="n">
-        <v>331.5</v>
+        <v>320.4</v>
       </c>
       <c r="H56" t="n">
-        <v>39.7</v>
+        <v>36.3</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-78.13</v>
+        <v>104.15</v>
       </c>
       <c r="K56" t="n">
-        <v>153.73</v>
+        <v>113.75</v>
       </c>
       <c r="L56" t="n">
-        <v>172.45</v>
+        <v>154.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:02:08</t>
+          <t>07:57:57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="F57" t="n">
-        <v>5.85</v>
+        <v>7.18</v>
       </c>
       <c r="G57" t="n">
-        <v>338.4</v>
+        <v>339.1</v>
       </c>
       <c r="H57" t="n">
-        <v>27</v>
+        <v>40.3</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>37.68</v>
+        <v>164.17</v>
       </c>
       <c r="K57" t="n">
-        <v>-261.08</v>
+        <v>-5.61</v>
       </c>
       <c r="L57" t="n">
-        <v>263.79</v>
+        <v>164.27</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:03:17</t>
+          <t>07:59:14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="F58" t="n">
-        <v>8.119999999999999</v>
+        <v>5.63</v>
       </c>
       <c r="G58" t="n">
-        <v>351.3</v>
+        <v>315</v>
       </c>
       <c r="H58" t="n">
-        <v>30.5</v>
+        <v>49.2</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>-227.06</v>
+        <v>-6.81</v>
       </c>
       <c r="K58" t="n">
-        <v>27.56</v>
+        <v>-195.04</v>
       </c>
       <c r="L58" t="n">
-        <v>228.73</v>
+        <v>195.16</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:14:46</t>
+          <t>08:09:47</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="F59" t="n">
-        <v>8.51</v>
+        <v>4.11</v>
       </c>
       <c r="G59" t="n">
-        <v>341.1</v>
+        <v>345.8</v>
       </c>
       <c r="H59" t="n">
-        <v>36.4</v>
+        <v>39.9</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-44.98</v>
+        <v>1.68</v>
       </c>
       <c r="K59" t="n">
-        <v>30.72</v>
+        <v>-27.31</v>
       </c>
       <c r="L59" t="n">
-        <v>54.47</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:17:11</t>
+          <t>08:11:36</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="F60" t="n">
-        <v>6.86</v>
+        <v>5.13</v>
       </c>
       <c r="G60" t="n">
-        <v>316.6</v>
+        <v>317.7</v>
       </c>
       <c r="H60" t="n">
-        <v>33.7</v>
+        <v>39.3</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.29</v>
+        <v>-31.95</v>
       </c>
       <c r="K60" t="n">
-        <v>-46.99</v>
+        <v>29.63</v>
       </c>
       <c r="L60" t="n">
-        <v>47.11</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:18:43</t>
+          <t>08:12:59</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.67</v>
+        <v>2.48</v>
       </c>
       <c r="F61" t="n">
-        <v>6.57</v>
+        <v>8.51</v>
       </c>
       <c r="G61" t="n">
-        <v>329.8</v>
+        <v>335.7</v>
       </c>
       <c r="H61" t="n">
-        <v>40.6</v>
+        <v>54.1</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.12</v>
+        <v>-16.64</v>
       </c>
       <c r="K61" t="n">
-        <v>60.81</v>
+        <v>23.8</v>
       </c>
       <c r="L61" t="n">
-        <v>61.82</v>
+        <v>29.04</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:23:05</t>
+          <t>08:17:11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.35</v>
+        <v>2.79</v>
       </c>
       <c r="F62" t="n">
-        <v>6.55</v>
+        <v>7.94</v>
       </c>
       <c r="G62" t="n">
-        <v>337.2</v>
+        <v>333.7</v>
       </c>
       <c r="H62" t="n">
-        <v>32.4</v>
+        <v>56.2</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>4.08</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-88.31</v>
+        <v>34.91</v>
       </c>
       <c r="L62" t="n">
-        <v>88.41</v>
+        <v>80.43000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:25:25</t>
+          <t>08:18:38</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="F63" t="n">
-        <v>6.14</v>
+        <v>7.77</v>
       </c>
       <c r="G63" t="n">
-        <v>329.3</v>
+        <v>332.6</v>
       </c>
       <c r="H63" t="n">
-        <v>35.4</v>
+        <v>48.4</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-53.78</v>
+        <v>43.27</v>
       </c>
       <c r="K63" t="n">
-        <v>-32.03</v>
+        <v>-10.02</v>
       </c>
       <c r="L63" t="n">
-        <v>62.6</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:26:46</t>
+          <t>08:19:58</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="F64" t="n">
-        <v>8.51</v>
+        <v>3.44</v>
       </c>
       <c r="G64" t="n">
-        <v>337.8</v>
+        <v>315.7</v>
       </c>
       <c r="H64" t="n">
-        <v>28.4</v>
+        <v>41.1</v>
       </c>
       <c r="I64" t="n">
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>21.5</v>
+        <v>-42.94</v>
       </c>
       <c r="K64" t="n">
-        <v>98.95</v>
+        <v>-13.9</v>
       </c>
       <c r="L64" t="n">
-        <v>101.26</v>
+        <v>45.13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:32:28</t>
+          <t>08:25:35</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="F65" t="n">
-        <v>7.97</v>
+        <v>7.81</v>
       </c>
       <c r="G65" t="n">
-        <v>326.6</v>
+        <v>338.2</v>
       </c>
       <c r="H65" t="n">
-        <v>37.8</v>
+        <v>25.7</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-105.76</v>
+        <v>-15.49</v>
       </c>
       <c r="K65" t="n">
-        <v>-81.97</v>
+        <v>12.44</v>
       </c>
       <c r="L65" t="n">
-        <v>133.81</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:34:21</t>
+          <t>08:27:37</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.09</v>
+        <v>2.3</v>
       </c>
       <c r="F66" t="n">
-        <v>6.93</v>
+        <v>8.51</v>
       </c>
       <c r="G66" t="n">
-        <v>325.1</v>
+        <v>321.5</v>
       </c>
       <c r="H66" t="n">
-        <v>35.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-55.02</v>
+        <v>-0.26</v>
       </c>
       <c r="K66" t="n">
-        <v>99</v>
+        <v>80.8</v>
       </c>
       <c r="L66" t="n">
-        <v>113.26</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:36:22</t>
+          <t>08:29:19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="F67" t="n">
         <v>8.51</v>
       </c>
       <c r="G67" t="n">
-        <v>330.6</v>
+        <v>318.4</v>
       </c>
       <c r="H67" t="n">
-        <v>39.9</v>
+        <v>23.7</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-90.43000000000001</v>
+        <v>-91.02</v>
       </c>
       <c r="K67" t="n">
-        <v>-77.31</v>
+        <v>-31.96</v>
       </c>
       <c r="L67" t="n">
-        <v>118.97</v>
+        <v>96.47</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:41:11</t>
+          <t>08:33:41</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="F68" t="n">
-        <v>8.51</v>
+        <v>7.57</v>
       </c>
       <c r="G68" t="n">
-        <v>324.1</v>
+        <v>324.9</v>
       </c>
       <c r="H68" t="n">
-        <v>26.7</v>
+        <v>56.2</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-108.5</v>
+        <v>-125.16</v>
       </c>
       <c r="K68" t="n">
-        <v>70.09</v>
+        <v>31.21</v>
       </c>
       <c r="L68" t="n">
-        <v>129.17</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:41:57</t>
+          <t>08:35:54</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.57</v>
+        <v>2.31</v>
       </c>
       <c r="F69" t="n">
-        <v>6.98</v>
+        <v>7.95</v>
       </c>
       <c r="G69" t="n">
-        <v>340.9</v>
+        <v>331.2</v>
       </c>
       <c r="H69" t="n">
-        <v>41.1</v>
+        <v>36.1</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>81.03</v>
+        <v>-146.73</v>
       </c>
       <c r="K69" t="n">
-        <v>154.95</v>
+        <v>-50.44</v>
       </c>
       <c r="L69" t="n">
-        <v>174.86</v>
+        <v>155.16</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:44:20</t>
+          <t>08:36:53</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="F70" t="n">
-        <v>7.22</v>
+        <v>8.51</v>
       </c>
       <c r="G70" t="n">
-        <v>331.7</v>
+        <v>337.5</v>
       </c>
       <c r="H70" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>94.2</v>
+        <v>-13.55</v>
       </c>
       <c r="K70" t="n">
-        <v>115.42</v>
+        <v>136.83</v>
       </c>
       <c r="L70" t="n">
-        <v>148.98</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:48:25</t>
+          <t>08:41:02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.1</v>
+        <v>2.79</v>
       </c>
       <c r="F71" t="n">
-        <v>7.14</v>
+        <v>6.85</v>
       </c>
       <c r="G71" t="n">
-        <v>326</v>
+        <v>324.5</v>
       </c>
       <c r="H71" t="n">
-        <v>23.4</v>
+        <v>36.8</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>-182.21</v>
+        <v>-321.13</v>
       </c>
       <c r="K71" t="n">
-        <v>147.15</v>
+        <v>-24.04</v>
       </c>
       <c r="L71" t="n">
-        <v>234.21</v>
+        <v>322.03</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:49:56</t>
+          <t>08:42:25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="F72" t="n">
-        <v>7.43</v>
+        <v>8.51</v>
       </c>
       <c r="G72" t="n">
-        <v>316.4</v>
+        <v>343.4</v>
       </c>
       <c r="H72" t="n">
-        <v>42.4</v>
+        <v>29.8</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>225.05</v>
+        <v>62.27</v>
       </c>
       <c r="K72" t="n">
-        <v>35.05</v>
+        <v>146.16</v>
       </c>
       <c r="L72" t="n">
-        <v>227.76</v>
+        <v>158.87</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:51:15</t>
+          <t>08:44:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.92</v>
+        <v>2.49</v>
       </c>
       <c r="F73" t="n">
         <v>8.51</v>
       </c>
       <c r="G73" t="n">
-        <v>319</v>
+        <v>325.9</v>
       </c>
       <c r="H73" t="n">
-        <v>34.2</v>
+        <v>52.8</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>-327.48</v>
+        <v>-67.34</v>
       </c>
       <c r="K73" t="n">
-        <v>112.57</v>
+        <v>176.05</v>
       </c>
       <c r="L73" t="n">
-        <v>346.29</v>
+        <v>188.49</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:04:22</t>
+          <t>08:56:53</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="F74" t="n">
-        <v>8.449999999999999</v>
+        <v>4.19</v>
       </c>
       <c r="G74" t="n">
-        <v>333.3</v>
+        <v>342.4</v>
       </c>
       <c r="H74" t="n">
-        <v>39.7</v>
+        <v>58.3</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>4.76</v>
+        <v>-35.14</v>
       </c>
       <c r="K74" t="n">
-        <v>74.75</v>
+        <v>-5.88</v>
       </c>
       <c r="L74" t="n">
-        <v>74.90000000000001</v>
+        <v>35.63</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:06:04</t>
+          <t>08:58:02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.64</v>
+        <v>2.27</v>
       </c>
       <c r="F75" t="n">
         <v>8.51</v>
       </c>
       <c r="G75" t="n">
-        <v>326.8</v>
+        <v>312.1</v>
       </c>
       <c r="H75" t="n">
-        <v>32.6</v>
+        <v>63.1</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>78.65000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="K75" t="n">
-        <v>42.95</v>
+        <v>-21.51</v>
       </c>
       <c r="L75" t="n">
-        <v>89.61</v>
+        <v>23.43</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:07:12</t>
+          <t>09:00:09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.39</v>
+        <v>2.64</v>
       </c>
       <c r="F76" t="n">
-        <v>8.01</v>
+        <v>8.51</v>
       </c>
       <c r="G76" t="n">
-        <v>332.9</v>
+        <v>330.6</v>
       </c>
       <c r="H76" t="n">
-        <v>35.7</v>
+        <v>47.3</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-91.18000000000001</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>7.56</v>
+        <v>41.45</v>
       </c>
       <c r="L76" t="n">
-        <v>91.48999999999999</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:11:31</t>
+          <t>09:04:29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="F77" t="n">
-        <v>6.14</v>
+        <v>5.75</v>
       </c>
       <c r="G77" t="n">
-        <v>337.1</v>
+        <v>323.7</v>
       </c>
       <c r="H77" t="n">
-        <v>35.7</v>
+        <v>75.7</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-60.48</v>
+        <v>46.74</v>
       </c>
       <c r="K77" t="n">
-        <v>53.31</v>
+        <v>60.09</v>
       </c>
       <c r="L77" t="n">
-        <v>80.62</v>
+        <v>76.13</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:14:02</t>
+          <t>09:05:59</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="F78" t="n">
-        <v>8.51</v>
+        <v>7.48</v>
       </c>
       <c r="G78" t="n">
-        <v>324.9</v>
+        <v>344.4</v>
       </c>
       <c r="H78" t="n">
-        <v>37.5</v>
+        <v>25.7</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>71.92</v>
+        <v>37.02</v>
       </c>
       <c r="K78" t="n">
-        <v>7.67</v>
+        <v>56.04</v>
       </c>
       <c r="L78" t="n">
-        <v>72.33</v>
+        <v>67.17</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:14:57</t>
+          <t>09:08:02</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="F79" t="n">
-        <v>8.51</v>
+        <v>8.01</v>
       </c>
       <c r="G79" t="n">
-        <v>340.4</v>
+        <v>341.7</v>
       </c>
       <c r="H79" t="n">
-        <v>35.7</v>
+        <v>36.3</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>125.75</v>
+        <v>48.94</v>
       </c>
       <c r="K79" t="n">
-        <v>-22.81</v>
+        <v>7.2</v>
       </c>
       <c r="L79" t="n">
-        <v>127.81</v>
+        <v>49.47</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:18:53</t>
+          <t>09:12:43</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.59</v>
+        <v>2.29</v>
       </c>
       <c r="F80" t="n">
-        <v>8.51</v>
+        <v>7.68</v>
       </c>
       <c r="G80" t="n">
-        <v>339.4</v>
+        <v>320.7</v>
       </c>
       <c r="H80" t="n">
-        <v>31.1</v>
+        <v>34.4</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>-130.33</v>
+        <v>-8.17</v>
       </c>
       <c r="K80" t="n">
-        <v>-69.47</v>
+        <v>96.42</v>
       </c>
       <c r="L80" t="n">
-        <v>147.69</v>
+        <v>96.77</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:21:04</t>
+          <t>09:14:40</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="F81" t="n">
-        <v>5.75</v>
+        <v>8.01</v>
       </c>
       <c r="G81" t="n">
-        <v>330.7</v>
+        <v>315.2</v>
       </c>
       <c r="H81" t="n">
-        <v>26.4</v>
+        <v>44.5</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>77.04000000000001</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>67.72</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>102.57</v>
+        <v>104.73</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:22:49</t>
+          <t>09:16:53</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="F82" t="n">
         <v>8.51</v>
       </c>
       <c r="G82" t="n">
-        <v>322.7</v>
+        <v>342</v>
       </c>
       <c r="H82" t="n">
-        <v>28.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>62.24</v>
+        <v>-64.88</v>
       </c>
       <c r="K82" t="n">
-        <v>56.18</v>
+        <v>-95.55</v>
       </c>
       <c r="L82" t="n">
-        <v>83.84999999999999</v>
+        <v>115.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:27:12</t>
+          <t>09:21:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.82</v>
+        <v>2.01</v>
       </c>
       <c r="F83" t="n">
-        <v>8.51</v>
+        <v>8.06</v>
       </c>
       <c r="G83" t="n">
-        <v>335.3</v>
+        <v>328.5</v>
       </c>
       <c r="H83" t="n">
-        <v>40.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-76.66</v>
+        <v>36.87</v>
       </c>
       <c r="K83" t="n">
-        <v>227.73</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>240.28</v>
+        <v>98.70999999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:28:40</t>
+          <t>09:23:12</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="F84" t="n">
         <v>8.51</v>
       </c>
       <c r="G84" t="n">
-        <v>320.8</v>
+        <v>323.2</v>
       </c>
       <c r="H84" t="n">
-        <v>33.1</v>
+        <v>38.2</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-116.23</v>
+        <v>-36.91</v>
       </c>
       <c r="K84" t="n">
-        <v>161.57</v>
+        <v>132.63</v>
       </c>
       <c r="L84" t="n">
-        <v>199.03</v>
+        <v>137.67</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:29:53</t>
+          <t>09:24:14</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.77</v>
+        <v>2.19</v>
       </c>
       <c r="F85" t="n">
-        <v>8.51</v>
+        <v>6.68</v>
       </c>
       <c r="G85" t="n">
-        <v>327.7</v>
+        <v>339.6</v>
       </c>
       <c r="H85" t="n">
-        <v>35.4</v>
+        <v>55.8</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>121.58</v>
+        <v>106.71</v>
       </c>
       <c r="K85" t="n">
-        <v>92.25</v>
+        <v>-7.4</v>
       </c>
       <c r="L85" t="n">
-        <v>152.62</v>
+        <v>106.97</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:34:23</t>
+          <t>09:29:20</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="F86" t="n">
-        <v>8.51</v>
+        <v>7.93</v>
       </c>
       <c r="G86" t="n">
-        <v>333.3</v>
+        <v>327.6</v>
       </c>
       <c r="H86" t="n">
-        <v>33.9</v>
+        <v>19.8</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>113.11</v>
+        <v>-111.42</v>
       </c>
       <c r="K86" t="n">
-        <v>-146.37</v>
+        <v>-150.42</v>
       </c>
       <c r="L86" t="n">
-        <v>184.99</v>
+        <v>187.19</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:35:21</t>
+          <t>09:30:45</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.52</v>
+        <v>2.77</v>
       </c>
       <c r="F87" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="G87" t="n">
-        <v>334.1</v>
+        <v>341</v>
       </c>
       <c r="H87" t="n">
-        <v>34.7</v>
+        <v>41.2</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-73.17</v>
+        <v>-62.44</v>
       </c>
       <c r="K87" t="n">
-        <v>-205.76</v>
+        <v>-169.32</v>
       </c>
       <c r="L87" t="n">
-        <v>218.39</v>
+        <v>180.47</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:36:32</t>
+          <t>09:32:06</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="F88" t="n">
-        <v>4.3</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>332.5</v>
+        <v>335.9</v>
       </c>
       <c r="H88" t="n">
-        <v>33.9</v>
+        <v>63.4</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-200.73</v>
+        <v>-169.04</v>
       </c>
       <c r="K88" t="n">
-        <v>64.33</v>
+        <v>-107.69</v>
       </c>
       <c r="L88" t="n">
-        <v>210.79</v>
+        <v>200.43</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-22.xlsx
+++ b/output/2025-04-22.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="F14" t="n">
-        <v>4.04</v>
+        <v>8.51</v>
       </c>
       <c r="G14" t="n">
-        <v>333.8</v>
+        <v>350.1</v>
       </c>
       <c r="H14" t="n">
-        <v>45.3</v>
+        <v>27.7</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>0.14</v>
+        <v>-48</v>
       </c>
       <c r="K14" t="n">
-        <v>37.32</v>
+        <v>-15.39</v>
       </c>
       <c r="L14" t="n">
-        <v>37.32</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:52:44</t>
+          <t>05:52:37</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.72</v>
+        <v>2.16</v>
       </c>
       <c r="F15" t="n">
-        <v>5.64</v>
+        <v>4.59</v>
       </c>
       <c r="G15" t="n">
-        <v>333.9</v>
+        <v>328.7</v>
       </c>
       <c r="H15" t="n">
-        <v>30.9</v>
+        <v>40.8</v>
       </c>
       <c r="I15" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.880000000000001</v>
+        <v>-35.32</v>
       </c>
       <c r="K15" t="n">
-        <v>52.32</v>
+        <v>6.95</v>
       </c>
       <c r="L15" t="n">
-        <v>53.07</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:54:23</t>
+          <t>05:54:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="F16" t="n">
-        <v>5.19</v>
+        <v>3.31</v>
       </c>
       <c r="G16" t="n">
-        <v>337.2</v>
+        <v>340.3</v>
       </c>
       <c r="H16" t="n">
-        <v>28.4</v>
+        <v>57.7</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>2.31</v>
+        <v>-53.51</v>
       </c>
       <c r="K16" t="n">
-        <v>34.16</v>
+        <v>22.16</v>
       </c>
       <c r="L16" t="n">
-        <v>34.23</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:59:13</t>
+          <t>05:59:02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="F17" t="n">
-        <v>6.39</v>
+        <v>6.77</v>
       </c>
       <c r="G17" t="n">
-        <v>340.3</v>
+        <v>328.9</v>
       </c>
       <c r="H17" t="n">
-        <v>48.3</v>
+        <v>81.8</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J17" t="n">
-        <v>33.82</v>
+        <v>-47.88</v>
       </c>
       <c r="K17" t="n">
-        <v>-30.59</v>
+        <v>-44.11</v>
       </c>
       <c r="L17" t="n">
-        <v>45.61</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:01:11</t>
+          <t>06:00:37</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="F18" t="n">
-        <v>2.28</v>
+        <v>8.51</v>
       </c>
       <c r="G18" t="n">
-        <v>330.4</v>
+        <v>331.2</v>
       </c>
       <c r="H18" t="n">
-        <v>40.3</v>
+        <v>62.7</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>51.08</v>
+        <v>5.2</v>
       </c>
       <c r="K18" t="n">
-        <v>36.16</v>
+        <v>-65.48</v>
       </c>
       <c r="L18" t="n">
-        <v>62.59</v>
+        <v>65.68000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:03:20</t>
+          <t>06:01:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="F19" t="n">
-        <v>6.16</v>
+        <v>6.88</v>
       </c>
       <c r="G19" t="n">
-        <v>330.3</v>
+        <v>356.4</v>
       </c>
       <c r="H19" t="n">
-        <v>84.5</v>
+        <v>27</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>44.07</v>
+        <v>12.99</v>
       </c>
       <c r="K19" t="n">
-        <v>45.55</v>
+        <v>-65.5</v>
       </c>
       <c r="L19" t="n">
-        <v>63.38</v>
+        <v>66.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:09:29</t>
+          <t>06:06:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="F20" t="n">
         <v>8.51</v>
       </c>
       <c r="G20" t="n">
-        <v>331.8</v>
+        <v>333</v>
       </c>
       <c r="H20" t="n">
-        <v>5.6</v>
+        <v>77.3</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-49.74</v>
+        <v>78.73</v>
       </c>
       <c r="K20" t="n">
-        <v>68.59</v>
+        <v>-81.31</v>
       </c>
       <c r="L20" t="n">
-        <v>84.73</v>
+        <v>113.18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:11:09</t>
+          <t>06:07:37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="F21" t="n">
-        <v>5.85</v>
+        <v>6.12</v>
       </c>
       <c r="G21" t="n">
-        <v>348.5</v>
+        <v>332</v>
       </c>
       <c r="H21" t="n">
-        <v>64.3</v>
+        <v>31.1</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>110.53</v>
+        <v>-63.91</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.609999999999999</v>
+        <v>97.25</v>
       </c>
       <c r="L21" t="n">
-        <v>110.86</v>
+        <v>116.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:12:41</t>
+          <t>06:08:50</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="F22" t="n">
-        <v>6.3</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>341.4</v>
+        <v>335</v>
       </c>
       <c r="H22" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="I22" t="n">
         <v>30</v>
       </c>
-      <c r="I22" t="n">
-        <v>24</v>
-      </c>
       <c r="J22" t="n">
-        <v>-56.54</v>
+        <v>52.83</v>
       </c>
       <c r="K22" t="n">
-        <v>35.17</v>
+        <v>51.52</v>
       </c>
       <c r="L22" t="n">
-        <v>66.58</v>
+        <v>73.79000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:16:03</t>
+          <t>06:13:37</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="F23" t="n">
-        <v>7.94</v>
+        <v>5.97</v>
       </c>
       <c r="G23" t="n">
-        <v>325.8</v>
+        <v>336.3</v>
       </c>
       <c r="H23" t="n">
-        <v>22.4</v>
+        <v>44.5</v>
       </c>
       <c r="I23" t="n">
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-106.64</v>
+        <v>-86.2</v>
       </c>
       <c r="K23" t="n">
-        <v>-35.23</v>
+        <v>149.78</v>
       </c>
       <c r="L23" t="n">
-        <v>112.31</v>
+        <v>172.81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:16:54</t>
+          <t>06:14:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="F24" t="n">
-        <v>4.1</v>
+        <v>7.43</v>
       </c>
       <c r="G24" t="n">
-        <v>321.8</v>
+        <v>334.6</v>
       </c>
       <c r="H24" t="n">
-        <v>84.7</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>120.3</v>
+        <v>55</v>
       </c>
       <c r="K24" t="n">
-        <v>-26.49</v>
+        <v>149.02</v>
       </c>
       <c r="L24" t="n">
-        <v>123.18</v>
+        <v>158.84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:18:09</t>
+          <t>06:16:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="F25" t="n">
-        <v>6.74</v>
+        <v>7.96</v>
       </c>
       <c r="G25" t="n">
-        <v>329.5</v>
+        <v>325.1</v>
       </c>
       <c r="H25" t="n">
-        <v>42.8</v>
+        <v>65.5</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-68.76000000000001</v>
+        <v>-67.20999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-69.13</v>
+        <v>131.59</v>
       </c>
       <c r="L25" t="n">
-        <v>97.5</v>
+        <v>147.76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:21:32</t>
+          <t>06:21:06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="F26" t="n">
-        <v>8.51</v>
+        <v>7.9</v>
       </c>
       <c r="G26" t="n">
-        <v>328.3</v>
+        <v>334.6</v>
       </c>
       <c r="H26" t="n">
-        <v>70.59999999999999</v>
+        <v>46.3</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-183.2</v>
+        <v>88.37</v>
       </c>
       <c r="K26" t="n">
-        <v>-80.25</v>
+        <v>-181.47</v>
       </c>
       <c r="L26" t="n">
-        <v>200.01</v>
+        <v>201.84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:23:36</t>
+          <t>06:23:05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="F27" t="n">
-        <v>4.54</v>
+        <v>8.51</v>
       </c>
       <c r="G27" t="n">
-        <v>329.6</v>
+        <v>329.7</v>
       </c>
       <c r="H27" t="n">
-        <v>37.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>82.03</v>
+        <v>-154.53</v>
       </c>
       <c r="K27" t="n">
-        <v>185.51</v>
+        <v>99.33</v>
       </c>
       <c r="L27" t="n">
-        <v>202.83</v>
+        <v>183.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:25:18</t>
+          <t>06:23:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.51</v>
+        <v>2.23</v>
       </c>
       <c r="F28" t="n">
-        <v>6.63</v>
+        <v>7.96</v>
       </c>
       <c r="G28" t="n">
-        <v>323.2</v>
+        <v>337.9</v>
       </c>
       <c r="H28" t="n">
-        <v>36.2</v>
+        <v>53.9</v>
       </c>
       <c r="I28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-230.68</v>
+        <v>-137.47</v>
       </c>
       <c r="K28" t="n">
-        <v>-18.29</v>
+        <v>50</v>
       </c>
       <c r="L28" t="n">
-        <v>231.4</v>
+        <v>146.28</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:36:48</t>
+          <t>06:33:09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1258,31 +1258,31 @@
         <v>2.26</v>
       </c>
       <c r="F29" t="n">
-        <v>7.34</v>
+        <v>7.16</v>
       </c>
       <c r="G29" t="n">
-        <v>330.4</v>
+        <v>312.1</v>
       </c>
       <c r="H29" t="n">
-        <v>82.8</v>
+        <v>37.9</v>
       </c>
       <c r="I29" t="n">
         <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-24.57</v>
+        <v>-33.44</v>
       </c>
       <c r="K29" t="n">
-        <v>24.92</v>
+        <v>-22.1</v>
       </c>
       <c r="L29" t="n">
-        <v>35</v>
+        <v>40.09</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:37:48</t>
+          <t>06:35:09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="F30" t="n">
-        <v>5.12</v>
+        <v>4.08</v>
       </c>
       <c r="G30" t="n">
-        <v>333</v>
+        <v>340.7</v>
       </c>
       <c r="H30" t="n">
-        <v>51</v>
+        <v>12.5</v>
       </c>
       <c r="I30" t="n">
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>9.130000000000001</v>
+        <v>2.58</v>
       </c>
       <c r="K30" t="n">
-        <v>-28.2</v>
+        <v>33.47</v>
       </c>
       <c r="L30" t="n">
-        <v>29.64</v>
+        <v>33.57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:39:22</t>
+          <t>06:36:15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.84</v>
+        <v>2.29</v>
       </c>
       <c r="F31" t="n">
-        <v>5.26</v>
+        <v>6.33</v>
       </c>
       <c r="G31" t="n">
-        <v>331.3</v>
+        <v>317.5</v>
       </c>
       <c r="H31" t="n">
-        <v>58.6</v>
+        <v>53.1</v>
       </c>
       <c r="I31" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-23.04</v>
+        <v>-5.73</v>
       </c>
       <c r="K31" t="n">
-        <v>-29.9</v>
+        <v>50.05</v>
       </c>
       <c r="L31" t="n">
-        <v>37.75</v>
+        <v>50.38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:44:29</t>
+          <t>06:41:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1384,31 +1384,31 @@
         <v>2.16</v>
       </c>
       <c r="F32" t="n">
-        <v>6.57</v>
+        <v>6.83</v>
       </c>
       <c r="G32" t="n">
-        <v>338.5</v>
+        <v>340.5</v>
       </c>
       <c r="H32" t="n">
-        <v>22.1</v>
+        <v>68</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-35.15</v>
+        <v>58.66</v>
       </c>
       <c r="K32" t="n">
-        <v>23.05</v>
+        <v>9.99</v>
       </c>
       <c r="L32" t="n">
-        <v>42.03</v>
+        <v>59.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:46:01</t>
+          <t>06:42:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.74</v>
+        <v>2.47</v>
       </c>
       <c r="F33" t="n">
-        <v>3.25</v>
+        <v>7.96</v>
       </c>
       <c r="G33" t="n">
-        <v>319.1</v>
+        <v>328.7</v>
       </c>
       <c r="H33" t="n">
-        <v>37.8</v>
+        <v>27.6</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-45.5</v>
+        <v>54.55</v>
       </c>
       <c r="K33" t="n">
-        <v>-35.44</v>
+        <v>34.68</v>
       </c>
       <c r="L33" t="n">
-        <v>57.67</v>
+        <v>64.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:48:23</t>
+          <t>06:43:28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="F34" t="n">
-        <v>5.74</v>
+        <v>2.2</v>
       </c>
       <c r="G34" t="n">
-        <v>331.3</v>
+        <v>328</v>
       </c>
       <c r="H34" t="n">
-        <v>34.4</v>
+        <v>82.7</v>
       </c>
       <c r="I34" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-35.82</v>
+        <v>-31.99</v>
       </c>
       <c r="K34" t="n">
-        <v>37.64</v>
+        <v>-47.52</v>
       </c>
       <c r="L34" t="n">
-        <v>51.95</v>
+        <v>57.29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:53:14</t>
+          <t>06:47:42</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="F35" t="n">
-        <v>7.88</v>
+        <v>8.51</v>
       </c>
       <c r="G35" t="n">
-        <v>332.6</v>
+        <v>326.4</v>
       </c>
       <c r="H35" t="n">
-        <v>28.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>-98.12</v>
+        <v>-66.53</v>
       </c>
       <c r="K35" t="n">
-        <v>28.12</v>
+        <v>56.14</v>
       </c>
       <c r="L35" t="n">
-        <v>102.07</v>
+        <v>87.06</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:55:45</t>
+          <t>06:49:13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>3.54</v>
+        <v>7.25</v>
       </c>
       <c r="G36" t="n">
-        <v>336.8</v>
+        <v>320.6</v>
       </c>
       <c r="H36" t="n">
-        <v>41.5</v>
+        <v>38.5</v>
       </c>
       <c r="I36" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-60.08</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-51.6</v>
+        <v>-33.24</v>
       </c>
       <c r="L36" t="n">
-        <v>79.2</v>
+        <v>89.97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:57:19</t>
+          <t>06:50:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.26</v>
+        <v>2.03</v>
       </c>
       <c r="F37" t="n">
-        <v>8.09</v>
+        <v>8.51</v>
       </c>
       <c r="G37" t="n">
-        <v>326.7</v>
+        <v>327.1</v>
       </c>
       <c r="H37" t="n">
-        <v>16.7</v>
+        <v>20.7</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-58.8</v>
+        <v>-11.23</v>
       </c>
       <c r="K37" t="n">
-        <v>57.7</v>
+        <v>-95.73</v>
       </c>
       <c r="L37" t="n">
-        <v>82.38</v>
+        <v>96.39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:03:05</t>
+          <t>06:54:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="F38" t="n">
-        <v>8.130000000000001</v>
+        <v>4.83</v>
       </c>
       <c r="G38" t="n">
-        <v>332.5</v>
+        <v>329.4</v>
       </c>
       <c r="H38" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>101.16</v>
+        <v>-73.72</v>
       </c>
       <c r="K38" t="n">
-        <v>-78.53</v>
+        <v>-108.82</v>
       </c>
       <c r="L38" t="n">
-        <v>128.06</v>
+        <v>131.44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:04:07</t>
+          <t>06:56:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.87</v>
+        <v>2.44</v>
       </c>
       <c r="F39" t="n">
-        <v>8.51</v>
+        <v>5.95</v>
       </c>
       <c r="G39" t="n">
-        <v>338</v>
+        <v>339.4</v>
       </c>
       <c r="H39" t="n">
-        <v>42.7</v>
+        <v>54</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J39" t="n">
-        <v>22.03</v>
+        <v>122.55</v>
       </c>
       <c r="K39" t="n">
-        <v>-95.43000000000001</v>
+        <v>26.83</v>
       </c>
       <c r="L39" t="n">
-        <v>97.94</v>
+        <v>125.45</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:06:07</t>
+          <t>06:57:58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="F40" t="n">
-        <v>6.93</v>
+        <v>5.06</v>
       </c>
       <c r="G40" t="n">
-        <v>349.4</v>
+        <v>317.2</v>
       </c>
       <c r="H40" t="n">
-        <v>13.5</v>
+        <v>33</v>
       </c>
       <c r="I40" t="n">
         <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>103.69</v>
+        <v>157.55</v>
       </c>
       <c r="K40" t="n">
-        <v>60.61</v>
+        <v>2.36</v>
       </c>
       <c r="L40" t="n">
-        <v>120.1</v>
+        <v>157.57</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:10:38</t>
+          <t>07:02:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.07</v>
+        <v>2.41</v>
       </c>
       <c r="F41" t="n">
-        <v>6.86</v>
+        <v>8.51</v>
       </c>
       <c r="G41" t="n">
-        <v>328.9</v>
+        <v>331.7</v>
       </c>
       <c r="H41" t="n">
-        <v>37.2</v>
+        <v>40.8</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-109.94</v>
+        <v>27.97</v>
       </c>
       <c r="K41" t="n">
-        <v>-170.3</v>
+        <v>-159.94</v>
       </c>
       <c r="L41" t="n">
-        <v>202.7</v>
+        <v>162.36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:12:27</t>
+          <t>07:02:45</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="F42" t="n">
-        <v>5.76</v>
+        <v>8.51</v>
       </c>
       <c r="G42" t="n">
-        <v>324.5</v>
+        <v>328.4</v>
       </c>
       <c r="H42" t="n">
-        <v>19.2</v>
+        <v>50.7</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>115.33</v>
+        <v>68.14</v>
       </c>
       <c r="K42" t="n">
-        <v>-92.98999999999999</v>
+        <v>-189.17</v>
       </c>
       <c r="L42" t="n">
-        <v>148.15</v>
+        <v>201.07</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:13:45</t>
+          <t>07:05:14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="F43" t="n">
-        <v>8.08</v>
+        <v>2.34</v>
       </c>
       <c r="G43" t="n">
-        <v>343.1</v>
+        <v>327.2</v>
       </c>
       <c r="H43" t="n">
-        <v>24.8</v>
+        <v>20.8</v>
       </c>
       <c r="I43" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>-171.94</v>
+        <v>130.91</v>
       </c>
       <c r="K43" t="n">
-        <v>39.38</v>
+        <v>-216.6</v>
       </c>
       <c r="L43" t="n">
-        <v>176.39</v>
+        <v>253.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:21:23</t>
+          <t>07:18:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="F44" t="n">
-        <v>7.34</v>
+        <v>7.19</v>
       </c>
       <c r="G44" t="n">
-        <v>325.7</v>
+        <v>336.2</v>
       </c>
       <c r="H44" t="n">
-        <v>68.40000000000001</v>
+        <v>62.7</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-31.62</v>
+        <v>-26.93</v>
       </c>
       <c r="K44" t="n">
-        <v>28.01</v>
+        <v>-39.13</v>
       </c>
       <c r="L44" t="n">
-        <v>42.24</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:22:39</t>
+          <t>07:19:10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="F45" t="n">
-        <v>5.86</v>
+        <v>4.47</v>
       </c>
       <c r="G45" t="n">
-        <v>330.3</v>
+        <v>332.7</v>
       </c>
       <c r="H45" t="n">
-        <v>40.7</v>
+        <v>72.2</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>-47.78</v>
+        <v>-16.8</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.59</v>
+        <v>-31.66</v>
       </c>
       <c r="L45" t="n">
-        <v>47.81</v>
+        <v>35.84</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:24:09</t>
+          <t>07:21:14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="F46" t="n">
-        <v>8.51</v>
+        <v>7.31</v>
       </c>
       <c r="G46" t="n">
-        <v>341.1</v>
+        <v>352.4</v>
       </c>
       <c r="H46" t="n">
-        <v>25.7</v>
+        <v>30.1</v>
       </c>
       <c r="I46" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>15.77</v>
+        <v>26.13</v>
       </c>
       <c r="K46" t="n">
-        <v>34.76</v>
+        <v>24.24</v>
       </c>
       <c r="L46" t="n">
-        <v>38.17</v>
+        <v>35.64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:29:34</t>
+          <t>07:24:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="F47" t="n">
-        <v>5.01</v>
+        <v>7.07</v>
       </c>
       <c r="G47" t="n">
-        <v>327.5</v>
+        <v>334.2</v>
       </c>
       <c r="H47" t="n">
-        <v>23.6</v>
+        <v>63.3</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>61.58</v>
+        <v>61.54</v>
       </c>
       <c r="K47" t="n">
-        <v>30.56</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>68.75</v>
+        <v>62.23</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:32:03</t>
+          <t>07:26:44</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="F48" t="n">
-        <v>8.51</v>
+        <v>7.8</v>
       </c>
       <c r="G48" t="n">
-        <v>326</v>
+        <v>340.5</v>
       </c>
       <c r="H48" t="n">
-        <v>8.699999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="I48" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>-25.61</v>
+        <v>-27.9</v>
       </c>
       <c r="K48" t="n">
-        <v>66</v>
+        <v>63.22</v>
       </c>
       <c r="L48" t="n">
-        <v>70.79000000000001</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:34:23</t>
+          <t>07:28:34</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="F49" t="n">
         <v>8.51</v>
       </c>
       <c r="G49" t="n">
-        <v>331</v>
+        <v>324.7</v>
       </c>
       <c r="H49" t="n">
-        <v>55.8</v>
+        <v>50.2</v>
       </c>
       <c r="I49" t="n">
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>68.51000000000001</v>
+        <v>68.37</v>
       </c>
       <c r="K49" t="n">
-        <v>37.83</v>
+        <v>-5.52</v>
       </c>
       <c r="L49" t="n">
-        <v>78.26000000000001</v>
+        <v>68.59</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:39:26</t>
+          <t>07:34:43</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.02</v>
+        <v>2.71</v>
       </c>
       <c r="F50" t="n">
-        <v>6.53</v>
+        <v>5.86</v>
       </c>
       <c r="G50" t="n">
-        <v>330.3</v>
+        <v>343.1</v>
       </c>
       <c r="H50" t="n">
-        <v>54.3</v>
+        <v>49.7</v>
       </c>
       <c r="I50" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.03</v>
+        <v>16.05</v>
       </c>
       <c r="K50" t="n">
-        <v>82.20999999999999</v>
+        <v>-99.87</v>
       </c>
       <c r="L50" t="n">
-        <v>82.43000000000001</v>
+        <v>101.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:41:13</t>
+          <t>07:35:54</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.57</v>
+        <v>1.97</v>
       </c>
       <c r="F51" t="n">
-        <v>8.51</v>
+        <v>6.93</v>
       </c>
       <c r="G51" t="n">
-        <v>331</v>
+        <v>343.9</v>
       </c>
       <c r="H51" t="n">
-        <v>83.2</v>
+        <v>50.4</v>
       </c>
       <c r="I51" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-95.05</v>
+        <v>-98.7</v>
       </c>
       <c r="K51" t="n">
-        <v>89.26000000000001</v>
+        <v>-20.56</v>
       </c>
       <c r="L51" t="n">
-        <v>130.38</v>
+        <v>100.82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:42:43</t>
+          <t>07:36:40</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.07</v>
+        <v>2.34</v>
       </c>
       <c r="F52" t="n">
-        <v>6.19</v>
+        <v>5.02</v>
       </c>
       <c r="G52" t="n">
-        <v>342.8</v>
+        <v>328.2</v>
       </c>
       <c r="H52" t="n">
-        <v>10.8</v>
+        <v>40.3</v>
       </c>
       <c r="I52" t="n">
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>9.470000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="K52" t="n">
-        <v>-135.6</v>
+        <v>71.28</v>
       </c>
       <c r="L52" t="n">
-        <v>135.93</v>
+        <v>106.52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:47:58</t>
+          <t>07:41:39</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="F53" t="n">
-        <v>7.35</v>
+        <v>4.84</v>
       </c>
       <c r="G53" t="n">
-        <v>328.1</v>
+        <v>337.7</v>
       </c>
       <c r="H53" t="n">
-        <v>48.9</v>
+        <v>42</v>
       </c>
       <c r="I53" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>-63.58</v>
+        <v>119.38</v>
       </c>
       <c r="K53" t="n">
-        <v>127.69</v>
+        <v>116.3</v>
       </c>
       <c r="L53" t="n">
-        <v>142.64</v>
+        <v>166.67</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:50:15</t>
+          <t>07:42:56</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="F54" t="n">
-        <v>6.88</v>
+        <v>7.24</v>
       </c>
       <c r="G54" t="n">
-        <v>334.3</v>
+        <v>330.6</v>
       </c>
       <c r="H54" t="n">
-        <v>19.3</v>
+        <v>61.9</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-40.53</v>
+        <v>-125.62</v>
       </c>
       <c r="K54" t="n">
-        <v>181.62</v>
+        <v>30.27</v>
       </c>
       <c r="L54" t="n">
-        <v>186.09</v>
+        <v>129.21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:50:58</t>
+          <t>07:45:07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="F55" t="n">
-        <v>8.51</v>
+        <v>8.07</v>
       </c>
       <c r="G55" t="n">
-        <v>337.3</v>
+        <v>327.6</v>
       </c>
       <c r="H55" t="n">
-        <v>42.6</v>
+        <v>47.8</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>89.17</v>
+        <v>-125.52</v>
       </c>
       <c r="K55" t="n">
-        <v>41.82</v>
+        <v>-27.04</v>
       </c>
       <c r="L55" t="n">
-        <v>98.48999999999999</v>
+        <v>128.39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:56:24</t>
+          <t>07:49:47</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="F56" t="n">
-        <v>7.22</v>
+        <v>7.39</v>
       </c>
       <c r="G56" t="n">
-        <v>320.4</v>
+        <v>326.2</v>
       </c>
       <c r="H56" t="n">
-        <v>36.3</v>
+        <v>39</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>104.15</v>
+        <v>132.15</v>
       </c>
       <c r="K56" t="n">
-        <v>113.75</v>
+        <v>-7.26</v>
       </c>
       <c r="L56" t="n">
-        <v>154.23</v>
+        <v>132.35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:57:57</t>
+          <t>07:51:06</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="F57" t="n">
-        <v>7.18</v>
+        <v>7.05</v>
       </c>
       <c r="G57" t="n">
-        <v>339.1</v>
+        <v>317.4</v>
       </c>
       <c r="H57" t="n">
-        <v>40.3</v>
+        <v>51</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>164.17</v>
+        <v>108.77</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.61</v>
+        <v>-120.24</v>
       </c>
       <c r="L57" t="n">
-        <v>164.27</v>
+        <v>162.14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:59:14</t>
+          <t>07:53:02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="F58" t="n">
-        <v>5.63</v>
+        <v>4.72</v>
       </c>
       <c r="G58" t="n">
-        <v>315</v>
+        <v>319.6</v>
       </c>
       <c r="H58" t="n">
-        <v>49.2</v>
+        <v>21.7</v>
       </c>
       <c r="I58" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>-6.81</v>
+        <v>141.89</v>
       </c>
       <c r="K58" t="n">
-        <v>-195.04</v>
+        <v>-83.16</v>
       </c>
       <c r="L58" t="n">
-        <v>195.16</v>
+        <v>164.46</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:09:47</t>
+          <t>08:04:25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="F59" t="n">
-        <v>4.11</v>
+        <v>7.32</v>
       </c>
       <c r="G59" t="n">
-        <v>345.8</v>
+        <v>332.9</v>
       </c>
       <c r="H59" t="n">
-        <v>39.9</v>
+        <v>57.2</v>
       </c>
       <c r="I59" t="n">
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>1.68</v>
+        <v>-26.78</v>
       </c>
       <c r="K59" t="n">
-        <v>-27.31</v>
+        <v>-24.38</v>
       </c>
       <c r="L59" t="n">
-        <v>27.36</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:11:36</t>
+          <t>08:06:48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.42</v>
+        <v>3.19</v>
       </c>
       <c r="F60" t="n">
-        <v>5.13</v>
+        <v>8.51</v>
       </c>
       <c r="G60" t="n">
-        <v>317.7</v>
+        <v>321.1</v>
       </c>
       <c r="H60" t="n">
-        <v>39.3</v>
+        <v>55.7</v>
       </c>
       <c r="I60" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-31.95</v>
+        <v>55.74</v>
       </c>
       <c r="K60" t="n">
-        <v>29.63</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>43.57</v>
+        <v>55.74</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:12:59</t>
+          <t>08:08:16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="F61" t="n">
-        <v>8.51</v>
+        <v>7.97</v>
       </c>
       <c r="G61" t="n">
-        <v>335.7</v>
+        <v>345.6</v>
       </c>
       <c r="H61" t="n">
-        <v>54.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.64</v>
+        <v>15.31</v>
       </c>
       <c r="K61" t="n">
-        <v>23.8</v>
+        <v>46.47</v>
       </c>
       <c r="L61" t="n">
-        <v>29.04</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:17:11</t>
+          <t>08:13:13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="F62" t="n">
-        <v>7.94</v>
+        <v>7.78</v>
       </c>
       <c r="G62" t="n">
-        <v>333.7</v>
+        <v>333.4</v>
       </c>
       <c r="H62" t="n">
-        <v>56.2</v>
+        <v>57.7</v>
       </c>
       <c r="I62" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>72.45999999999999</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>34.91</v>
+        <v>-56.38</v>
       </c>
       <c r="L62" t="n">
-        <v>80.43000000000001</v>
+        <v>107.23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:18:38</t>
+          <t>08:15:19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="F63" t="n">
-        <v>7.77</v>
+        <v>6.7</v>
       </c>
       <c r="G63" t="n">
-        <v>332.6</v>
+        <v>318.5</v>
       </c>
       <c r="H63" t="n">
-        <v>48.4</v>
+        <v>39.7</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>43.27</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-10.02</v>
+        <v>27.01</v>
       </c>
       <c r="L63" t="n">
-        <v>44.42</v>
+        <v>69.92</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:19:58</t>
+          <t>08:17:47</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="F64" t="n">
-        <v>3.44</v>
+        <v>8.51</v>
       </c>
       <c r="G64" t="n">
-        <v>315.7</v>
+        <v>320.9</v>
       </c>
       <c r="H64" t="n">
-        <v>41.1</v>
+        <v>51.1</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>-42.94</v>
+        <v>-59.3</v>
       </c>
       <c r="K64" t="n">
-        <v>-13.9</v>
+        <v>-16.8</v>
       </c>
       <c r="L64" t="n">
-        <v>45.13</v>
+        <v>61.64</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:25:35</t>
+          <t>08:22:36</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="F65" t="n">
-        <v>7.81</v>
+        <v>8.51</v>
       </c>
       <c r="G65" t="n">
-        <v>338.2</v>
+        <v>334</v>
       </c>
       <c r="H65" t="n">
-        <v>25.7</v>
+        <v>50.6</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-15.49</v>
+        <v>-89.76000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>12.44</v>
+        <v>131.1</v>
       </c>
       <c r="L65" t="n">
-        <v>19.86</v>
+        <v>158.88</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:27:37</t>
+          <t>08:25:12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="F66" t="n">
-        <v>8.51</v>
+        <v>7.28</v>
       </c>
       <c r="G66" t="n">
-        <v>321.5</v>
+        <v>339.3</v>
       </c>
       <c r="H66" t="n">
-        <v>66.09999999999999</v>
+        <v>31.3</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.26</v>
+        <v>32.65</v>
       </c>
       <c r="K66" t="n">
-        <v>80.8</v>
+        <v>-21.27</v>
       </c>
       <c r="L66" t="n">
-        <v>80.8</v>
+        <v>38.97</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:29:19</t>
+          <t>08:26:43</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="F67" t="n">
-        <v>8.51</v>
+        <v>8.18</v>
       </c>
       <c r="G67" t="n">
-        <v>318.4</v>
+        <v>325.5</v>
       </c>
       <c r="H67" t="n">
-        <v>23.7</v>
+        <v>50.6</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-91.02</v>
+        <v>-25.65</v>
       </c>
       <c r="K67" t="n">
-        <v>-31.96</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>96.47</v>
+        <v>99.11</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:33:41</t>
+          <t>08:30:02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.73</v>
+        <v>2.36</v>
       </c>
       <c r="F68" t="n">
-        <v>7.57</v>
+        <v>8.51</v>
       </c>
       <c r="G68" t="n">
-        <v>324.9</v>
+        <v>347.7</v>
       </c>
       <c r="H68" t="n">
-        <v>56.2</v>
+        <v>54.5</v>
       </c>
       <c r="I68" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-125.16</v>
+        <v>-24.69</v>
       </c>
       <c r="K68" t="n">
-        <v>31.21</v>
+        <v>88.92</v>
       </c>
       <c r="L68" t="n">
-        <v>129</v>
+        <v>92.28</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:35:54</t>
+          <t>08:31:54</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.31</v>
+        <v>2.67</v>
       </c>
       <c r="F69" t="n">
-        <v>7.95</v>
+        <v>6.83</v>
       </c>
       <c r="G69" t="n">
-        <v>331.2</v>
+        <v>323.5</v>
       </c>
       <c r="H69" t="n">
-        <v>36.1</v>
+        <v>45.2</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>-146.73</v>
+        <v>164.38</v>
       </c>
       <c r="K69" t="n">
-        <v>-50.44</v>
+        <v>-81.38</v>
       </c>
       <c r="L69" t="n">
-        <v>155.16</v>
+        <v>183.42</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:36:53</t>
+          <t>08:33:25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="F70" t="n">
-        <v>8.51</v>
+        <v>5.28</v>
       </c>
       <c r="G70" t="n">
-        <v>337.5</v>
+        <v>342.1</v>
       </c>
       <c r="H70" t="n">
-        <v>29</v>
+        <v>37.5</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J70" t="n">
-        <v>-13.55</v>
+        <v>83</v>
       </c>
       <c r="K70" t="n">
-        <v>136.83</v>
+        <v>-73.64</v>
       </c>
       <c r="L70" t="n">
-        <v>137.5</v>
+        <v>110.96</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:41:02</t>
+          <t>08:37:15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.79</v>
+        <v>2.68</v>
       </c>
       <c r="F71" t="n">
-        <v>6.85</v>
+        <v>5.26</v>
       </c>
       <c r="G71" t="n">
-        <v>324.5</v>
+        <v>320.3</v>
       </c>
       <c r="H71" t="n">
-        <v>36.8</v>
+        <v>38.8</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J71" t="n">
-        <v>-321.13</v>
+        <v>155.33</v>
       </c>
       <c r="K71" t="n">
-        <v>-24.04</v>
+        <v>154.56</v>
       </c>
       <c r="L71" t="n">
-        <v>322.03</v>
+        <v>219.12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:42:25</t>
+          <t>08:39:42</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.34</v>
+        <v>2.71</v>
       </c>
       <c r="F72" t="n">
         <v>8.51</v>
       </c>
       <c r="G72" t="n">
-        <v>343.4</v>
+        <v>325.2</v>
       </c>
       <c r="H72" t="n">
-        <v>29.8</v>
+        <v>46.3</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>62.27</v>
+        <v>-106.81</v>
       </c>
       <c r="K72" t="n">
-        <v>146.16</v>
+        <v>141.29</v>
       </c>
       <c r="L72" t="n">
-        <v>158.87</v>
+        <v>177.12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:44:00</t>
+          <t>08:41:10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="F73" t="n">
         <v>8.51</v>
       </c>
       <c r="G73" t="n">
-        <v>325.9</v>
+        <v>334.5</v>
       </c>
       <c r="H73" t="n">
-        <v>52.8</v>
+        <v>28.2</v>
       </c>
       <c r="I73" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>-67.34</v>
+        <v>226.89</v>
       </c>
       <c r="K73" t="n">
-        <v>176.05</v>
+        <v>49.22</v>
       </c>
       <c r="L73" t="n">
-        <v>188.49</v>
+        <v>232.17</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:56:53</t>
+          <t>08:51:48</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.13</v>
+        <v>2.66</v>
       </c>
       <c r="F74" t="n">
-        <v>4.19</v>
+        <v>8.51</v>
       </c>
       <c r="G74" t="n">
-        <v>342.4</v>
+        <v>327.7</v>
       </c>
       <c r="H74" t="n">
-        <v>58.3</v>
+        <v>46.2</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>-35.14</v>
+        <v>3.38</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.88</v>
+        <v>-53.17</v>
       </c>
       <c r="L74" t="n">
-        <v>35.63</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:58:02</t>
+          <t>08:53:24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="F75" t="n">
-        <v>8.51</v>
+        <v>2.35</v>
       </c>
       <c r="G75" t="n">
-        <v>312.1</v>
+        <v>312.5</v>
       </c>
       <c r="H75" t="n">
-        <v>63.1</v>
+        <v>50.8</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>9.27</v>
+        <v>-32.65</v>
       </c>
       <c r="K75" t="n">
-        <v>-21.51</v>
+        <v>20.91</v>
       </c>
       <c r="L75" t="n">
-        <v>23.43</v>
+        <v>38.77</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:00:09</t>
+          <t>08:55:21</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.64</v>
+        <v>2.43</v>
       </c>
       <c r="F76" t="n">
         <v>8.51</v>
       </c>
       <c r="G76" t="n">
-        <v>330.6</v>
+        <v>327</v>
       </c>
       <c r="H76" t="n">
-        <v>47.3</v>
+        <v>28.4</v>
       </c>
       <c r="I76" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.869999999999999</v>
+        <v>7.66</v>
       </c>
       <c r="K76" t="n">
-        <v>41.45</v>
+        <v>54.39</v>
       </c>
       <c r="L76" t="n">
-        <v>42.39</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:04:29</t>
+          <t>09:00:18</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="F77" t="n">
-        <v>5.75</v>
+        <v>7.51</v>
       </c>
       <c r="G77" t="n">
-        <v>323.7</v>
+        <v>321.6</v>
       </c>
       <c r="H77" t="n">
-        <v>75.7</v>
+        <v>27.9</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>46.74</v>
+        <v>55.9</v>
       </c>
       <c r="K77" t="n">
-        <v>60.09</v>
+        <v>37.87</v>
       </c>
       <c r="L77" t="n">
-        <v>76.13</v>
+        <v>67.52</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:05:59</t>
+          <t>09:02:27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.82</v>
+        <v>2.13</v>
       </c>
       <c r="F78" t="n">
-        <v>7.48</v>
+        <v>5.07</v>
       </c>
       <c r="G78" t="n">
-        <v>344.4</v>
+        <v>325.3</v>
       </c>
       <c r="H78" t="n">
-        <v>25.7</v>
+        <v>42.4</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>37.02</v>
+        <v>-25.63</v>
       </c>
       <c r="K78" t="n">
-        <v>56.04</v>
+        <v>-53.39</v>
       </c>
       <c r="L78" t="n">
-        <v>67.17</v>
+        <v>59.22</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:08:02</t>
+          <t>09:04:15</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="F79" t="n">
-        <v>8.01</v>
+        <v>5.72</v>
       </c>
       <c r="G79" t="n">
-        <v>341.7</v>
+        <v>327.3</v>
       </c>
       <c r="H79" t="n">
-        <v>36.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>48.94</v>
+        <v>65.06</v>
       </c>
       <c r="K79" t="n">
-        <v>7.2</v>
+        <v>8.58</v>
       </c>
       <c r="L79" t="n">
-        <v>49.47</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:12:43</t>
+          <t>09:09:13</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="F80" t="n">
-        <v>7.68</v>
+        <v>8.51</v>
       </c>
       <c r="G80" t="n">
-        <v>320.7</v>
+        <v>337.1</v>
       </c>
       <c r="H80" t="n">
-        <v>34.4</v>
+        <v>50.4</v>
       </c>
       <c r="I80" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.17</v>
+        <v>-67.20999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>96.42</v>
+        <v>77.81</v>
       </c>
       <c r="L80" t="n">
-        <v>96.77</v>
+        <v>102.82</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:14:40</t>
+          <t>09:11:37</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="F81" t="n">
-        <v>8.01</v>
+        <v>8.51</v>
       </c>
       <c r="G81" t="n">
-        <v>315.2</v>
+        <v>329.7</v>
       </c>
       <c r="H81" t="n">
-        <v>44.5</v>
+        <v>8</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J81" t="n">
-        <v>76.93000000000001</v>
+        <v>-121.79</v>
       </c>
       <c r="K81" t="n">
-        <v>71.06999999999999</v>
+        <v>63</v>
       </c>
       <c r="L81" t="n">
-        <v>104.73</v>
+        <v>137.12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:16:53</t>
+          <t>09:12:58</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="F82" t="n">
-        <v>8.51</v>
+        <v>5.63</v>
       </c>
       <c r="G82" t="n">
-        <v>342</v>
+        <v>314.6</v>
       </c>
       <c r="H82" t="n">
-        <v>70.90000000000001</v>
+        <v>48.5</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-64.88</v>
+        <v>-39.94</v>
       </c>
       <c r="K82" t="n">
-        <v>-95.55</v>
+        <v>-111.54</v>
       </c>
       <c r="L82" t="n">
-        <v>115.49</v>
+        <v>118.47</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:21:00</t>
+          <t>09:16:17</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.01</v>
+        <v>2.36</v>
       </c>
       <c r="F83" t="n">
-        <v>8.06</v>
+        <v>8.51</v>
       </c>
       <c r="G83" t="n">
-        <v>328.5</v>
+        <v>336.1</v>
       </c>
       <c r="H83" t="n">
-        <v>66.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>36.87</v>
+        <v>-97.97</v>
       </c>
       <c r="K83" t="n">
-        <v>91.56999999999999</v>
+        <v>-142.36</v>
       </c>
       <c r="L83" t="n">
-        <v>98.70999999999999</v>
+        <v>172.81</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:23:12</t>
+          <t>09:17:30</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.72</v>
+        <v>2.12</v>
       </c>
       <c r="F84" t="n">
         <v>8.51</v>
       </c>
       <c r="G84" t="n">
-        <v>323.2</v>
+        <v>326</v>
       </c>
       <c r="H84" t="n">
-        <v>38.2</v>
+        <v>64</v>
       </c>
       <c r="I84" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-36.91</v>
+        <v>49.4</v>
       </c>
       <c r="K84" t="n">
-        <v>132.63</v>
+        <v>143.86</v>
       </c>
       <c r="L84" t="n">
-        <v>137.67</v>
+        <v>152.11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:24:14</t>
+          <t>09:18:34</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.19</v>
+        <v>2.42</v>
       </c>
       <c r="F85" t="n">
-        <v>6.68</v>
+        <v>7.42</v>
       </c>
       <c r="G85" t="n">
-        <v>339.6</v>
+        <v>331.4</v>
       </c>
       <c r="H85" t="n">
-        <v>55.8</v>
+        <v>48.5</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>106.71</v>
+        <v>111.99</v>
       </c>
       <c r="K85" t="n">
-        <v>-7.4</v>
+        <v>113.74</v>
       </c>
       <c r="L85" t="n">
-        <v>106.97</v>
+        <v>159.62</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:29:20</t>
+          <t>09:23:51</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="F86" t="n">
-        <v>7.93</v>
+        <v>8.51</v>
       </c>
       <c r="G86" t="n">
-        <v>327.6</v>
+        <v>311.4</v>
       </c>
       <c r="H86" t="n">
-        <v>19.8</v>
+        <v>27.8</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-111.42</v>
+        <v>-143.46</v>
       </c>
       <c r="K86" t="n">
-        <v>-150.42</v>
+        <v>182.59</v>
       </c>
       <c r="L86" t="n">
-        <v>187.19</v>
+        <v>232.21</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:30:45</t>
+          <t>09:26:26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.77</v>
+        <v>2.28</v>
       </c>
       <c r="F87" t="n">
-        <v>6.5</v>
+        <v>8.35</v>
       </c>
       <c r="G87" t="n">
-        <v>341</v>
+        <v>338.2</v>
       </c>
       <c r="H87" t="n">
-        <v>41.2</v>
+        <v>25.7</v>
       </c>
       <c r="I87" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-62.44</v>
+        <v>-80.3</v>
       </c>
       <c r="K87" t="n">
-        <v>-169.32</v>
+        <v>3.82</v>
       </c>
       <c r="L87" t="n">
-        <v>180.47</v>
+        <v>80.39</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:32:06</t>
+          <t>09:28:40</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F88" t="n">
-        <v>8.119999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="G88" t="n">
-        <v>335.9</v>
+        <v>321.5</v>
       </c>
       <c r="H88" t="n">
-        <v>63.4</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-169.04</v>
+        <v>23.56</v>
       </c>
       <c r="K88" t="n">
-        <v>-107.69</v>
+        <v>196.81</v>
       </c>
       <c r="L88" t="n">
-        <v>200.43</v>
+        <v>198.22</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-04-22.xlsx
+++ b/output/2025-04-22.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>22.99</v>
+        <v>21.89</v>
       </c>
       <c r="K14" t="n">
-        <v>-55.43</v>
+        <v>-52.78</v>
       </c>
       <c r="L14" t="n">
-        <v>60.01</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>10.63</v>
+        <v>10.24</v>
       </c>
       <c r="K15" t="n">
-        <v>-60.4</v>
+        <v>-58.16</v>
       </c>
       <c r="L15" t="n">
-        <v>61.33</v>
+        <v>59.05</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>32.79</v>
+        <v>36.75</v>
       </c>
       <c r="K16" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>32.79</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>21.97</v>
+        <v>22.81</v>
       </c>
       <c r="K17" t="n">
-        <v>62.91</v>
+        <v>65.34</v>
       </c>
       <c r="L17" t="n">
-        <v>66.64</v>
+        <v>69.20999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>63.44</v>
+        <v>62.36</v>
       </c>
       <c r="K18" t="n">
-        <v>65.87</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>91.45</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-46.34</v>
+        <v>-51.08</v>
       </c>
       <c r="K19" t="n">
-        <v>16.78</v>
+        <v>18.49</v>
       </c>
       <c r="L19" t="n">
-        <v>49.28</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>93.33</v>
+        <v>103.71</v>
       </c>
       <c r="K20" t="n">
-        <v>5.66</v>
+        <v>6.29</v>
       </c>
       <c r="L20" t="n">
-        <v>93.5</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>11.5</v>
+        <v>12.14</v>
       </c>
       <c r="K21" t="n">
-        <v>122.88</v>
+        <v>129.68</v>
       </c>
       <c r="L21" t="n">
-        <v>123.41</v>
+        <v>130.24</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-45.2</v>
+        <v>-51.73</v>
       </c>
       <c r="K22" t="n">
-        <v>69.37</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>82.79000000000001</v>
+        <v>94.77</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>118.5</v>
+        <v>129.91</v>
       </c>
       <c r="K23" t="n">
-        <v>88.06</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>147.63</v>
+        <v>161.85</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-133.76</v>
+        <v>-148.21</v>
       </c>
       <c r="K24" t="n">
-        <v>8.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>134.02</v>
+        <v>148.5</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-121.24</v>
+        <v>-126.92</v>
       </c>
       <c r="K25" t="n">
-        <v>107.5</v>
+        <v>112.54</v>
       </c>
       <c r="L25" t="n">
-        <v>162.03</v>
+        <v>169.63</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-230.62</v>
+        <v>-254.65</v>
       </c>
       <c r="K26" t="n">
-        <v>-101.47</v>
+        <v>-112.04</v>
       </c>
       <c r="L26" t="n">
-        <v>251.96</v>
+        <v>278.21</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>175.08</v>
+        <v>202.04</v>
       </c>
       <c r="K27" t="n">
-        <v>-95.09</v>
+        <v>-109.73</v>
       </c>
       <c r="L27" t="n">
-        <v>199.24</v>
+        <v>229.92</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-133.2</v>
+        <v>-172.05</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.93</v>
+        <v>-10.25</v>
       </c>
       <c r="L28" t="n">
-        <v>133.44</v>
+        <v>172.35</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="K29" t="n">
-        <v>70.05</v>
+        <v>68.53</v>
       </c>
       <c r="L29" t="n">
-        <v>70.05</v>
+        <v>68.53</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.52</v>
+        <v>-16.96</v>
       </c>
       <c r="K30" t="n">
-        <v>-58.96</v>
+        <v>-57.1</v>
       </c>
       <c r="L30" t="n">
-        <v>61.51</v>
+        <v>59.56</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>18.67</v>
+        <v>18.16</v>
       </c>
       <c r="K31" t="n">
-        <v>-53.62</v>
+        <v>-52.15</v>
       </c>
       <c r="L31" t="n">
-        <v>56.78</v>
+        <v>55.22</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>41.97</v>
+        <v>45.91</v>
       </c>
       <c r="K32" t="n">
-        <v>-37.77</v>
+        <v>-41.32</v>
       </c>
       <c r="L32" t="n">
-        <v>56.47</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>51.51</v>
+        <v>55.22</v>
       </c>
       <c r="K33" t="n">
-        <v>20.26</v>
+        <v>21.72</v>
       </c>
       <c r="L33" t="n">
-        <v>55.35</v>
+        <v>59.34</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-48.99</v>
+        <v>-50.3</v>
       </c>
       <c r="K34" t="n">
-        <v>-40.53</v>
+        <v>-41.62</v>
       </c>
       <c r="L34" t="n">
-        <v>63.58</v>
+        <v>65.29000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.26</v>
+        <v>-14.17</v>
       </c>
       <c r="K35" t="n">
-        <v>76.73999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="L35" t="n">
-        <v>77.70999999999999</v>
+        <v>89.84</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>80.86</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-19.64</v>
+        <v>-21.57</v>
       </c>
       <c r="L36" t="n">
-        <v>83.20999999999999</v>
+        <v>91.38</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-12.58</v>
+        <v>-13.45</v>
       </c>
       <c r="K37" t="n">
-        <v>-104.33</v>
+        <v>-111.54</v>
       </c>
       <c r="L37" t="n">
-        <v>105.09</v>
+        <v>112.35</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>132.47</v>
+        <v>155.25</v>
       </c>
       <c r="K38" t="n">
-        <v>7.83</v>
+        <v>9.18</v>
       </c>
       <c r="L38" t="n">
-        <v>132.7</v>
+        <v>155.52</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-103.18</v>
+        <v>-116.81</v>
       </c>
       <c r="K39" t="n">
-        <v>-68.38</v>
+        <v>-77.41</v>
       </c>
       <c r="L39" t="n">
-        <v>123.78</v>
+        <v>140.14</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>140.6</v>
+        <v>145.73</v>
       </c>
       <c r="K40" t="n">
-        <v>125.84</v>
+        <v>130.43</v>
       </c>
       <c r="L40" t="n">
-        <v>188.69</v>
+        <v>195.57</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.73</v>
+        <v>-17.86</v>
       </c>
       <c r="K41" t="n">
-        <v>207.41</v>
+        <v>235.46</v>
       </c>
       <c r="L41" t="n">
-        <v>208</v>
+        <v>236.14</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>183.42</v>
+        <v>211.64</v>
       </c>
       <c r="K42" t="n">
-        <v>-45.95</v>
+        <v>-53.02</v>
       </c>
       <c r="L42" t="n">
-        <v>189.08</v>
+        <v>218.18</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-110.92</v>
+        <v>-127.47</v>
       </c>
       <c r="K43" t="n">
-        <v>152.75</v>
+        <v>175.54</v>
       </c>
       <c r="L43" t="n">
-        <v>188.77</v>
+        <v>216.94</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>47.58</v>
+        <v>47.64</v>
       </c>
       <c r="K44" t="n">
-        <v>-21.98</v>
+        <v>-22.01</v>
       </c>
       <c r="L44" t="n">
-        <v>52.41</v>
+        <v>52.48</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-59.87</v>
+        <v>-58.68</v>
       </c>
       <c r="K45" t="n">
-        <v>-15.64</v>
+        <v>-15.33</v>
       </c>
       <c r="L45" t="n">
-        <v>61.88</v>
+        <v>60.65</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>18.72</v>
+        <v>21.18</v>
       </c>
       <c r="K46" t="n">
-        <v>30</v>
+        <v>33.94</v>
       </c>
       <c r="L46" t="n">
-        <v>35.36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-82.47</v>
+        <v>-83.08</v>
       </c>
       <c r="K47" t="n">
-        <v>25.48</v>
+        <v>25.67</v>
       </c>
       <c r="L47" t="n">
-        <v>86.31999999999999</v>
+        <v>86.95999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>38.87</v>
+        <v>39.54</v>
       </c>
       <c r="K48" t="n">
-        <v>69.11</v>
+        <v>70.3</v>
       </c>
       <c r="L48" t="n">
-        <v>79.3</v>
+        <v>80.66</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>25.66</v>
+        <v>28.99</v>
       </c>
       <c r="K49" t="n">
-        <v>41.89</v>
+        <v>47.32</v>
       </c>
       <c r="L49" t="n">
-        <v>49.13</v>
+        <v>55.49</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-32.4</v>
+        <v>-34.94</v>
       </c>
       <c r="K50" t="n">
-        <v>77.56999999999999</v>
+        <v>83.66</v>
       </c>
       <c r="L50" t="n">
-        <v>84.06999999999999</v>
+        <v>90.66</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-102.66</v>
+        <v>-109.41</v>
       </c>
       <c r="K51" t="n">
-        <v>-36.9</v>
+        <v>-39.32</v>
       </c>
       <c r="L51" t="n">
-        <v>109.09</v>
+        <v>116.27</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-72.11</v>
+        <v>-71.22</v>
       </c>
       <c r="K52" t="n">
-        <v>-159.04</v>
+        <v>-157.08</v>
       </c>
       <c r="L52" t="n">
-        <v>174.62</v>
+        <v>172.48</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>12.07</v>
+        <v>14.36</v>
       </c>
       <c r="K53" t="n">
-        <v>-8.710000000000001</v>
+        <v>-10.36</v>
       </c>
       <c r="L53" t="n">
-        <v>14.88</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-25.98</v>
+        <v>-27.68</v>
       </c>
       <c r="K54" t="n">
-        <v>147.19</v>
+        <v>156.81</v>
       </c>
       <c r="L54" t="n">
-        <v>149.47</v>
+        <v>159.23</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-133.42</v>
+        <v>-142.63</v>
       </c>
       <c r="K55" t="n">
-        <v>101.09</v>
+        <v>108.06</v>
       </c>
       <c r="L55" t="n">
-        <v>167.39</v>
+        <v>178.94</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>122.54</v>
+        <v>159.34</v>
       </c>
       <c r="K56" t="n">
-        <v>22.68</v>
+        <v>29.49</v>
       </c>
       <c r="L56" t="n">
-        <v>124.62</v>
+        <v>162.04</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-169.54</v>
+        <v>-198.48</v>
       </c>
       <c r="K57" t="n">
-        <v>-59.67</v>
+        <v>-69.86</v>
       </c>
       <c r="L57" t="n">
-        <v>179.74</v>
+        <v>210.42</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-140.91</v>
+        <v>-164.86</v>
       </c>
       <c r="K58" t="n">
-        <v>-149.56</v>
+        <v>-174.98</v>
       </c>
       <c r="L58" t="n">
-        <v>205.48</v>
+        <v>240.41</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-52.1</v>
+        <v>-54.02</v>
       </c>
       <c r="K59" t="n">
-        <v>-21.14</v>
+        <v>-21.92</v>
       </c>
       <c r="L59" t="n">
-        <v>56.22</v>
+        <v>58.29</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>39.95</v>
+        <v>38.93</v>
       </c>
       <c r="K60" t="n">
-        <v>46.97</v>
+        <v>45.77</v>
       </c>
       <c r="L60" t="n">
-        <v>61.66</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>42.29</v>
+        <v>41.39</v>
       </c>
       <c r="K61" t="n">
-        <v>-19.48</v>
+        <v>-19.06</v>
       </c>
       <c r="L61" t="n">
-        <v>46.56</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>45.73</v>
+        <v>48.02</v>
       </c>
       <c r="K62" t="n">
-        <v>-40.79</v>
+        <v>-42.84</v>
       </c>
       <c r="L62" t="n">
-        <v>61.28</v>
+        <v>64.34999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>4.52</v>
+        <v>4.96</v>
       </c>
       <c r="K63" t="n">
-        <v>56.19</v>
+        <v>61.78</v>
       </c>
       <c r="L63" t="n">
-        <v>56.37</v>
+        <v>61.98</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-62.03</v>
+        <v>-64.27</v>
       </c>
       <c r="K64" t="n">
-        <v>10.89</v>
+        <v>11.29</v>
       </c>
       <c r="L64" t="n">
-        <v>62.98</v>
+        <v>65.25</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-41.73</v>
+        <v>-49.2</v>
       </c>
       <c r="K65" t="n">
-        <v>-53.42</v>
+        <v>-62.99</v>
       </c>
       <c r="L65" t="n">
-        <v>67.79000000000001</v>
+        <v>79.93000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-44.75</v>
+        <v>-48.67</v>
       </c>
       <c r="K66" t="n">
-        <v>84.04000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>95.20999999999999</v>
+        <v>103.55</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-60.72</v>
+        <v>-67.15000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-62.12</v>
+        <v>-68.70999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>86.87</v>
+        <v>96.06999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-106.95</v>
+        <v>-126.57</v>
       </c>
       <c r="K68" t="n">
-        <v>54.16</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>119.89</v>
+        <v>141.87</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>87.22</v>
+        <v>92.53</v>
       </c>
       <c r="K69" t="n">
-        <v>145.74</v>
+        <v>154.61</v>
       </c>
       <c r="L69" t="n">
-        <v>169.84</v>
+        <v>180.18</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>92.95</v>
+        <v>100.2</v>
       </c>
       <c r="K70" t="n">
-        <v>97.31999999999999</v>
+        <v>104.91</v>
       </c>
       <c r="L70" t="n">
-        <v>134.58</v>
+        <v>145.07</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-83.06999999999999</v>
+        <v>-95.23999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>-180.86</v>
+        <v>-207.35</v>
       </c>
       <c r="L71" t="n">
-        <v>199.02</v>
+        <v>228.18</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-194.44</v>
+        <v>-214.01</v>
       </c>
       <c r="K72" t="n">
-        <v>62.28</v>
+        <v>68.55</v>
       </c>
       <c r="L72" t="n">
-        <v>204.17</v>
+        <v>224.72</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-189.68</v>
+        <v>-215.51</v>
       </c>
       <c r="K73" t="n">
-        <v>-107.78</v>
+        <v>-122.45</v>
       </c>
       <c r="L73" t="n">
-        <v>218.17</v>
+        <v>247.87</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>18.35</v>
+        <v>19.83</v>
       </c>
       <c r="K74" t="n">
-        <v>-34.19</v>
+        <v>-36.95</v>
       </c>
       <c r="L74" t="n">
-        <v>38.81</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-43.12</v>
+        <v>-47.4</v>
       </c>
       <c r="K75" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="L75" t="n">
-        <v>43.13</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>9.16</v>
+        <v>8.98</v>
       </c>
       <c r="K76" t="n">
-        <v>-77.95999999999999</v>
+        <v>-76.38</v>
       </c>
       <c r="L76" t="n">
-        <v>78.5</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>44.02</v>
+        <v>45.84</v>
       </c>
       <c r="K77" t="n">
-        <v>27.31</v>
+        <v>28.44</v>
       </c>
       <c r="L77" t="n">
-        <v>51.8</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-42.09</v>
+        <v>-43.87</v>
       </c>
       <c r="K78" t="n">
-        <v>61.31</v>
+        <v>63.9</v>
       </c>
       <c r="L78" t="n">
-        <v>74.36</v>
+        <v>77.51000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>62.68</v>
+        <v>64.52</v>
       </c>
       <c r="K79" t="n">
-        <v>-51.43</v>
+        <v>-52.94</v>
       </c>
       <c r="L79" t="n">
-        <v>81.08</v>
+        <v>83.45999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>86.47</v>
+        <v>95.75</v>
       </c>
       <c r="K80" t="n">
-        <v>-65.87</v>
+        <v>-72.93000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>108.7</v>
+        <v>120.36</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-5.02</v>
+        <v>-5.52</v>
       </c>
       <c r="K81" t="n">
-        <v>-92.33</v>
+        <v>-101.48</v>
       </c>
       <c r="L81" t="n">
-        <v>92.47</v>
+        <v>101.63</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-79.09</v>
+        <v>-85.90000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>74.65000000000001</v>
+        <v>81.08</v>
       </c>
       <c r="L82" t="n">
-        <v>108.75</v>
+        <v>118.12</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>59.96</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>124.7</v>
+        <v>141.27</v>
       </c>
       <c r="L83" t="n">
-        <v>138.37</v>
+        <v>156.76</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-113.73</v>
+        <v>-124.57</v>
       </c>
       <c r="K84" t="n">
-        <v>76.12</v>
+        <v>83.38</v>
       </c>
       <c r="L84" t="n">
-        <v>136.85</v>
+        <v>149.9</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-41.25</v>
+        <v>-45.17</v>
       </c>
       <c r="K85" t="n">
-        <v>-133.64</v>
+        <v>-146.35</v>
       </c>
       <c r="L85" t="n">
-        <v>139.86</v>
+        <v>153.16</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>209.88</v>
+        <v>246.45</v>
       </c>
       <c r="K86" t="n">
-        <v>-119.1</v>
+        <v>-139.85</v>
       </c>
       <c r="L86" t="n">
-        <v>241.32</v>
+        <v>283.36</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-40.2</v>
+        <v>-46.8</v>
       </c>
       <c r="K87" t="n">
-        <v>-188.6</v>
+        <v>-219.56</v>
       </c>
       <c r="L87" t="n">
-        <v>192.84</v>
+        <v>224.49</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-187.74</v>
+        <v>-218.93</v>
       </c>
       <c r="K88" t="n">
-        <v>30.32</v>
+        <v>35.36</v>
       </c>
       <c r="L88" t="n">
-        <v>190.17</v>
+        <v>221.77</v>
       </c>
     </row>
   </sheetData>
